--- a/output/Grille_horaire.xlsx
+++ b/output/Grille_horaire.xlsx
@@ -162,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,7 +181,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -555,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:EP26"/>
+  <dimension ref="A1:EP28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -908,10 +907,10 @@
       <c r="EO2" s="4" t="n"/>
       <c r="EP2" s="4" t="n"/>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" ht="17.33333333333333" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Grande Scène</t>
+          <t>La Ruche</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
@@ -941,24 +940,28 @@
       <c r="AA3" s="6" t="n"/>
       <c r="AB3" s="7" t="n"/>
       <c r="AC3" s="7" t="n"/>
-      <c r="AD3" s="7" t="n"/>
-      <c r="AE3" s="7" t="n"/>
-      <c r="AF3" s="7" t="n"/>
-      <c r="AG3" s="7" t="n"/>
-      <c r="AH3" s="7" t="n"/>
-      <c r="AI3" s="7" t="n"/>
-      <c r="AJ3" s="7" t="n"/>
-      <c r="AK3" s="7" t="n"/>
-      <c r="AL3" s="7" t="n"/>
-      <c r="AM3" s="6" t="n"/>
-      <c r="AN3" s="7" t="n"/>
-      <c r="AO3" s="7" t="n"/>
+      <c r="AD3" s="8" t="inlineStr">
+        <is>
+          <t>T'es rien sans la terre</t>
+        </is>
+      </c>
+      <c r="AE3" s="9" t="n"/>
+      <c r="AF3" s="9" t="n"/>
+      <c r="AG3" s="9" t="n"/>
+      <c r="AH3" s="9" t="n"/>
+      <c r="AI3" s="9" t="n"/>
+      <c r="AJ3" s="9" t="n"/>
+      <c r="AK3" s="9" t="n"/>
+      <c r="AL3" s="9" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="9" t="n"/>
+      <c r="AO3" s="9" t="n"/>
       <c r="AP3" s="7" t="n"/>
       <c r="AQ3" s="7" t="n"/>
       <c r="AR3" s="7" t="n"/>
       <c r="AS3" s="8" t="inlineStr">
         <is>
-          <t>Suzane</t>
+          <t>Phusis</t>
         </is>
       </c>
       <c r="AT3" s="9" t="n"/>
@@ -969,32 +972,36 @@
       <c r="AY3" s="10" t="n"/>
       <c r="AZ3" s="9" t="n"/>
       <c r="BA3" s="9" t="n"/>
-      <c r="BB3" s="9" t="n"/>
-      <c r="BC3" s="9" t="n"/>
-      <c r="BD3" s="9" t="n"/>
-      <c r="BE3" s="7" t="n"/>
-      <c r="BF3" s="7" t="n"/>
-      <c r="BG3" s="7" t="n"/>
-      <c r="BH3" s="7" t="n"/>
-      <c r="BI3" s="7" t="n"/>
-      <c r="BJ3" s="7" t="n"/>
-      <c r="BK3" s="6" t="n"/>
-      <c r="BL3" s="7" t="n"/>
-      <c r="BM3" s="7" t="n"/>
-      <c r="BN3" s="7" t="n"/>
-      <c r="BO3" s="7" t="n"/>
-      <c r="BP3" s="7" t="n"/>
+      <c r="BB3" s="7" t="n"/>
+      <c r="BC3" s="7" t="n"/>
+      <c r="BD3" s="7" t="n"/>
+      <c r="BE3" s="8" t="inlineStr">
+        <is>
+          <t>Les PCGB</t>
+        </is>
+      </c>
+      <c r="BF3" s="9" t="n"/>
+      <c r="BG3" s="9" t="n"/>
+      <c r="BH3" s="9" t="n"/>
+      <c r="BI3" s="9" t="n"/>
+      <c r="BJ3" s="9" t="n"/>
+      <c r="BK3" s="10" t="n"/>
+      <c r="BL3" s="9" t="n"/>
+      <c r="BM3" s="9" t="n"/>
+      <c r="BN3" s="9" t="n"/>
+      <c r="BO3" s="9" t="n"/>
+      <c r="BP3" s="9" t="n"/>
       <c r="BQ3" s="7" t="n"/>
       <c r="BR3" s="7" t="n"/>
       <c r="BS3" s="7" t="n"/>
-      <c r="BT3" s="7" t="n"/>
-      <c r="BU3" s="7" t="n"/>
-      <c r="BV3" s="7" t="n"/>
-      <c r="BW3" s="11" t="inlineStr">
-        <is>
-          <t>Lorde</t>
-        </is>
-      </c>
+      <c r="BT3" s="8" t="inlineStr">
+        <is>
+          <t>Les Frères Jacquard</t>
+        </is>
+      </c>
+      <c r="BU3" s="9" t="n"/>
+      <c r="BV3" s="9" t="n"/>
+      <c r="BW3" s="10" t="n"/>
       <c r="BX3" s="9" t="n"/>
       <c r="BY3" s="9" t="n"/>
       <c r="BZ3" s="9" t="n"/>
@@ -1007,50 +1014,54 @@
       <c r="CG3" s="9" t="n"/>
       <c r="CH3" s="9" t="n"/>
       <c r="CI3" s="10" t="n"/>
-      <c r="CJ3" s="9" t="n"/>
-      <c r="CK3" s="9" t="n"/>
-      <c r="CL3" s="7" t="n"/>
-      <c r="CM3" s="7" t="n"/>
-      <c r="CN3" s="7" t="n"/>
-      <c r="CO3" s="7" t="n"/>
-      <c r="CP3" s="7" t="n"/>
-      <c r="CQ3" s="7" t="n"/>
+      <c r="CJ3" s="7" t="n"/>
+      <c r="CK3" s="7" t="n"/>
+      <c r="CL3" s="8" t="inlineStr">
+        <is>
+          <t>Spoutnik Disko Mobil</t>
+        </is>
+      </c>
+      <c r="CM3" s="9" t="n"/>
+      <c r="CN3" s="9" t="n"/>
+      <c r="CO3" s="9" t="n"/>
+      <c r="CP3" s="9" t="n"/>
+      <c r="CQ3" s="9" t="n"/>
       <c r="CR3" s="7" t="n"/>
       <c r="CS3" s="7" t="n"/>
-      <c r="CT3" s="7" t="n"/>
-      <c r="CU3" s="6" t="n"/>
-      <c r="CV3" s="7" t="n"/>
-      <c r="CW3" s="7" t="n"/>
-      <c r="CX3" s="7" t="n"/>
-      <c r="CY3" s="7" t="n"/>
-      <c r="CZ3" s="7" t="n"/>
-      <c r="DA3" s="7" t="n"/>
-      <c r="DB3" s="7" t="n"/>
+      <c r="CT3" s="8" t="inlineStr">
+        <is>
+          <t>Volkanik</t>
+        </is>
+      </c>
+      <c r="CU3" s="10" t="n"/>
+      <c r="CV3" s="9" t="n"/>
+      <c r="CW3" s="9" t="n"/>
+      <c r="CX3" s="9" t="n"/>
+      <c r="CY3" s="9" t="n"/>
+      <c r="CZ3" s="9" t="n"/>
+      <c r="DA3" s="9" t="n"/>
+      <c r="DB3" s="9" t="n"/>
       <c r="DC3" s="7" t="n"/>
       <c r="DD3" s="7" t="n"/>
-      <c r="DE3" s="8" t="inlineStr">
-        <is>
-          <t>Twenty One Pilots</t>
-        </is>
-      </c>
-      <c r="DF3" s="9" t="n"/>
-      <c r="DG3" s="10" t="n"/>
-      <c r="DH3" s="9" t="n"/>
-      <c r="DI3" s="9" t="n"/>
-      <c r="DJ3" s="9" t="n"/>
-      <c r="DK3" s="9" t="n"/>
-      <c r="DL3" s="9" t="n"/>
-      <c r="DM3" s="9" t="n"/>
-      <c r="DN3" s="9" t="n"/>
-      <c r="DO3" s="9" t="n"/>
-      <c r="DP3" s="9" t="n"/>
-      <c r="DQ3" s="9" t="n"/>
-      <c r="DR3" s="9" t="n"/>
-      <c r="DS3" s="10" t="n"/>
-      <c r="DT3" s="9" t="n"/>
-      <c r="DU3" s="9" t="n"/>
-      <c r="DV3" s="9" t="n"/>
-      <c r="DW3" s="9" t="n"/>
+      <c r="DE3" s="7" t="n"/>
+      <c r="DF3" s="7" t="n"/>
+      <c r="DG3" s="6" t="n"/>
+      <c r="DH3" s="7" t="n"/>
+      <c r="DI3" s="7" t="n"/>
+      <c r="DJ3" s="7" t="n"/>
+      <c r="DK3" s="7" t="n"/>
+      <c r="DL3" s="7" t="n"/>
+      <c r="DM3" s="7" t="n"/>
+      <c r="DN3" s="7" t="n"/>
+      <c r="DO3" s="7" t="n"/>
+      <c r="DP3" s="7" t="n"/>
+      <c r="DQ3" s="7" t="n"/>
+      <c r="DR3" s="7" t="n"/>
+      <c r="DS3" s="6" t="n"/>
+      <c r="DT3" s="7" t="n"/>
+      <c r="DU3" s="7" t="n"/>
+      <c r="DV3" s="7" t="n"/>
+      <c r="DW3" s="7" t="n"/>
       <c r="DX3" s="7" t="n"/>
       <c r="DY3" s="7" t="n"/>
       <c r="DZ3" s="7" t="n"/>
@@ -1071,12 +1082,8 @@
       <c r="EO3" s="7" t="n"/>
       <c r="EP3" s="7" t="n"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Véga</t>
-        </is>
-      </c>
+    <row r="4" ht="17.33333333333333" customHeight="1">
+      <c r="A4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="7" t="n"/>
@@ -1089,56 +1096,56 @@
       <c r="L4" s="7" t="n"/>
       <c r="M4" s="7" t="n"/>
       <c r="N4" s="7" t="n"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="7" t="n"/>
-      <c r="Q4" s="7" t="n"/>
-      <c r="R4" s="7" t="n"/>
-      <c r="S4" s="7" t="n"/>
-      <c r="T4" s="7" t="n"/>
-      <c r="U4" s="7" t="n"/>
-      <c r="V4" s="7" t="n"/>
-      <c r="W4" s="7" t="n"/>
-      <c r="X4" s="7" t="n"/>
-      <c r="Y4" s="7" t="n"/>
-      <c r="Z4" s="7" t="n"/>
-      <c r="AA4" s="6" t="n"/>
-      <c r="AB4" s="7" t="n"/>
-      <c r="AC4" s="7" t="n"/>
-      <c r="AD4" s="7" t="n"/>
-      <c r="AE4" s="7" t="n"/>
-      <c r="AF4" s="7" t="n"/>
-      <c r="AG4" s="7" t="n"/>
-      <c r="AH4" s="7" t="n"/>
-      <c r="AI4" s="7" t="n"/>
-      <c r="AJ4" s="7" t="n"/>
-      <c r="AK4" s="7" t="n"/>
-      <c r="AL4" s="7" t="n"/>
-      <c r="AM4" s="6" t="n"/>
-      <c r="AN4" s="7" t="n"/>
-      <c r="AO4" s="7" t="n"/>
-      <c r="AP4" s="7" t="n"/>
-      <c r="AQ4" s="7" t="n"/>
-      <c r="AR4" s="7" t="n"/>
-      <c r="AS4" s="7" t="n"/>
-      <c r="AT4" s="7" t="n"/>
-      <c r="AU4" s="7" t="n"/>
-      <c r="AV4" s="7" t="n"/>
-      <c r="AW4" s="7" t="n"/>
-      <c r="AX4" s="7" t="n"/>
-      <c r="AY4" s="6" t="n"/>
-      <c r="AZ4" s="7" t="n"/>
-      <c r="BA4" s="7" t="n"/>
-      <c r="BB4" s="7" t="n"/>
-      <c r="BC4" s="7" t="n"/>
-      <c r="BD4" s="7" t="n"/>
-      <c r="BE4" s="7" t="n"/>
-      <c r="BF4" s="7" t="n"/>
-      <c r="BG4" s="7" t="n"/>
-      <c r="BH4" s="8" t="inlineStr">
-        <is>
-          <t>Balu Brigada</t>
-        </is>
-      </c>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>Surprises foraines</t>
+        </is>
+      </c>
+      <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="9" t="n"/>
+      <c r="T4" s="9" t="n"/>
+      <c r="U4" s="9" t="n"/>
+      <c r="V4" s="9" t="n"/>
+      <c r="W4" s="9" t="n"/>
+      <c r="X4" s="9" t="n"/>
+      <c r="Y4" s="9" t="n"/>
+      <c r="Z4" s="9" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="9" t="n"/>
+      <c r="AC4" s="9" t="n"/>
+      <c r="AD4" s="9" t="n"/>
+      <c r="AE4" s="9" t="n"/>
+      <c r="AF4" s="9" t="n"/>
+      <c r="AG4" s="9" t="n"/>
+      <c r="AH4" s="9" t="n"/>
+      <c r="AI4" s="9" t="n"/>
+      <c r="AJ4" s="9" t="n"/>
+      <c r="AK4" s="9" t="n"/>
+      <c r="AL4" s="9" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="9" t="n"/>
+      <c r="AO4" s="9" t="n"/>
+      <c r="AP4" s="9" t="n"/>
+      <c r="AQ4" s="9" t="n"/>
+      <c r="AR4" s="9" t="n"/>
+      <c r="AS4" s="9" t="n"/>
+      <c r="AT4" s="9" t="n"/>
+      <c r="AU4" s="9" t="n"/>
+      <c r="AV4" s="9" t="n"/>
+      <c r="AW4" s="9" t="n"/>
+      <c r="AX4" s="9" t="n"/>
+      <c r="AY4" s="10" t="n"/>
+      <c r="AZ4" s="9" t="n"/>
+      <c r="BA4" s="9" t="n"/>
+      <c r="BB4" s="9" t="n"/>
+      <c r="BC4" s="9" t="n"/>
+      <c r="BD4" s="9" t="n"/>
+      <c r="BE4" s="9" t="n"/>
+      <c r="BF4" s="9" t="n"/>
+      <c r="BG4" s="9" t="n"/>
+      <c r="BH4" s="9" t="n"/>
       <c r="BI4" s="9" t="n"/>
       <c r="BJ4" s="9" t="n"/>
       <c r="BK4" s="10" t="n"/>
@@ -1150,45 +1157,41 @@
       <c r="BQ4" s="9" t="n"/>
       <c r="BR4" s="9" t="n"/>
       <c r="BS4" s="9" t="n"/>
-      <c r="BT4" s="7" t="n"/>
-      <c r="BU4" s="7" t="n"/>
-      <c r="BV4" s="7" t="n"/>
-      <c r="BW4" s="6" t="n"/>
-      <c r="BX4" s="7" t="n"/>
-      <c r="BY4" s="7" t="n"/>
-      <c r="BZ4" s="7" t="n"/>
-      <c r="CA4" s="7" t="n"/>
-      <c r="CB4" s="7" t="n"/>
-      <c r="CC4" s="7" t="n"/>
-      <c r="CD4" s="7" t="n"/>
-      <c r="CE4" s="7" t="n"/>
-      <c r="CF4" s="7" t="n"/>
-      <c r="CG4" s="7" t="n"/>
-      <c r="CH4" s="7" t="n"/>
+      <c r="BT4" s="9" t="n"/>
+      <c r="BU4" s="9" t="n"/>
+      <c r="BV4" s="9" t="n"/>
+      <c r="BW4" s="10" t="n"/>
+      <c r="BX4" s="9" t="n"/>
+      <c r="BY4" s="9" t="n"/>
+      <c r="BZ4" s="9" t="n"/>
+      <c r="CA4" s="9" t="n"/>
+      <c r="CB4" s="9" t="n"/>
+      <c r="CC4" s="9" t="n"/>
+      <c r="CD4" s="9" t="n"/>
+      <c r="CE4" s="9" t="n"/>
+      <c r="CF4" s="9" t="n"/>
+      <c r="CG4" s="9" t="n"/>
+      <c r="CH4" s="9" t="n"/>
       <c r="CI4" s="6" t="n"/>
       <c r="CJ4" s="7" t="n"/>
       <c r="CK4" s="7" t="n"/>
       <c r="CL4" s="7" t="n"/>
       <c r="CM4" s="7" t="n"/>
-      <c r="CN4" s="8" t="inlineStr">
-        <is>
-          <t>Asaf Avidan</t>
-        </is>
-      </c>
-      <c r="CO4" s="9" t="n"/>
-      <c r="CP4" s="9" t="n"/>
-      <c r="CQ4" s="9" t="n"/>
-      <c r="CR4" s="9" t="n"/>
-      <c r="CS4" s="9" t="n"/>
-      <c r="CT4" s="9" t="n"/>
-      <c r="CU4" s="10" t="n"/>
-      <c r="CV4" s="9" t="n"/>
-      <c r="CW4" s="9" t="n"/>
-      <c r="CX4" s="9" t="n"/>
-      <c r="CY4" s="9" t="n"/>
-      <c r="CZ4" s="9" t="n"/>
-      <c r="DA4" s="9" t="n"/>
-      <c r="DB4" s="9" t="n"/>
+      <c r="CN4" s="7" t="n"/>
+      <c r="CO4" s="7" t="n"/>
+      <c r="CP4" s="7" t="n"/>
+      <c r="CQ4" s="7" t="n"/>
+      <c r="CR4" s="7" t="n"/>
+      <c r="CS4" s="7" t="n"/>
+      <c r="CT4" s="7" t="n"/>
+      <c r="CU4" s="6" t="n"/>
+      <c r="CV4" s="7" t="n"/>
+      <c r="CW4" s="7" t="n"/>
+      <c r="CX4" s="7" t="n"/>
+      <c r="CY4" s="7" t="n"/>
+      <c r="CZ4" s="7" t="n"/>
+      <c r="DA4" s="7" t="n"/>
+      <c r="DB4" s="7" t="n"/>
       <c r="DC4" s="7" t="n"/>
       <c r="DD4" s="7" t="n"/>
       <c r="DE4" s="7" t="n"/>
@@ -1211,22 +1214,18 @@
       <c r="DV4" s="7" t="n"/>
       <c r="DW4" s="7" t="n"/>
       <c r="DX4" s="7" t="n"/>
-      <c r="DY4" s="8" t="inlineStr">
-        <is>
-          <t>Perceval</t>
-        </is>
-      </c>
-      <c r="DZ4" s="9" t="n"/>
-      <c r="EA4" s="9" t="n"/>
-      <c r="EB4" s="9" t="n"/>
-      <c r="EC4" s="9" t="n"/>
-      <c r="ED4" s="9" t="n"/>
-      <c r="EE4" s="10" t="n"/>
-      <c r="EF4" s="9" t="n"/>
-      <c r="EG4" s="9" t="n"/>
-      <c r="EH4" s="9" t="n"/>
-      <c r="EI4" s="9" t="n"/>
-      <c r="EJ4" s="9" t="n"/>
+      <c r="DY4" s="7" t="n"/>
+      <c r="DZ4" s="7" t="n"/>
+      <c r="EA4" s="7" t="n"/>
+      <c r="EB4" s="7" t="n"/>
+      <c r="EC4" s="7" t="n"/>
+      <c r="ED4" s="7" t="n"/>
+      <c r="EE4" s="6" t="n"/>
+      <c r="EF4" s="7" t="n"/>
+      <c r="EG4" s="7" t="n"/>
+      <c r="EH4" s="7" t="n"/>
+      <c r="EI4" s="7" t="n"/>
+      <c r="EJ4" s="7" t="n"/>
       <c r="EK4" s="7" t="n"/>
       <c r="EL4" s="7" t="n"/>
       <c r="EM4" s="7" t="n"/>
@@ -1234,10 +1233,10 @@
       <c r="EO4" s="7" t="n"/>
       <c r="EP4" s="7" t="n"/>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Abeilles Ruche</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
@@ -1252,120 +1251,132 @@
       <c r="L5" s="7" t="n"/>
       <c r="M5" s="7" t="n"/>
       <c r="N5" s="7" t="n"/>
-      <c r="O5" s="6" t="n"/>
-      <c r="P5" s="7" t="n"/>
-      <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="7" t="n"/>
-      <c r="S5" s="7" t="n"/>
-      <c r="T5" s="7" t="n"/>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="6" t="n"/>
-      <c r="AB5" s="7" t="n"/>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="8" t="inlineStr">
-        <is>
-          <t>Club Katel</t>
-        </is>
-      </c>
-      <c r="AE5" s="9" t="n"/>
-      <c r="AF5" s="9" t="n"/>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="9" t="n"/>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="9" t="n"/>
-      <c r="AM5" s="10" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="9" t="n"/>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="9" t="n"/>
-      <c r="AR5" s="9" t="n"/>
-      <c r="AS5" s="7" t="n"/>
-      <c r="AT5" s="7" t="n"/>
-      <c r="AU5" s="7" t="n"/>
-      <c r="AV5" s="7" t="n"/>
-      <c r="AW5" s="7" t="n"/>
-      <c r="AX5" s="7" t="n"/>
-      <c r="AY5" s="6" t="n"/>
-      <c r="AZ5" s="7" t="n"/>
-      <c r="BA5" s="7" t="n"/>
-      <c r="BB5" s="7" t="n"/>
-      <c r="BC5" s="7" t="n"/>
-      <c r="BD5" s="7" t="n"/>
-      <c r="BE5" s="8" t="inlineStr">
-        <is>
-          <t>Dylan Dylan</t>
-        </is>
-      </c>
-      <c r="BF5" s="9" t="n"/>
-      <c r="BG5" s="9" t="n"/>
-      <c r="BH5" s="9" t="n"/>
-      <c r="BI5" s="9" t="n"/>
-      <c r="BJ5" s="9" t="n"/>
-      <c r="BK5" s="10" t="n"/>
-      <c r="BL5" s="9" t="n"/>
-      <c r="BM5" s="9" t="n"/>
-      <c r="BN5" s="9" t="n"/>
-      <c r="BO5" s="9" t="n"/>
-      <c r="BP5" s="9" t="n"/>
-      <c r="BQ5" s="9" t="n"/>
-      <c r="BR5" s="9" t="n"/>
-      <c r="BS5" s="9" t="n"/>
-      <c r="BT5" s="9" t="n"/>
-      <c r="BU5" s="9" t="n"/>
-      <c r="BV5" s="7" t="n"/>
-      <c r="BW5" s="6" t="n"/>
-      <c r="BX5" s="7" t="n"/>
-      <c r="BY5" s="7" t="n"/>
-      <c r="BZ5" s="7" t="n"/>
-      <c r="CA5" s="7" t="n"/>
-      <c r="CB5" s="7" t="n"/>
-      <c r="CC5" s="7" t="n"/>
-      <c r="CD5" s="7" t="n"/>
-      <c r="CE5" s="7" t="n"/>
-      <c r="CF5" s="7" t="n"/>
-      <c r="CG5" s="7" t="n"/>
-      <c r="CH5" s="7" t="n"/>
-      <c r="CI5" s="6" t="n"/>
-      <c r="CJ5" s="7" t="n"/>
-      <c r="CK5" s="7" t="n"/>
-      <c r="CL5" s="8" t="inlineStr">
-        <is>
-          <t>okgiorgio</t>
-        </is>
-      </c>
-      <c r="CM5" s="9" t="n"/>
-      <c r="CN5" s="9" t="n"/>
-      <c r="CO5" s="9" t="n"/>
-      <c r="CP5" s="9" t="n"/>
-      <c r="CQ5" s="9" t="n"/>
-      <c r="CR5" s="9" t="n"/>
-      <c r="CS5" s="9" t="n"/>
-      <c r="CT5" s="9" t="n"/>
-      <c r="CU5" s="10" t="n"/>
-      <c r="CV5" s="9" t="n"/>
-      <c r="CW5" s="9" t="n"/>
-      <c r="CX5" s="9" t="n"/>
-      <c r="CY5" s="9" t="n"/>
-      <c r="CZ5" s="9" t="n"/>
-      <c r="DA5" s="9" t="n"/>
-      <c r="DB5" s="9" t="n"/>
-      <c r="DC5" s="9" t="n"/>
-      <c r="DD5" s="7" t="n"/>
-      <c r="DE5" s="7" t="n"/>
-      <c r="DF5" s="7" t="n"/>
-      <c r="DG5" s="6" t="n"/>
-      <c r="DH5" s="7" t="n"/>
-      <c r="DI5" s="7" t="n"/>
-      <c r="DJ5" s="7" t="n"/>
-      <c r="DK5" s="7" t="n"/>
-      <c r="DL5" s="7" t="n"/>
+      <c r="O5" s="12" t="inlineStr">
+        <is>
+          <t>Mickaël, Yann, Ysatis</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="14" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="15" t="inlineStr">
+        <is>
+          <t>Nathalia, Noah, Raphaëlle</t>
+        </is>
+      </c>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
+      <c r="AJ5" s="13" t="n"/>
+      <c r="AK5" s="13" t="n"/>
+      <c r="AL5" s="13" t="n"/>
+      <c r="AM5" s="14" t="n"/>
+      <c r="AN5" s="13" t="n"/>
+      <c r="AO5" s="13" t="n"/>
+      <c r="AP5" s="13" t="n"/>
+      <c r="AQ5" s="13" t="n"/>
+      <c r="AR5" s="13" t="n"/>
+      <c r="AS5" s="13" t="n"/>
+      <c r="AT5" s="13" t="n"/>
+      <c r="AU5" s="13" t="n"/>
+      <c r="AV5" s="13" t="n"/>
+      <c r="AW5" s="13" t="n"/>
+      <c r="AX5" s="13" t="n"/>
+      <c r="AY5" s="12" t="inlineStr">
+        <is>
+          <t>Alexandra, Lisa J., Morgane</t>
+        </is>
+      </c>
+      <c r="AZ5" s="13" t="n"/>
+      <c r="BA5" s="13" t="n"/>
+      <c r="BB5" s="13" t="n"/>
+      <c r="BC5" s="13" t="n"/>
+      <c r="BD5" s="13" t="n"/>
+      <c r="BE5" s="13" t="n"/>
+      <c r="BF5" s="13" t="n"/>
+      <c r="BG5" s="13" t="n"/>
+      <c r="BH5" s="13" t="n"/>
+      <c r="BI5" s="13" t="n"/>
+      <c r="BJ5" s="13" t="n"/>
+      <c r="BK5" s="14" t="n"/>
+      <c r="BL5" s="13" t="n"/>
+      <c r="BM5" s="13" t="n"/>
+      <c r="BN5" s="13" t="n"/>
+      <c r="BO5" s="13" t="n"/>
+      <c r="BP5" s="13" t="n"/>
+      <c r="BQ5" s="15" t="inlineStr">
+        <is>
+          <t>Alegria Lily, Jolan, Mickaël</t>
+        </is>
+      </c>
+      <c r="BR5" s="13" t="n"/>
+      <c r="BS5" s="13" t="n"/>
+      <c r="BT5" s="13" t="n"/>
+      <c r="BU5" s="13" t="n"/>
+      <c r="BV5" s="13" t="n"/>
+      <c r="BW5" s="14" t="n"/>
+      <c r="BX5" s="13" t="n"/>
+      <c r="BY5" s="13" t="n"/>
+      <c r="BZ5" s="13" t="n"/>
+      <c r="CA5" s="13" t="n"/>
+      <c r="CB5" s="13" t="n"/>
+      <c r="CC5" s="13" t="n"/>
+      <c r="CD5" s="13" t="n"/>
+      <c r="CE5" s="13" t="n"/>
+      <c r="CF5" s="13" t="n"/>
+      <c r="CG5" s="13" t="n"/>
+      <c r="CH5" s="13" t="n"/>
+      <c r="CI5" s="12" t="inlineStr">
+        <is>
+          <t>Noah, Raphaëlle, Tristan</t>
+        </is>
+      </c>
+      <c r="CJ5" s="13" t="n"/>
+      <c r="CK5" s="13" t="n"/>
+      <c r="CL5" s="13" t="n"/>
+      <c r="CM5" s="13" t="n"/>
+      <c r="CN5" s="13" t="n"/>
+      <c r="CO5" s="13" t="n"/>
+      <c r="CP5" s="13" t="n"/>
+      <c r="CQ5" s="13" t="n"/>
+      <c r="CR5" s="13" t="n"/>
+      <c r="CS5" s="13" t="n"/>
+      <c r="CT5" s="13" t="n"/>
+      <c r="CU5" s="14" t="n"/>
+      <c r="CV5" s="13" t="n"/>
+      <c r="CW5" s="13" t="n"/>
+      <c r="CX5" s="13" t="n"/>
+      <c r="CY5" s="13" t="n"/>
+      <c r="CZ5" s="13" t="n"/>
+      <c r="DA5" s="15" t="inlineStr">
+        <is>
+          <t>Mireille, Thibault</t>
+        </is>
+      </c>
+      <c r="DB5" s="13" t="n"/>
+      <c r="DC5" s="13" t="n"/>
+      <c r="DD5" s="13" t="n"/>
+      <c r="DE5" s="13" t="n"/>
+      <c r="DF5" s="13" t="n"/>
+      <c r="DG5" s="14" t="n"/>
+      <c r="DH5" s="13" t="n"/>
+      <c r="DI5" s="13" t="n"/>
+      <c r="DJ5" s="13" t="n"/>
+      <c r="DK5" s="13" t="n"/>
+      <c r="DL5" s="13" t="n"/>
       <c r="DM5" s="7" t="n"/>
       <c r="DN5" s="7" t="n"/>
       <c r="DO5" s="7" t="n"/>
@@ -1377,23 +1388,19 @@
       <c r="DU5" s="7" t="n"/>
       <c r="DV5" s="7" t="n"/>
       <c r="DW5" s="7" t="n"/>
-      <c r="DX5" s="8" t="inlineStr">
-        <is>
-          <t>Upsilone</t>
-        </is>
-      </c>
-      <c r="DY5" s="9" t="n"/>
-      <c r="DZ5" s="9" t="n"/>
-      <c r="EA5" s="9" t="n"/>
-      <c r="EB5" s="9" t="n"/>
-      <c r="EC5" s="9" t="n"/>
-      <c r="ED5" s="9" t="n"/>
-      <c r="EE5" s="10" t="n"/>
-      <c r="EF5" s="9" t="n"/>
-      <c r="EG5" s="9" t="n"/>
-      <c r="EH5" s="9" t="n"/>
-      <c r="EI5" s="9" t="n"/>
-      <c r="EJ5" s="9" t="n"/>
+      <c r="DX5" s="7" t="n"/>
+      <c r="DY5" s="7" t="n"/>
+      <c r="DZ5" s="7" t="n"/>
+      <c r="EA5" s="7" t="n"/>
+      <c r="EB5" s="7" t="n"/>
+      <c r="EC5" s="7" t="n"/>
+      <c r="ED5" s="7" t="n"/>
+      <c r="EE5" s="6" t="n"/>
+      <c r="EF5" s="7" t="n"/>
+      <c r="EG5" s="7" t="n"/>
+      <c r="EH5" s="7" t="n"/>
+      <c r="EI5" s="7" t="n"/>
+      <c r="EJ5" s="7" t="n"/>
       <c r="EK5" s="7" t="n"/>
       <c r="EL5" s="7" t="n"/>
       <c r="EM5" s="7" t="n"/>
@@ -1401,10 +1408,10 @@
       <c r="EO5" s="7" t="n"/>
       <c r="EP5" s="7" t="n"/>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Dôme</t>
+          <t>Entrée backstage</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -1419,120 +1426,132 @@
       <c r="L6" s="7" t="n"/>
       <c r="M6" s="7" t="n"/>
       <c r="N6" s="7" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
-      <c r="X6" s="7" t="n"/>
-      <c r="Y6" s="7" t="n"/>
-      <c r="Z6" s="7" t="n"/>
-      <c r="AA6" s="6" t="n"/>
-      <c r="AB6" s="7" t="n"/>
-      <c r="AC6" s="7" t="n"/>
-      <c r="AD6" s="8" t="inlineStr">
-        <is>
-          <t>Maustetytöt</t>
-        </is>
-      </c>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="9" t="n"/>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="9" t="n"/>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="9" t="n"/>
-      <c r="AM6" s="10" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="9" t="n"/>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="9" t="n"/>
-      <c r="AR6" s="9" t="n"/>
-      <c r="AS6" s="7" t="n"/>
-      <c r="AT6" s="7" t="n"/>
-      <c r="AU6" s="7" t="n"/>
-      <c r="AV6" s="7" t="n"/>
-      <c r="AW6" s="7" t="n"/>
-      <c r="AX6" s="7" t="n"/>
-      <c r="AY6" s="6" t="n"/>
-      <c r="AZ6" s="7" t="n"/>
-      <c r="BA6" s="7" t="n"/>
-      <c r="BB6" s="7" t="n"/>
-      <c r="BC6" s="7" t="n"/>
-      <c r="BD6" s="7" t="n"/>
-      <c r="BE6" s="8" t="inlineStr">
-        <is>
-          <t>Skald</t>
-        </is>
-      </c>
-      <c r="BF6" s="9" t="n"/>
-      <c r="BG6" s="9" t="n"/>
-      <c r="BH6" s="9" t="n"/>
-      <c r="BI6" s="9" t="n"/>
-      <c r="BJ6" s="9" t="n"/>
-      <c r="BK6" s="10" t="n"/>
-      <c r="BL6" s="9" t="n"/>
-      <c r="BM6" s="9" t="n"/>
-      <c r="BN6" s="9" t="n"/>
-      <c r="BO6" s="9" t="n"/>
-      <c r="BP6" s="9" t="n"/>
-      <c r="BQ6" s="9" t="n"/>
-      <c r="BR6" s="9" t="n"/>
-      <c r="BS6" s="9" t="n"/>
-      <c r="BT6" s="7" t="n"/>
-      <c r="BU6" s="7" t="n"/>
-      <c r="BV6" s="7" t="n"/>
-      <c r="BW6" s="6" t="n"/>
-      <c r="BX6" s="7" t="n"/>
-      <c r="BY6" s="7" t="n"/>
-      <c r="BZ6" s="7" t="n"/>
-      <c r="CA6" s="7" t="n"/>
-      <c r="CB6" s="7" t="n"/>
-      <c r="CC6" s="7" t="n"/>
-      <c r="CD6" s="7" t="n"/>
-      <c r="CE6" s="7" t="n"/>
-      <c r="CF6" s="7" t="n"/>
-      <c r="CG6" s="7" t="n"/>
-      <c r="CH6" s="7" t="n"/>
-      <c r="CI6" s="6" t="n"/>
-      <c r="CJ6" s="7" t="n"/>
-      <c r="CK6" s="7" t="n"/>
-      <c r="CL6" s="7" t="n"/>
-      <c r="CM6" s="7" t="n"/>
-      <c r="CN6" s="7" t="n"/>
-      <c r="CO6" s="8" t="inlineStr">
-        <is>
-          <t>Witch Club Satan</t>
-        </is>
-      </c>
-      <c r="CP6" s="9" t="n"/>
-      <c r="CQ6" s="9" t="n"/>
-      <c r="CR6" s="9" t="n"/>
-      <c r="CS6" s="9" t="n"/>
-      <c r="CT6" s="9" t="n"/>
-      <c r="CU6" s="10" t="n"/>
-      <c r="CV6" s="9" t="n"/>
-      <c r="CW6" s="9" t="n"/>
-      <c r="CX6" s="9" t="n"/>
-      <c r="CY6" s="9" t="n"/>
-      <c r="CZ6" s="9" t="n"/>
-      <c r="DA6" s="7" t="n"/>
-      <c r="DB6" s="7" t="n"/>
-      <c r="DC6" s="7" t="n"/>
-      <c r="DD6" s="7" t="n"/>
-      <c r="DE6" s="7" t="n"/>
-      <c r="DF6" s="7" t="n"/>
-      <c r="DG6" s="6" t="n"/>
-      <c r="DH6" s="7" t="n"/>
-      <c r="DI6" s="7" t="n"/>
-      <c r="DJ6" s="7" t="n"/>
-      <c r="DK6" s="7" t="n"/>
-      <c r="DL6" s="7" t="n"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>Jolan</t>
+        </is>
+      </c>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="13" t="n"/>
+      <c r="R6" s="13" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="13" t="n"/>
+      <c r="U6" s="13" t="n"/>
+      <c r="V6" s="13" t="n"/>
+      <c r="W6" s="13" t="n"/>
+      <c r="X6" s="13" t="n"/>
+      <c r="Y6" s="13" t="n"/>
+      <c r="Z6" s="13" t="n"/>
+      <c r="AA6" s="14" t="n"/>
+      <c r="AB6" s="13" t="n"/>
+      <c r="AC6" s="13" t="n"/>
+      <c r="AD6" s="13" t="n"/>
+      <c r="AE6" s="13" t="n"/>
+      <c r="AF6" s="13" t="n"/>
+      <c r="AG6" s="15" t="inlineStr">
+        <is>
+          <t>Iris</t>
+        </is>
+      </c>
+      <c r="AH6" s="13" t="n"/>
+      <c r="AI6" s="13" t="n"/>
+      <c r="AJ6" s="13" t="n"/>
+      <c r="AK6" s="13" t="n"/>
+      <c r="AL6" s="13" t="n"/>
+      <c r="AM6" s="14" t="n"/>
+      <c r="AN6" s="13" t="n"/>
+      <c r="AO6" s="13" t="n"/>
+      <c r="AP6" s="13" t="n"/>
+      <c r="AQ6" s="13" t="n"/>
+      <c r="AR6" s="13" t="n"/>
+      <c r="AS6" s="13" t="n"/>
+      <c r="AT6" s="13" t="n"/>
+      <c r="AU6" s="13" t="n"/>
+      <c r="AV6" s="13" t="n"/>
+      <c r="AW6" s="13" t="n"/>
+      <c r="AX6" s="13" t="n"/>
+      <c r="AY6" s="12" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="AZ6" s="13" t="n"/>
+      <c r="BA6" s="13" t="n"/>
+      <c r="BB6" s="13" t="n"/>
+      <c r="BC6" s="13" t="n"/>
+      <c r="BD6" s="13" t="n"/>
+      <c r="BE6" s="13" t="n"/>
+      <c r="BF6" s="13" t="n"/>
+      <c r="BG6" s="13" t="n"/>
+      <c r="BH6" s="13" t="n"/>
+      <c r="BI6" s="13" t="n"/>
+      <c r="BJ6" s="13" t="n"/>
+      <c r="BK6" s="14" t="n"/>
+      <c r="BL6" s="13" t="n"/>
+      <c r="BM6" s="13" t="n"/>
+      <c r="BN6" s="13" t="n"/>
+      <c r="BO6" s="13" t="n"/>
+      <c r="BP6" s="13" t="n"/>
+      <c r="BQ6" s="15" t="inlineStr">
+        <is>
+          <t>Arsène</t>
+        </is>
+      </c>
+      <c r="BR6" s="13" t="n"/>
+      <c r="BS6" s="13" t="n"/>
+      <c r="BT6" s="13" t="n"/>
+      <c r="BU6" s="13" t="n"/>
+      <c r="BV6" s="13" t="n"/>
+      <c r="BW6" s="14" t="n"/>
+      <c r="BX6" s="13" t="n"/>
+      <c r="BY6" s="13" t="n"/>
+      <c r="BZ6" s="13" t="n"/>
+      <c r="CA6" s="13" t="n"/>
+      <c r="CB6" s="13" t="n"/>
+      <c r="CC6" s="13" t="n"/>
+      <c r="CD6" s="13" t="n"/>
+      <c r="CE6" s="13" t="n"/>
+      <c r="CF6" s="13" t="n"/>
+      <c r="CG6" s="13" t="n"/>
+      <c r="CH6" s="13" t="n"/>
+      <c r="CI6" s="12" t="inlineStr">
+        <is>
+          <t>Iris</t>
+        </is>
+      </c>
+      <c r="CJ6" s="13" t="n"/>
+      <c r="CK6" s="13" t="n"/>
+      <c r="CL6" s="13" t="n"/>
+      <c r="CM6" s="13" t="n"/>
+      <c r="CN6" s="13" t="n"/>
+      <c r="CO6" s="13" t="n"/>
+      <c r="CP6" s="13" t="n"/>
+      <c r="CQ6" s="13" t="n"/>
+      <c r="CR6" s="13" t="n"/>
+      <c r="CS6" s="13" t="n"/>
+      <c r="CT6" s="13" t="n"/>
+      <c r="CU6" s="14" t="n"/>
+      <c r="CV6" s="13" t="n"/>
+      <c r="CW6" s="13" t="n"/>
+      <c r="CX6" s="13" t="n"/>
+      <c r="CY6" s="13" t="n"/>
+      <c r="CZ6" s="13" t="n"/>
+      <c r="DA6" s="15" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="DB6" s="13" t="n"/>
+      <c r="DC6" s="13" t="n"/>
+      <c r="DD6" s="13" t="n"/>
+      <c r="DE6" s="13" t="n"/>
+      <c r="DF6" s="13" t="n"/>
+      <c r="DG6" s="14" t="n"/>
+      <c r="DH6" s="13" t="n"/>
+      <c r="DI6" s="13" t="n"/>
+      <c r="DJ6" s="13" t="n"/>
+      <c r="DK6" s="13" t="n"/>
+      <c r="DL6" s="13" t="n"/>
       <c r="DM6" s="7" t="n"/>
       <c r="DN6" s="7" t="n"/>
       <c r="DO6" s="7" t="n"/>
@@ -1564,177 +1583,205 @@
       <c r="EO6" s="7" t="n"/>
       <c r="EP6" s="7" t="n"/>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Club Tent</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="7" t="n"/>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>Soft Loft</t>
-        </is>
-      </c>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="9" t="n"/>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="9" t="n"/>
-      <c r="AA7" s="10" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="9" t="n"/>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="9" t="n"/>
-      <c r="AG7" s="7" t="n"/>
-      <c r="AH7" s="7" t="n"/>
-      <c r="AI7" s="7" t="n"/>
-      <c r="AJ7" s="7" t="n"/>
-      <c r="AK7" s="7" t="n"/>
-      <c r="AL7" s="7" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="7" t="n"/>
-      <c r="AO7" s="7" t="n"/>
-      <c r="AP7" s="7" t="n"/>
-      <c r="AQ7" s="7" t="n"/>
-      <c r="AR7" s="7" t="n"/>
-      <c r="AS7" s="7" t="n"/>
-      <c r="AT7" s="7" t="n"/>
-      <c r="AU7" s="7" t="n"/>
-      <c r="AV7" s="8" t="inlineStr">
-        <is>
-          <t>DITTER</t>
-        </is>
-      </c>
-      <c r="AW7" s="9" t="n"/>
-      <c r="AX7" s="9" t="n"/>
-      <c r="AY7" s="10" t="n"/>
-      <c r="AZ7" s="9" t="n"/>
-      <c r="BA7" s="9" t="n"/>
-      <c r="BB7" s="9" t="n"/>
-      <c r="BC7" s="9" t="n"/>
-      <c r="BD7" s="9" t="n"/>
-      <c r="BE7" s="9" t="n"/>
-      <c r="BF7" s="9" t="n"/>
-      <c r="BG7" s="9" t="n"/>
-      <c r="BH7" s="7" t="n"/>
-      <c r="BI7" s="7" t="n"/>
-      <c r="BJ7" s="7" t="n"/>
-      <c r="BK7" s="6" t="n"/>
-      <c r="BL7" s="7" t="n"/>
-      <c r="BM7" s="7" t="n"/>
-      <c r="BN7" s="7" t="n"/>
-      <c r="BO7" s="7" t="n"/>
-      <c r="BP7" s="7" t="n"/>
-      <c r="BQ7" s="7" t="n"/>
-      <c r="BR7" s="7" t="n"/>
-      <c r="BS7" s="7" t="n"/>
-      <c r="BT7" s="7" t="n"/>
-      <c r="BU7" s="7" t="n"/>
-      <c r="BV7" s="7" t="n"/>
-      <c r="BW7" s="6" t="n"/>
-      <c r="BX7" s="7" t="n"/>
-      <c r="BY7" s="7" t="n"/>
-      <c r="BZ7" s="8" t="inlineStr">
-        <is>
-          <t>Sprints</t>
-        </is>
-      </c>
-      <c r="CA7" s="9" t="n"/>
-      <c r="CB7" s="9" t="n"/>
-      <c r="CC7" s="9" t="n"/>
-      <c r="CD7" s="9" t="n"/>
-      <c r="CE7" s="9" t="n"/>
-      <c r="CF7" s="9" t="n"/>
-      <c r="CG7" s="9" t="n"/>
-      <c r="CH7" s="9" t="n"/>
-      <c r="CI7" s="10" t="n"/>
-      <c r="CJ7" s="9" t="n"/>
-      <c r="CK7" s="9" t="n"/>
-      <c r="CL7" s="7" t="n"/>
-      <c r="CM7" s="7" t="n"/>
-      <c r="CN7" s="7" t="n"/>
-      <c r="CO7" s="7" t="n"/>
-      <c r="CP7" s="7" t="n"/>
-      <c r="CQ7" s="7" t="n"/>
-      <c r="CR7" s="7" t="n"/>
-      <c r="CS7" s="7" t="n"/>
-      <c r="CT7" s="7" t="n"/>
-      <c r="CU7" s="6" t="n"/>
-      <c r="CV7" s="7" t="n"/>
-      <c r="CW7" s="7" t="n"/>
-      <c r="CX7" s="7" t="n"/>
-      <c r="CY7" s="7" t="n"/>
-      <c r="CZ7" s="7" t="n"/>
-      <c r="DA7" s="7" t="n"/>
-      <c r="DB7" s="7" t="n"/>
-      <c r="DC7" s="7" t="n"/>
-      <c r="DD7" s="7" t="n"/>
-      <c r="DE7" s="7" t="n"/>
-      <c r="DF7" s="7" t="n"/>
-      <c r="DG7" s="6" t="n"/>
-      <c r="DH7" s="7" t="n"/>
-      <c r="DI7" s="7" t="n"/>
-      <c r="DJ7" s="7" t="n"/>
-      <c r="DK7" s="7" t="n"/>
-      <c r="DL7" s="7" t="n"/>
-      <c r="DM7" s="8" t="inlineStr">
-        <is>
-          <t>Sam Quealy</t>
-        </is>
-      </c>
-      <c r="DN7" s="9" t="n"/>
-      <c r="DO7" s="9" t="n"/>
-      <c r="DP7" s="9" t="n"/>
-      <c r="DQ7" s="9" t="n"/>
-      <c r="DR7" s="9" t="n"/>
-      <c r="DS7" s="10" t="n"/>
-      <c r="DT7" s="9" t="n"/>
-      <c r="DU7" s="9" t="n"/>
-      <c r="DV7" s="9" t="n"/>
-      <c r="DW7" s="9" t="n"/>
-      <c r="DX7" s="9" t="n"/>
-      <c r="DY7" s="7" t="n"/>
-      <c r="DZ7" s="7" t="n"/>
-      <c r="EA7" s="7" t="n"/>
-      <c r="EB7" s="7" t="n"/>
-      <c r="EC7" s="7" t="n"/>
-      <c r="ED7" s="7" t="n"/>
-      <c r="EE7" s="6" t="n"/>
-      <c r="EF7" s="7" t="n"/>
-      <c r="EG7" s="7" t="n"/>
-      <c r="EH7" s="7" t="n"/>
-      <c r="EI7" s="7" t="n"/>
-      <c r="EJ7" s="7" t="n"/>
-      <c r="EK7" s="7" t="n"/>
-      <c r="EL7" s="7" t="n"/>
-      <c r="EM7" s="7" t="n"/>
-      <c r="EN7" s="7" t="n"/>
-      <c r="EO7" s="7" t="n"/>
-      <c r="EP7" s="7" t="n"/>
+    <row r="7" ht="14" customHeight="1">
+      <c r="A7" s="2" t="n"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n"/>
+      <c r="S7" s="4" t="n"/>
+      <c r="T7" s="4" t="n"/>
+      <c r="U7" s="4" t="n"/>
+      <c r="V7" s="4" t="n"/>
+      <c r="W7" s="4" t="n"/>
+      <c r="X7" s="4" t="n"/>
+      <c r="Y7" s="4" t="n"/>
+      <c r="Z7" s="4" t="n"/>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="n"/>
+      <c r="AC7" s="4" t="n"/>
+      <c r="AD7" s="4" t="n"/>
+      <c r="AE7" s="4" t="n"/>
+      <c r="AF7" s="4" t="n"/>
+      <c r="AG7" s="4" t="n"/>
+      <c r="AH7" s="4" t="n"/>
+      <c r="AI7" s="4" t="n"/>
+      <c r="AJ7" s="4" t="n"/>
+      <c r="AK7" s="4" t="n"/>
+      <c r="AL7" s="4" t="n"/>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="AN7" s="4" t="n"/>
+      <c r="AO7" s="4" t="n"/>
+      <c r="AP7" s="4" t="n"/>
+      <c r="AQ7" s="4" t="n"/>
+      <c r="AR7" s="4" t="n"/>
+      <c r="AS7" s="4" t="n"/>
+      <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="n"/>
+      <c r="AV7" s="4" t="n"/>
+      <c r="AW7" s="4" t="n"/>
+      <c r="AX7" s="4" t="n"/>
+      <c r="AY7" s="3" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="AZ7" s="4" t="n"/>
+      <c r="BA7" s="4" t="n"/>
+      <c r="BB7" s="4" t="n"/>
+      <c r="BC7" s="4" t="n"/>
+      <c r="BD7" s="4" t="n"/>
+      <c r="BE7" s="4" t="n"/>
+      <c r="BF7" s="4" t="n"/>
+      <c r="BG7" s="4" t="n"/>
+      <c r="BH7" s="4" t="n"/>
+      <c r="BI7" s="4" t="n"/>
+      <c r="BJ7" s="4" t="n"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="n"/>
+      <c r="BM7" s="4" t="n"/>
+      <c r="BN7" s="4" t="n"/>
+      <c r="BO7" s="4" t="n"/>
+      <c r="BP7" s="4" t="n"/>
+      <c r="BQ7" s="4" t="n"/>
+      <c r="BR7" s="4" t="n"/>
+      <c r="BS7" s="4" t="n"/>
+      <c r="BT7" s="4" t="n"/>
+      <c r="BU7" s="4" t="n"/>
+      <c r="BV7" s="4" t="n"/>
+      <c r="BW7" s="3" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="BX7" s="4" t="n"/>
+      <c r="BY7" s="4" t="n"/>
+      <c r="BZ7" s="4" t="n"/>
+      <c r="CA7" s="4" t="n"/>
+      <c r="CB7" s="4" t="n"/>
+      <c r="CC7" s="4" t="n"/>
+      <c r="CD7" s="4" t="n"/>
+      <c r="CE7" s="4" t="n"/>
+      <c r="CF7" s="4" t="n"/>
+      <c r="CG7" s="4" t="n"/>
+      <c r="CH7" s="4" t="n"/>
+      <c r="CI7" s="3" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="CJ7" s="4" t="n"/>
+      <c r="CK7" s="4" t="n"/>
+      <c r="CL7" s="4" t="n"/>
+      <c r="CM7" s="4" t="n"/>
+      <c r="CN7" s="4" t="n"/>
+      <c r="CO7" s="4" t="n"/>
+      <c r="CP7" s="4" t="n"/>
+      <c r="CQ7" s="4" t="n"/>
+      <c r="CR7" s="4" t="n"/>
+      <c r="CS7" s="4" t="n"/>
+      <c r="CT7" s="4" t="n"/>
+      <c r="CU7" s="3" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="CV7" s="4" t="n"/>
+      <c r="CW7" s="4" t="n"/>
+      <c r="CX7" s="4" t="n"/>
+      <c r="CY7" s="4" t="n"/>
+      <c r="CZ7" s="4" t="n"/>
+      <c r="DA7" s="4" t="n"/>
+      <c r="DB7" s="4" t="n"/>
+      <c r="DC7" s="4" t="n"/>
+      <c r="DD7" s="4" t="n"/>
+      <c r="DE7" s="4" t="n"/>
+      <c r="DF7" s="4" t="n"/>
+      <c r="DG7" s="3" t="inlineStr">
+        <is>
+          <t>00h</t>
+        </is>
+      </c>
+      <c r="DH7" s="4" t="n"/>
+      <c r="DI7" s="4" t="n"/>
+      <c r="DJ7" s="4" t="n"/>
+      <c r="DK7" s="4" t="n"/>
+      <c r="DL7" s="4" t="n"/>
+      <c r="DM7" s="4" t="n"/>
+      <c r="DN7" s="4" t="n"/>
+      <c r="DO7" s="4" t="n"/>
+      <c r="DP7" s="4" t="n"/>
+      <c r="DQ7" s="4" t="n"/>
+      <c r="DR7" s="4" t="n"/>
+      <c r="DS7" s="3" t="inlineStr">
+        <is>
+          <t>01h</t>
+        </is>
+      </c>
+      <c r="DT7" s="4" t="n"/>
+      <c r="DU7" s="4" t="n"/>
+      <c r="DV7" s="4" t="n"/>
+      <c r="DW7" s="4" t="n"/>
+      <c r="DX7" s="4" t="n"/>
+      <c r="DY7" s="4" t="n"/>
+      <c r="DZ7" s="4" t="n"/>
+      <c r="EA7" s="4" t="n"/>
+      <c r="EB7" s="4" t="n"/>
+      <c r="EC7" s="4" t="n"/>
+      <c r="ED7" s="4" t="n"/>
+      <c r="EE7" s="3" t="inlineStr">
+        <is>
+          <t>02h</t>
+        </is>
+      </c>
+      <c r="EF7" s="4" t="n"/>
+      <c r="EG7" s="4" t="n"/>
+      <c r="EH7" s="4" t="n"/>
+      <c r="EI7" s="4" t="n"/>
+      <c r="EJ7" s="4" t="n"/>
+      <c r="EK7" s="4" t="n"/>
+      <c r="EL7" s="4" t="n"/>
+      <c r="EM7" s="4" t="n"/>
+      <c r="EN7" s="4" t="n"/>
+      <c r="EO7" s="4" t="n"/>
+      <c r="EP7" s="4" t="n"/>
     </row>
-    <row r="8" ht="17.33333333333333" customHeight="1">
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>La Ruche</t>
+          <t>Ailes</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
@@ -1749,126 +1796,118 @@
       <c r="L8" s="7" t="n"/>
       <c r="M8" s="7" t="n"/>
       <c r="N8" s="7" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
-      <c r="X8" s="7" t="n"/>
-      <c r="Y8" s="7" t="n"/>
-      <c r="Z8" s="7" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="7" t="n"/>
-      <c r="AC8" s="7" t="n"/>
-      <c r="AD8" s="8" t="inlineStr">
-        <is>
-          <t>T'es rien sans la terre</t>
-        </is>
-      </c>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="9" t="n"/>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="9" t="n"/>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="9" t="n"/>
-      <c r="AM8" s="10" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="9" t="n"/>
-      <c r="AP8" s="7" t="n"/>
-      <c r="AQ8" s="7" t="n"/>
-      <c r="AR8" s="7" t="n"/>
-      <c r="AS8" s="8" t="inlineStr">
-        <is>
-          <t>Phusis</t>
-        </is>
-      </c>
-      <c r="AT8" s="9" t="n"/>
-      <c r="AU8" s="9" t="n"/>
-      <c r="AV8" s="9" t="n"/>
-      <c r="AW8" s="9" t="n"/>
-      <c r="AX8" s="9" t="n"/>
-      <c r="AY8" s="10" t="n"/>
-      <c r="AZ8" s="9" t="n"/>
-      <c r="BA8" s="9" t="n"/>
-      <c r="BB8" s="7" t="n"/>
-      <c r="BC8" s="7" t="n"/>
-      <c r="BD8" s="7" t="n"/>
-      <c r="BE8" s="8" t="inlineStr">
-        <is>
-          <t>Les PCGB</t>
-        </is>
-      </c>
-      <c r="BF8" s="9" t="n"/>
-      <c r="BG8" s="9" t="n"/>
-      <c r="BH8" s="9" t="n"/>
-      <c r="BI8" s="9" t="n"/>
-      <c r="BJ8" s="9" t="n"/>
-      <c r="BK8" s="10" t="n"/>
-      <c r="BL8" s="9" t="n"/>
-      <c r="BM8" s="9" t="n"/>
-      <c r="BN8" s="9" t="n"/>
-      <c r="BO8" s="9" t="n"/>
-      <c r="BP8" s="9" t="n"/>
-      <c r="BQ8" s="7" t="n"/>
-      <c r="BR8" s="7" t="n"/>
-      <c r="BS8" s="7" t="n"/>
-      <c r="BT8" s="8" t="inlineStr">
-        <is>
-          <t>Les Frères Jacquard</t>
-        </is>
-      </c>
-      <c r="BU8" s="9" t="n"/>
-      <c r="BV8" s="9" t="n"/>
-      <c r="BW8" s="10" t="n"/>
-      <c r="BX8" s="9" t="n"/>
-      <c r="BY8" s="9" t="n"/>
-      <c r="BZ8" s="9" t="n"/>
-      <c r="CA8" s="9" t="n"/>
-      <c r="CB8" s="9" t="n"/>
-      <c r="CC8" s="9" t="n"/>
-      <c r="CD8" s="9" t="n"/>
-      <c r="CE8" s="9" t="n"/>
-      <c r="CF8" s="9" t="n"/>
-      <c r="CG8" s="9" t="n"/>
-      <c r="CH8" s="9" t="n"/>
-      <c r="CI8" s="10" t="n"/>
-      <c r="CJ8" s="7" t="n"/>
-      <c r="CK8" s="7" t="n"/>
-      <c r="CL8" s="8" t="inlineStr">
-        <is>
-          <t>Spoutnik Disko Mobil</t>
-        </is>
-      </c>
-      <c r="CM8" s="9" t="n"/>
-      <c r="CN8" s="9" t="n"/>
-      <c r="CO8" s="9" t="n"/>
-      <c r="CP8" s="9" t="n"/>
-      <c r="CQ8" s="9" t="n"/>
-      <c r="CR8" s="7" t="n"/>
-      <c r="CS8" s="7" t="n"/>
-      <c r="CT8" s="8" t="inlineStr">
-        <is>
-          <t>Volkanik</t>
-        </is>
-      </c>
-      <c r="CU8" s="10" t="n"/>
-      <c r="CV8" s="9" t="n"/>
-      <c r="CW8" s="9" t="n"/>
-      <c r="CX8" s="9" t="n"/>
-      <c r="CY8" s="9" t="n"/>
-      <c r="CZ8" s="9" t="n"/>
-      <c r="DA8" s="9" t="n"/>
-      <c r="DB8" s="9" t="n"/>
-      <c r="DC8" s="7" t="n"/>
-      <c r="DD8" s="7" t="n"/>
-      <c r="DE8" s="7" t="n"/>
-      <c r="DF8" s="7" t="n"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>Arthur, Lucie, Maya</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
+      <c r="U8" s="13" t="n"/>
+      <c r="V8" s="13" t="n"/>
+      <c r="W8" s="13" t="n"/>
+      <c r="X8" s="13" t="n"/>
+      <c r="Y8" s="13" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="14" t="n"/>
+      <c r="AB8" s="13" t="n"/>
+      <c r="AC8" s="13" t="n"/>
+      <c r="AD8" s="13" t="n"/>
+      <c r="AE8" s="13" t="n"/>
+      <c r="AF8" s="13" t="n"/>
+      <c r="AG8" s="13" t="n"/>
+      <c r="AH8" s="13" t="n"/>
+      <c r="AI8" s="13" t="n"/>
+      <c r="AJ8" s="13" t="n"/>
+      <c r="AK8" s="13" t="n"/>
+      <c r="AL8" s="13" t="n"/>
+      <c r="AM8" s="12" t="inlineStr">
+        <is>
+          <t>Rama, Roxanne, Tristan</t>
+        </is>
+      </c>
+      <c r="AN8" s="13" t="n"/>
+      <c r="AO8" s="13" t="n"/>
+      <c r="AP8" s="13" t="n"/>
+      <c r="AQ8" s="13" t="n"/>
+      <c r="AR8" s="13" t="n"/>
+      <c r="AS8" s="13" t="n"/>
+      <c r="AT8" s="13" t="n"/>
+      <c r="AU8" s="13" t="n"/>
+      <c r="AV8" s="13" t="n"/>
+      <c r="AW8" s="13" t="n"/>
+      <c r="AX8" s="13" t="n"/>
+      <c r="AY8" s="14" t="n"/>
+      <c r="AZ8" s="13" t="n"/>
+      <c r="BA8" s="13" t="n"/>
+      <c r="BB8" s="13" t="n"/>
+      <c r="BC8" s="13" t="n"/>
+      <c r="BD8" s="13" t="n"/>
+      <c r="BE8" s="13" t="n"/>
+      <c r="BF8" s="13" t="n"/>
+      <c r="BG8" s="13" t="n"/>
+      <c r="BH8" s="13" t="n"/>
+      <c r="BI8" s="13" t="n"/>
+      <c r="BJ8" s="13" t="n"/>
+      <c r="BK8" s="12" t="inlineStr">
+        <is>
+          <t>Analou, Louis C., Lucas</t>
+        </is>
+      </c>
+      <c r="BL8" s="13" t="n"/>
+      <c r="BM8" s="13" t="n"/>
+      <c r="BN8" s="13" t="n"/>
+      <c r="BO8" s="13" t="n"/>
+      <c r="BP8" s="13" t="n"/>
+      <c r="BQ8" s="13" t="n"/>
+      <c r="BR8" s="13" t="n"/>
+      <c r="BS8" s="13" t="n"/>
+      <c r="BT8" s="13" t="n"/>
+      <c r="BU8" s="13" t="n"/>
+      <c r="BV8" s="13" t="n"/>
+      <c r="BW8" s="14" t="n"/>
+      <c r="BX8" s="13" t="n"/>
+      <c r="BY8" s="13" t="n"/>
+      <c r="BZ8" s="13" t="n"/>
+      <c r="CA8" s="13" t="n"/>
+      <c r="CB8" s="13" t="n"/>
+      <c r="CC8" s="13" t="n"/>
+      <c r="CD8" s="13" t="n"/>
+      <c r="CE8" s="13" t="n"/>
+      <c r="CF8" s="13" t="n"/>
+      <c r="CG8" s="13" t="n"/>
+      <c r="CH8" s="13" t="n"/>
+      <c r="CI8" s="12" t="inlineStr">
+        <is>
+          <t>Louis P., Roxanne, Titouan</t>
+        </is>
+      </c>
+      <c r="CJ8" s="13" t="n"/>
+      <c r="CK8" s="13" t="n"/>
+      <c r="CL8" s="13" t="n"/>
+      <c r="CM8" s="13" t="n"/>
+      <c r="CN8" s="13" t="n"/>
+      <c r="CO8" s="13" t="n"/>
+      <c r="CP8" s="13" t="n"/>
+      <c r="CQ8" s="13" t="n"/>
+      <c r="CR8" s="13" t="n"/>
+      <c r="CS8" s="13" t="n"/>
+      <c r="CT8" s="13" t="n"/>
+      <c r="CU8" s="14" t="n"/>
+      <c r="CV8" s="13" t="n"/>
+      <c r="CW8" s="13" t="n"/>
+      <c r="CX8" s="13" t="n"/>
+      <c r="CY8" s="13" t="n"/>
+      <c r="CZ8" s="13" t="n"/>
+      <c r="DA8" s="13" t="n"/>
+      <c r="DB8" s="13" t="n"/>
+      <c r="DC8" s="13" t="n"/>
+      <c r="DD8" s="13" t="n"/>
+      <c r="DE8" s="13" t="n"/>
+      <c r="DF8" s="13" t="n"/>
       <c r="DG8" s="6" t="n"/>
       <c r="DH8" s="7" t="n"/>
       <c r="DI8" s="7" t="n"/>
@@ -1906,8 +1945,12 @@
       <c r="EO8" s="7" t="n"/>
       <c r="EP8" s="7" t="n"/>
     </row>
-    <row r="9" ht="17.33333333333333" customHeight="1">
-      <c r="A9" s="5" t="inlineStr"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Bar public</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
@@ -1920,112 +1963,132 @@
       <c r="L9" s="7" t="n"/>
       <c r="M9" s="7" t="n"/>
       <c r="N9" s="7" t="n"/>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>Surprises foraines</t>
-        </is>
-      </c>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="9" t="n"/>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="9" t="n"/>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="9" t="n"/>
-      <c r="AA9" s="10" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="9" t="n"/>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="9" t="n"/>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="9" t="n"/>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="9" t="n"/>
-      <c r="AM9" s="10" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="9" t="n"/>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="9" t="n"/>
-      <c r="AR9" s="9" t="n"/>
-      <c r="AS9" s="9" t="n"/>
-      <c r="AT9" s="9" t="n"/>
-      <c r="AU9" s="9" t="n"/>
-      <c r="AV9" s="9" t="n"/>
-      <c r="AW9" s="9" t="n"/>
-      <c r="AX9" s="9" t="n"/>
-      <c r="AY9" s="10" t="n"/>
-      <c r="AZ9" s="9" t="n"/>
-      <c r="BA9" s="9" t="n"/>
-      <c r="BB9" s="9" t="n"/>
-      <c r="BC9" s="9" t="n"/>
-      <c r="BD9" s="9" t="n"/>
-      <c r="BE9" s="9" t="n"/>
-      <c r="BF9" s="9" t="n"/>
-      <c r="BG9" s="9" t="n"/>
-      <c r="BH9" s="9" t="n"/>
-      <c r="BI9" s="9" t="n"/>
-      <c r="BJ9" s="9" t="n"/>
-      <c r="BK9" s="10" t="n"/>
-      <c r="BL9" s="9" t="n"/>
-      <c r="BM9" s="9" t="n"/>
-      <c r="BN9" s="9" t="n"/>
-      <c r="BO9" s="9" t="n"/>
-      <c r="BP9" s="9" t="n"/>
-      <c r="BQ9" s="9" t="n"/>
-      <c r="BR9" s="9" t="n"/>
-      <c r="BS9" s="9" t="n"/>
-      <c r="BT9" s="9" t="n"/>
-      <c r="BU9" s="9" t="n"/>
-      <c r="BV9" s="9" t="n"/>
-      <c r="BW9" s="10" t="n"/>
-      <c r="BX9" s="9" t="n"/>
-      <c r="BY9" s="9" t="n"/>
-      <c r="BZ9" s="9" t="n"/>
-      <c r="CA9" s="9" t="n"/>
-      <c r="CB9" s="9" t="n"/>
-      <c r="CC9" s="9" t="n"/>
-      <c r="CD9" s="9" t="n"/>
-      <c r="CE9" s="9" t="n"/>
-      <c r="CF9" s="9" t="n"/>
-      <c r="CG9" s="9" t="n"/>
-      <c r="CH9" s="9" t="n"/>
-      <c r="CI9" s="6" t="n"/>
-      <c r="CJ9" s="7" t="n"/>
-      <c r="CK9" s="7" t="n"/>
-      <c r="CL9" s="7" t="n"/>
-      <c r="CM9" s="7" t="n"/>
-      <c r="CN9" s="7" t="n"/>
-      <c r="CO9" s="7" t="n"/>
-      <c r="CP9" s="7" t="n"/>
-      <c r="CQ9" s="7" t="n"/>
-      <c r="CR9" s="7" t="n"/>
-      <c r="CS9" s="7" t="n"/>
-      <c r="CT9" s="7" t="n"/>
-      <c r="CU9" s="6" t="n"/>
-      <c r="CV9" s="7" t="n"/>
-      <c r="CW9" s="7" t="n"/>
-      <c r="CX9" s="7" t="n"/>
-      <c r="CY9" s="7" t="n"/>
-      <c r="CZ9" s="7" t="n"/>
-      <c r="DA9" s="7" t="n"/>
-      <c r="DB9" s="7" t="n"/>
-      <c r="DC9" s="7" t="n"/>
-      <c r="DD9" s="7" t="n"/>
-      <c r="DE9" s="7" t="n"/>
-      <c r="DF9" s="7" t="n"/>
-      <c r="DG9" s="6" t="n"/>
-      <c r="DH9" s="7" t="n"/>
-      <c r="DI9" s="7" t="n"/>
-      <c r="DJ9" s="7" t="n"/>
-      <c r="DK9" s="7" t="n"/>
-      <c r="DL9" s="7" t="n"/>
+      <c r="O9" s="12" t="inlineStr">
+        <is>
+          <t>Enzo, Louis P., Maëlle</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="13" t="n"/>
+      <c r="S9" s="13" t="n"/>
+      <c r="T9" s="13" t="n"/>
+      <c r="U9" s="13" t="n"/>
+      <c r="V9" s="13" t="n"/>
+      <c r="W9" s="13" t="n"/>
+      <c r="X9" s="13" t="n"/>
+      <c r="Y9" s="13" t="n"/>
+      <c r="Z9" s="13" t="n"/>
+      <c r="AA9" s="14" t="n"/>
+      <c r="AB9" s="13" t="n"/>
+      <c r="AC9" s="13" t="n"/>
+      <c r="AD9" s="13" t="n"/>
+      <c r="AE9" s="13" t="n"/>
+      <c r="AF9" s="13" t="n"/>
+      <c r="AG9" s="15" t="inlineStr">
+        <is>
+          <t>Antonin, Theo, Titouan</t>
+        </is>
+      </c>
+      <c r="AH9" s="13" t="n"/>
+      <c r="AI9" s="13" t="n"/>
+      <c r="AJ9" s="13" t="n"/>
+      <c r="AK9" s="13" t="n"/>
+      <c r="AL9" s="13" t="n"/>
+      <c r="AM9" s="14" t="n"/>
+      <c r="AN9" s="13" t="n"/>
+      <c r="AO9" s="13" t="n"/>
+      <c r="AP9" s="13" t="n"/>
+      <c r="AQ9" s="13" t="n"/>
+      <c r="AR9" s="13" t="n"/>
+      <c r="AS9" s="13" t="n"/>
+      <c r="AT9" s="13" t="n"/>
+      <c r="AU9" s="13" t="n"/>
+      <c r="AV9" s="13" t="n"/>
+      <c r="AW9" s="13" t="n"/>
+      <c r="AX9" s="13" t="n"/>
+      <c r="AY9" s="12" t="inlineStr">
+        <is>
+          <t>Athénaé, Ava, Simon, Thibault</t>
+        </is>
+      </c>
+      <c r="AZ9" s="13" t="n"/>
+      <c r="BA9" s="13" t="n"/>
+      <c r="BB9" s="13" t="n"/>
+      <c r="BC9" s="13" t="n"/>
+      <c r="BD9" s="13" t="n"/>
+      <c r="BE9" s="13" t="n"/>
+      <c r="BF9" s="13" t="n"/>
+      <c r="BG9" s="13" t="n"/>
+      <c r="BH9" s="13" t="n"/>
+      <c r="BI9" s="13" t="n"/>
+      <c r="BJ9" s="13" t="n"/>
+      <c r="BK9" s="14" t="n"/>
+      <c r="BL9" s="13" t="n"/>
+      <c r="BM9" s="13" t="n"/>
+      <c r="BN9" s="13" t="n"/>
+      <c r="BO9" s="13" t="n"/>
+      <c r="BP9" s="13" t="n"/>
+      <c r="BQ9" s="15" t="inlineStr">
+        <is>
+          <t>Lucie, Maëlan, Maëlle, Matteo</t>
+        </is>
+      </c>
+      <c r="BR9" s="13" t="n"/>
+      <c r="BS9" s="13" t="n"/>
+      <c r="BT9" s="13" t="n"/>
+      <c r="BU9" s="13" t="n"/>
+      <c r="BV9" s="13" t="n"/>
+      <c r="BW9" s="14" t="n"/>
+      <c r="BX9" s="13" t="n"/>
+      <c r="BY9" s="13" t="n"/>
+      <c r="BZ9" s="13" t="n"/>
+      <c r="CA9" s="13" t="n"/>
+      <c r="CB9" s="13" t="n"/>
+      <c r="CC9" s="13" t="n"/>
+      <c r="CD9" s="13" t="n"/>
+      <c r="CE9" s="13" t="n"/>
+      <c r="CF9" s="13" t="n"/>
+      <c r="CG9" s="13" t="n"/>
+      <c r="CH9" s="13" t="n"/>
+      <c r="CI9" s="12" t="inlineStr">
+        <is>
+          <t>Léa B., Nathalia, Raphaël</t>
+        </is>
+      </c>
+      <c r="CJ9" s="13" t="n"/>
+      <c r="CK9" s="13" t="n"/>
+      <c r="CL9" s="13" t="n"/>
+      <c r="CM9" s="13" t="n"/>
+      <c r="CN9" s="13" t="n"/>
+      <c r="CO9" s="13" t="n"/>
+      <c r="CP9" s="13" t="n"/>
+      <c r="CQ9" s="13" t="n"/>
+      <c r="CR9" s="13" t="n"/>
+      <c r="CS9" s="13" t="n"/>
+      <c r="CT9" s="13" t="n"/>
+      <c r="CU9" s="14" t="n"/>
+      <c r="CV9" s="13" t="n"/>
+      <c r="CW9" s="13" t="n"/>
+      <c r="CX9" s="13" t="n"/>
+      <c r="CY9" s="13" t="n"/>
+      <c r="CZ9" s="13" t="n"/>
+      <c r="DA9" s="15" t="inlineStr">
+        <is>
+          <t>Corentin, Morgana, Morgane</t>
+        </is>
+      </c>
+      <c r="DB9" s="13" t="n"/>
+      <c r="DC9" s="13" t="n"/>
+      <c r="DD9" s="13" t="n"/>
+      <c r="DE9" s="13" t="n"/>
+      <c r="DF9" s="13" t="n"/>
+      <c r="DG9" s="14" t="n"/>
+      <c r="DH9" s="13" t="n"/>
+      <c r="DI9" s="13" t="n"/>
+      <c r="DJ9" s="13" t="n"/>
+      <c r="DK9" s="13" t="n"/>
+      <c r="DL9" s="13" t="n"/>
       <c r="DM9" s="7" t="n"/>
       <c r="DN9" s="7" t="n"/>
       <c r="DO9" s="7" t="n"/>
@@ -2057,12 +2120,179 @@
       <c r="EO9" s="7" t="n"/>
       <c r="EP9" s="7" t="n"/>
     </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Bar loges</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="7" t="n"/>
+      <c r="N10" s="7" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="7" t="n"/>
+      <c r="Q10" s="7" t="n"/>
+      <c r="R10" s="7" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="7" t="n"/>
+      <c r="U10" s="15" t="inlineStr">
+        <is>
+          <t>Léa B., Léa C.</t>
+        </is>
+      </c>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="14" t="n"/>
+      <c r="AB10" s="13" t="n"/>
+      <c r="AC10" s="13" t="n"/>
+      <c r="AD10" s="13" t="n"/>
+      <c r="AE10" s="13" t="n"/>
+      <c r="AF10" s="13" t="n"/>
+      <c r="AG10" s="13" t="n"/>
+      <c r="AH10" s="13" t="n"/>
+      <c r="AI10" s="13" t="n"/>
+      <c r="AJ10" s="13" t="n"/>
+      <c r="AK10" s="13" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="12" t="inlineStr">
+        <is>
+          <t>Agathe, Marot</t>
+        </is>
+      </c>
+      <c r="AN10" s="13" t="n"/>
+      <c r="AO10" s="13" t="n"/>
+      <c r="AP10" s="13" t="n"/>
+      <c r="AQ10" s="13" t="n"/>
+      <c r="AR10" s="13" t="n"/>
+      <c r="AS10" s="13" t="n"/>
+      <c r="AT10" s="13" t="n"/>
+      <c r="AU10" s="13" t="n"/>
+      <c r="AV10" s="13" t="n"/>
+      <c r="AW10" s="13" t="n"/>
+      <c r="AX10" s="13" t="n"/>
+      <c r="AY10" s="14" t="n"/>
+      <c r="AZ10" s="13" t="n"/>
+      <c r="BA10" s="13" t="n"/>
+      <c r="BB10" s="13" t="n"/>
+      <c r="BC10" s="13" t="n"/>
+      <c r="BD10" s="13" t="n"/>
+      <c r="BE10" s="15" t="inlineStr">
+        <is>
+          <t>Corentin, Enzo</t>
+        </is>
+      </c>
+      <c r="BF10" s="13" t="n"/>
+      <c r="BG10" s="13" t="n"/>
+      <c r="BH10" s="13" t="n"/>
+      <c r="BI10" s="13" t="n"/>
+      <c r="BJ10" s="13" t="n"/>
+      <c r="BK10" s="14" t="n"/>
+      <c r="BL10" s="13" t="n"/>
+      <c r="BM10" s="13" t="n"/>
+      <c r="BN10" s="13" t="n"/>
+      <c r="BO10" s="13" t="n"/>
+      <c r="BP10" s="13" t="n"/>
+      <c r="BQ10" s="13" t="n"/>
+      <c r="BR10" s="13" t="n"/>
+      <c r="BS10" s="13" t="n"/>
+      <c r="BT10" s="13" t="n"/>
+      <c r="BU10" s="13" t="n"/>
+      <c r="BV10" s="13" t="n"/>
+      <c r="BW10" s="12" t="inlineStr">
+        <is>
+          <t>Annouk, Jules</t>
+        </is>
+      </c>
+      <c r="BX10" s="13" t="n"/>
+      <c r="BY10" s="13" t="n"/>
+      <c r="BZ10" s="13" t="n"/>
+      <c r="CA10" s="13" t="n"/>
+      <c r="CB10" s="13" t="n"/>
+      <c r="CC10" s="13" t="n"/>
+      <c r="CD10" s="13" t="n"/>
+      <c r="CE10" s="13" t="n"/>
+      <c r="CF10" s="13" t="n"/>
+      <c r="CG10" s="13" t="n"/>
+      <c r="CH10" s="13" t="n"/>
+      <c r="CI10" s="14" t="n"/>
+      <c r="CJ10" s="13" t="n"/>
+      <c r="CK10" s="13" t="n"/>
+      <c r="CL10" s="13" t="n"/>
+      <c r="CM10" s="13" t="n"/>
+      <c r="CN10" s="13" t="n"/>
+      <c r="CO10" s="15" t="inlineStr">
+        <is>
+          <t>Rama, Simon</t>
+        </is>
+      </c>
+      <c r="CP10" s="13" t="n"/>
+      <c r="CQ10" s="13" t="n"/>
+      <c r="CR10" s="13" t="n"/>
+      <c r="CS10" s="13" t="n"/>
+      <c r="CT10" s="13" t="n"/>
+      <c r="CU10" s="14" t="n"/>
+      <c r="CV10" s="13" t="n"/>
+      <c r="CW10" s="13" t="n"/>
+      <c r="CX10" s="13" t="n"/>
+      <c r="CY10" s="13" t="n"/>
+      <c r="CZ10" s="13" t="n"/>
+      <c r="DA10" s="13" t="n"/>
+      <c r="DB10" s="13" t="n"/>
+      <c r="DC10" s="13" t="n"/>
+      <c r="DD10" s="13" t="n"/>
+      <c r="DE10" s="13" t="n"/>
+      <c r="DF10" s="13" t="n"/>
+      <c r="DG10" s="6" t="n"/>
+      <c r="DH10" s="7" t="n"/>
+      <c r="DI10" s="7" t="n"/>
+      <c r="DJ10" s="7" t="n"/>
+      <c r="DK10" s="7" t="n"/>
+      <c r="DL10" s="7" t="n"/>
+      <c r="DM10" s="7" t="n"/>
+      <c r="DN10" s="7" t="n"/>
+      <c r="DO10" s="7" t="n"/>
+      <c r="DP10" s="7" t="n"/>
+      <c r="DQ10" s="7" t="n"/>
+      <c r="DR10" s="7" t="n"/>
+      <c r="DS10" s="6" t="n"/>
+      <c r="DT10" s="7" t="n"/>
+      <c r="DU10" s="7" t="n"/>
+      <c r="DV10" s="7" t="n"/>
+      <c r="DW10" s="7" t="n"/>
+      <c r="DX10" s="7" t="n"/>
+      <c r="DY10" s="7" t="n"/>
+      <c r="DZ10" s="7" t="n"/>
+      <c r="EA10" s="7" t="n"/>
+      <c r="EB10" s="7" t="n"/>
+      <c r="EC10" s="7" t="n"/>
+      <c r="ED10" s="7" t="n"/>
+      <c r="EE10" s="6" t="n"/>
+      <c r="EF10" s="7" t="n"/>
+      <c r="EG10" s="7" t="n"/>
+      <c r="EH10" s="7" t="n"/>
+      <c r="EI10" s="7" t="n"/>
+      <c r="EJ10" s="7" t="n"/>
+      <c r="EK10" s="7" t="n"/>
+      <c r="EL10" s="7" t="n"/>
+      <c r="EM10" s="7" t="n"/>
+      <c r="EN10" s="7" t="n"/>
+      <c r="EO10" s="7" t="n"/>
+      <c r="EP10" s="7" t="n"/>
+    </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Plannings</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="n"/>
       <c r="C11" s="3" t="inlineStr">
         <is>
           <t>15h</t>
@@ -2256,10 +2486,10 @@
       <c r="EO11" s="4" t="n"/>
       <c r="EP11" s="4" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="26" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Abeilles Ruche</t>
+          <t>Grande Scène</t>
         </is>
       </c>
       <c r="C12" s="6" t="n"/>
@@ -2274,143 +2504,131 @@
       <c r="L12" s="7" t="n"/>
       <c r="M12" s="7" t="n"/>
       <c r="N12" s="7" t="n"/>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>Corentin, Morgana, Raphaëlle</t>
-        </is>
-      </c>
-      <c r="P12" s="14" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="14" t="n"/>
-      <c r="S12" s="14" t="n"/>
-      <c r="T12" s="14" t="n"/>
-      <c r="U12" s="14" t="n"/>
-      <c r="V12" s="14" t="n"/>
-      <c r="W12" s="14" t="n"/>
-      <c r="X12" s="14" t="n"/>
-      <c r="Y12" s="14" t="n"/>
-      <c r="Z12" s="14" t="n"/>
-      <c r="AA12" s="15" t="n"/>
-      <c r="AB12" s="14" t="n"/>
-      <c r="AC12" s="14" t="n"/>
-      <c r="AD12" s="14" t="n"/>
-      <c r="AE12" s="14" t="n"/>
-      <c r="AF12" s="14" t="n"/>
-      <c r="AG12" s="16" t="inlineStr">
-        <is>
-          <t>Louis C., Maya C., Thibault</t>
-        </is>
-      </c>
-      <c r="AH12" s="14" t="n"/>
-      <c r="AI12" s="14" t="n"/>
-      <c r="AJ12" s="14" t="n"/>
-      <c r="AK12" s="14" t="n"/>
-      <c r="AL12" s="14" t="n"/>
-      <c r="AM12" s="15" t="n"/>
-      <c r="AN12" s="14" t="n"/>
-      <c r="AO12" s="14" t="n"/>
-      <c r="AP12" s="14" t="n"/>
-      <c r="AQ12" s="14" t="n"/>
-      <c r="AR12" s="14" t="n"/>
-      <c r="AS12" s="14" t="n"/>
-      <c r="AT12" s="14" t="n"/>
-      <c r="AU12" s="14" t="n"/>
-      <c r="AV12" s="14" t="n"/>
-      <c r="AW12" s="14" t="n"/>
-      <c r="AX12" s="14" t="n"/>
-      <c r="AY12" s="13" t="inlineStr">
-        <is>
-          <t>Nathalia, Tristan, Yann</t>
-        </is>
-      </c>
-      <c r="AZ12" s="14" t="n"/>
-      <c r="BA12" s="14" t="n"/>
-      <c r="BB12" s="14" t="n"/>
-      <c r="BC12" s="14" t="n"/>
-      <c r="BD12" s="14" t="n"/>
-      <c r="BE12" s="14" t="n"/>
-      <c r="BF12" s="14" t="n"/>
-      <c r="BG12" s="14" t="n"/>
-      <c r="BH12" s="14" t="n"/>
-      <c r="BI12" s="14" t="n"/>
-      <c r="BJ12" s="14" t="n"/>
-      <c r="BK12" s="15" t="n"/>
-      <c r="BL12" s="14" t="n"/>
-      <c r="BM12" s="14" t="n"/>
-      <c r="BN12" s="14" t="n"/>
-      <c r="BO12" s="14" t="n"/>
-      <c r="BP12" s="14" t="n"/>
-      <c r="BQ12" s="16" t="inlineStr">
-        <is>
-          <t>Arthur, Lucas, Titouan</t>
-        </is>
-      </c>
-      <c r="BR12" s="14" t="n"/>
-      <c r="BS12" s="14" t="n"/>
-      <c r="BT12" s="14" t="n"/>
-      <c r="BU12" s="14" t="n"/>
-      <c r="BV12" s="14" t="n"/>
-      <c r="BW12" s="15" t="n"/>
-      <c r="BX12" s="14" t="n"/>
-      <c r="BY12" s="14" t="n"/>
-      <c r="BZ12" s="14" t="n"/>
-      <c r="CA12" s="14" t="n"/>
-      <c r="CB12" s="14" t="n"/>
-      <c r="CC12" s="14" t="n"/>
-      <c r="CD12" s="14" t="n"/>
-      <c r="CE12" s="14" t="n"/>
-      <c r="CF12" s="14" t="n"/>
-      <c r="CG12" s="14" t="n"/>
-      <c r="CH12" s="14" t="n"/>
-      <c r="CI12" s="13" t="inlineStr">
-        <is>
-          <t>Thibault, Mireille, Maya R.</t>
-        </is>
-      </c>
-      <c r="CJ12" s="14" t="n"/>
-      <c r="CK12" s="14" t="n"/>
-      <c r="CL12" s="14" t="n"/>
-      <c r="CM12" s="14" t="n"/>
-      <c r="CN12" s="14" t="n"/>
-      <c r="CO12" s="14" t="n"/>
-      <c r="CP12" s="14" t="n"/>
-      <c r="CQ12" s="14" t="n"/>
-      <c r="CR12" s="14" t="n"/>
-      <c r="CS12" s="14" t="n"/>
-      <c r="CT12" s="14" t="n"/>
-      <c r="CU12" s="15" t="n"/>
-      <c r="CV12" s="14" t="n"/>
-      <c r="CW12" s="14" t="n"/>
-      <c r="CX12" s="14" t="n"/>
-      <c r="CY12" s="14" t="n"/>
-      <c r="CZ12" s="14" t="n"/>
-      <c r="DA12" s="16" t="inlineStr">
-        <is>
-          <t>Lucie, Maëlan</t>
-        </is>
-      </c>
-      <c r="DB12" s="14" t="n"/>
-      <c r="DC12" s="14" t="n"/>
-      <c r="DD12" s="14" t="n"/>
-      <c r="DE12" s="14" t="n"/>
-      <c r="DF12" s="14" t="n"/>
-      <c r="DG12" s="15" t="n"/>
-      <c r="DH12" s="14" t="n"/>
-      <c r="DI12" s="14" t="n"/>
-      <c r="DJ12" s="14" t="n"/>
-      <c r="DK12" s="14" t="n"/>
-      <c r="DL12" s="14" t="n"/>
-      <c r="DM12" s="7" t="n"/>
-      <c r="DN12" s="7" t="n"/>
-      <c r="DO12" s="7" t="n"/>
-      <c r="DP12" s="7" t="n"/>
-      <c r="DQ12" s="7" t="n"/>
-      <c r="DR12" s="7" t="n"/>
-      <c r="DS12" s="6" t="n"/>
-      <c r="DT12" s="7" t="n"/>
-      <c r="DU12" s="7" t="n"/>
-      <c r="DV12" s="7" t="n"/>
-      <c r="DW12" s="7" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="7" t="n"/>
+      <c r="U12" s="7" t="n"/>
+      <c r="V12" s="7" t="n"/>
+      <c r="W12" s="7" t="n"/>
+      <c r="X12" s="7" t="n"/>
+      <c r="Y12" s="7" t="n"/>
+      <c r="Z12" s="7" t="n"/>
+      <c r="AA12" s="6" t="n"/>
+      <c r="AB12" s="7" t="n"/>
+      <c r="AC12" s="7" t="n"/>
+      <c r="AD12" s="7" t="n"/>
+      <c r="AE12" s="7" t="n"/>
+      <c r="AF12" s="7" t="n"/>
+      <c r="AG12" s="7" t="n"/>
+      <c r="AH12" s="7" t="n"/>
+      <c r="AI12" s="7" t="n"/>
+      <c r="AJ12" s="7" t="n"/>
+      <c r="AK12" s="7" t="n"/>
+      <c r="AL12" s="7" t="n"/>
+      <c r="AM12" s="6" t="n"/>
+      <c r="AN12" s="7" t="n"/>
+      <c r="AO12" s="7" t="n"/>
+      <c r="AP12" s="7" t="n"/>
+      <c r="AQ12" s="7" t="n"/>
+      <c r="AR12" s="7" t="n"/>
+      <c r="AS12" s="8" t="inlineStr">
+        <is>
+          <t>Suzane</t>
+        </is>
+      </c>
+      <c r="AT12" s="9" t="n"/>
+      <c r="AU12" s="9" t="n"/>
+      <c r="AV12" s="9" t="n"/>
+      <c r="AW12" s="9" t="n"/>
+      <c r="AX12" s="9" t="n"/>
+      <c r="AY12" s="10" t="n"/>
+      <c r="AZ12" s="9" t="n"/>
+      <c r="BA12" s="9" t="n"/>
+      <c r="BB12" s="9" t="n"/>
+      <c r="BC12" s="9" t="n"/>
+      <c r="BD12" s="9" t="n"/>
+      <c r="BE12" s="7" t="n"/>
+      <c r="BF12" s="7" t="n"/>
+      <c r="BG12" s="7" t="n"/>
+      <c r="BH12" s="7" t="n"/>
+      <c r="BI12" s="7" t="n"/>
+      <c r="BJ12" s="7" t="n"/>
+      <c r="BK12" s="6" t="n"/>
+      <c r="BL12" s="7" t="n"/>
+      <c r="BM12" s="7" t="n"/>
+      <c r="BN12" s="7" t="n"/>
+      <c r="BO12" s="7" t="n"/>
+      <c r="BP12" s="7" t="n"/>
+      <c r="BQ12" s="7" t="n"/>
+      <c r="BR12" s="7" t="n"/>
+      <c r="BS12" s="7" t="n"/>
+      <c r="BT12" s="7" t="n"/>
+      <c r="BU12" s="7" t="n"/>
+      <c r="BV12" s="7" t="n"/>
+      <c r="BW12" s="11" t="inlineStr">
+        <is>
+          <t>Lorde</t>
+        </is>
+      </c>
+      <c r="BX12" s="9" t="n"/>
+      <c r="BY12" s="9" t="n"/>
+      <c r="BZ12" s="9" t="n"/>
+      <c r="CA12" s="9" t="n"/>
+      <c r="CB12" s="9" t="n"/>
+      <c r="CC12" s="9" t="n"/>
+      <c r="CD12" s="9" t="n"/>
+      <c r="CE12" s="9" t="n"/>
+      <c r="CF12" s="9" t="n"/>
+      <c r="CG12" s="9" t="n"/>
+      <c r="CH12" s="9" t="n"/>
+      <c r="CI12" s="10" t="n"/>
+      <c r="CJ12" s="9" t="n"/>
+      <c r="CK12" s="9" t="n"/>
+      <c r="CL12" s="7" t="n"/>
+      <c r="CM12" s="7" t="n"/>
+      <c r="CN12" s="7" t="n"/>
+      <c r="CO12" s="7" t="n"/>
+      <c r="CP12" s="7" t="n"/>
+      <c r="CQ12" s="7" t="n"/>
+      <c r="CR12" s="7" t="n"/>
+      <c r="CS12" s="7" t="n"/>
+      <c r="CT12" s="7" t="n"/>
+      <c r="CU12" s="6" t="n"/>
+      <c r="CV12" s="7" t="n"/>
+      <c r="CW12" s="7" t="n"/>
+      <c r="CX12" s="7" t="n"/>
+      <c r="CY12" s="7" t="n"/>
+      <c r="CZ12" s="7" t="n"/>
+      <c r="DA12" s="7" t="n"/>
+      <c r="DB12" s="7" t="n"/>
+      <c r="DC12" s="7" t="n"/>
+      <c r="DD12" s="7" t="n"/>
+      <c r="DE12" s="8" t="inlineStr">
+        <is>
+          <t>Twenty One Pilots</t>
+        </is>
+      </c>
+      <c r="DF12" s="9" t="n"/>
+      <c r="DG12" s="10" t="n"/>
+      <c r="DH12" s="9" t="n"/>
+      <c r="DI12" s="9" t="n"/>
+      <c r="DJ12" s="9" t="n"/>
+      <c r="DK12" s="9" t="n"/>
+      <c r="DL12" s="9" t="n"/>
+      <c r="DM12" s="9" t="n"/>
+      <c r="DN12" s="9" t="n"/>
+      <c r="DO12" s="9" t="n"/>
+      <c r="DP12" s="9" t="n"/>
+      <c r="DQ12" s="9" t="n"/>
+      <c r="DR12" s="9" t="n"/>
+      <c r="DS12" s="10" t="n"/>
+      <c r="DT12" s="9" t="n"/>
+      <c r="DU12" s="9" t="n"/>
+      <c r="DV12" s="9" t="n"/>
+      <c r="DW12" s="9" t="n"/>
       <c r="DX12" s="7" t="n"/>
       <c r="DY12" s="7" t="n"/>
       <c r="DZ12" s="7" t="n"/>
@@ -2431,10 +2649,10 @@
       <c r="EO12" s="7" t="n"/>
       <c r="EP12" s="7" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="26" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Ailes</t>
+          <t>Véga</t>
         </is>
       </c>
       <c r="C13" s="6" t="n"/>
@@ -2449,118 +2667,110 @@
       <c r="L13" s="7" t="n"/>
       <c r="M13" s="7" t="n"/>
       <c r="N13" s="7" t="n"/>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>Enzo, Lucas, Rama</t>
-        </is>
-      </c>
-      <c r="P13" s="14" t="n"/>
-      <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="14" t="n"/>
-      <c r="S13" s="14" t="n"/>
-      <c r="T13" s="14" t="n"/>
-      <c r="U13" s="14" t="n"/>
-      <c r="V13" s="14" t="n"/>
-      <c r="W13" s="14" t="n"/>
-      <c r="X13" s="14" t="n"/>
-      <c r="Y13" s="14" t="n"/>
-      <c r="Z13" s="14" t="n"/>
-      <c r="AA13" s="15" t="n"/>
-      <c r="AB13" s="14" t="n"/>
-      <c r="AC13" s="14" t="n"/>
-      <c r="AD13" s="14" t="n"/>
-      <c r="AE13" s="14" t="n"/>
-      <c r="AF13" s="14" t="n"/>
-      <c r="AG13" s="14" t="n"/>
-      <c r="AH13" s="14" t="n"/>
-      <c r="AI13" s="14" t="n"/>
-      <c r="AJ13" s="14" t="n"/>
-      <c r="AK13" s="14" t="n"/>
-      <c r="AL13" s="14" t="n"/>
-      <c r="AM13" s="13" t="inlineStr">
-        <is>
-          <t>Léa B., Marot, Roxanne</t>
-        </is>
-      </c>
-      <c r="AN13" s="14" t="n"/>
-      <c r="AO13" s="14" t="n"/>
-      <c r="AP13" s="14" t="n"/>
-      <c r="AQ13" s="14" t="n"/>
-      <c r="AR13" s="14" t="n"/>
-      <c r="AS13" s="14" t="n"/>
-      <c r="AT13" s="14" t="n"/>
-      <c r="AU13" s="14" t="n"/>
-      <c r="AV13" s="14" t="n"/>
-      <c r="AW13" s="14" t="n"/>
-      <c r="AX13" s="14" t="n"/>
-      <c r="AY13" s="15" t="n"/>
-      <c r="AZ13" s="14" t="n"/>
-      <c r="BA13" s="14" t="n"/>
-      <c r="BB13" s="14" t="n"/>
-      <c r="BC13" s="14" t="n"/>
-      <c r="BD13" s="14" t="n"/>
-      <c r="BE13" s="14" t="n"/>
-      <c r="BF13" s="14" t="n"/>
-      <c r="BG13" s="14" t="n"/>
-      <c r="BH13" s="14" t="n"/>
-      <c r="BI13" s="14" t="n"/>
-      <c r="BJ13" s="14" t="n"/>
-      <c r="BK13" s="13" t="inlineStr">
-        <is>
-          <t>Agathe, Enzo, Theo</t>
-        </is>
-      </c>
-      <c r="BL13" s="14" t="n"/>
-      <c r="BM13" s="14" t="n"/>
-      <c r="BN13" s="14" t="n"/>
-      <c r="BO13" s="14" t="n"/>
-      <c r="BP13" s="14" t="n"/>
-      <c r="BQ13" s="14" t="n"/>
-      <c r="BR13" s="14" t="n"/>
-      <c r="BS13" s="14" t="n"/>
-      <c r="BT13" s="14" t="n"/>
-      <c r="BU13" s="14" t="n"/>
-      <c r="BV13" s="14" t="n"/>
-      <c r="BW13" s="15" t="n"/>
-      <c r="BX13" s="14" t="n"/>
-      <c r="BY13" s="14" t="n"/>
-      <c r="BZ13" s="14" t="n"/>
-      <c r="CA13" s="14" t="n"/>
-      <c r="CB13" s="14" t="n"/>
-      <c r="CC13" s="14" t="n"/>
-      <c r="CD13" s="14" t="n"/>
-      <c r="CE13" s="14" t="n"/>
-      <c r="CF13" s="14" t="n"/>
-      <c r="CG13" s="14" t="n"/>
-      <c r="CH13" s="14" t="n"/>
-      <c r="CI13" s="13" t="inlineStr">
-        <is>
-          <t>Marot, Roxanne, Ysatis</t>
-        </is>
-      </c>
-      <c r="CJ13" s="14" t="n"/>
-      <c r="CK13" s="14" t="n"/>
-      <c r="CL13" s="14" t="n"/>
-      <c r="CM13" s="14" t="n"/>
-      <c r="CN13" s="14" t="n"/>
-      <c r="CO13" s="14" t="n"/>
-      <c r="CP13" s="14" t="n"/>
-      <c r="CQ13" s="14" t="n"/>
-      <c r="CR13" s="14" t="n"/>
-      <c r="CS13" s="14" t="n"/>
-      <c r="CT13" s="14" t="n"/>
-      <c r="CU13" s="15" t="n"/>
-      <c r="CV13" s="14" t="n"/>
-      <c r="CW13" s="14" t="n"/>
-      <c r="CX13" s="14" t="n"/>
-      <c r="CY13" s="14" t="n"/>
-      <c r="CZ13" s="14" t="n"/>
-      <c r="DA13" s="14" t="n"/>
-      <c r="DB13" s="14" t="n"/>
-      <c r="DC13" s="14" t="n"/>
-      <c r="DD13" s="14" t="n"/>
-      <c r="DE13" s="14" t="n"/>
-      <c r="DF13" s="14" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="7" t="n"/>
+      <c r="Q13" s="7" t="n"/>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="7" t="n"/>
+      <c r="U13" s="7" t="n"/>
+      <c r="V13" s="7" t="n"/>
+      <c r="W13" s="7" t="n"/>
+      <c r="X13" s="7" t="n"/>
+      <c r="Y13" s="7" t="n"/>
+      <c r="Z13" s="7" t="n"/>
+      <c r="AA13" s="6" t="n"/>
+      <c r="AB13" s="7" t="n"/>
+      <c r="AC13" s="7" t="n"/>
+      <c r="AD13" s="7" t="n"/>
+      <c r="AE13" s="7" t="n"/>
+      <c r="AF13" s="7" t="n"/>
+      <c r="AG13" s="7" t="n"/>
+      <c r="AH13" s="7" t="n"/>
+      <c r="AI13" s="7" t="n"/>
+      <c r="AJ13" s="7" t="n"/>
+      <c r="AK13" s="7" t="n"/>
+      <c r="AL13" s="7" t="n"/>
+      <c r="AM13" s="6" t="n"/>
+      <c r="AN13" s="7" t="n"/>
+      <c r="AO13" s="7" t="n"/>
+      <c r="AP13" s="7" t="n"/>
+      <c r="AQ13" s="7" t="n"/>
+      <c r="AR13" s="7" t="n"/>
+      <c r="AS13" s="7" t="n"/>
+      <c r="AT13" s="7" t="n"/>
+      <c r="AU13" s="7" t="n"/>
+      <c r="AV13" s="7" t="n"/>
+      <c r="AW13" s="7" t="n"/>
+      <c r="AX13" s="7" t="n"/>
+      <c r="AY13" s="6" t="n"/>
+      <c r="AZ13" s="7" t="n"/>
+      <c r="BA13" s="7" t="n"/>
+      <c r="BB13" s="7" t="n"/>
+      <c r="BC13" s="7" t="n"/>
+      <c r="BD13" s="7" t="n"/>
+      <c r="BE13" s="7" t="n"/>
+      <c r="BF13" s="7" t="n"/>
+      <c r="BG13" s="7" t="n"/>
+      <c r="BH13" s="8" t="inlineStr">
+        <is>
+          <t>Balu Brigada</t>
+        </is>
+      </c>
+      <c r="BI13" s="9" t="n"/>
+      <c r="BJ13" s="9" t="n"/>
+      <c r="BK13" s="10" t="n"/>
+      <c r="BL13" s="9" t="n"/>
+      <c r="BM13" s="9" t="n"/>
+      <c r="BN13" s="9" t="n"/>
+      <c r="BO13" s="9" t="n"/>
+      <c r="BP13" s="9" t="n"/>
+      <c r="BQ13" s="9" t="n"/>
+      <c r="BR13" s="9" t="n"/>
+      <c r="BS13" s="9" t="n"/>
+      <c r="BT13" s="7" t="n"/>
+      <c r="BU13" s="7" t="n"/>
+      <c r="BV13" s="7" t="n"/>
+      <c r="BW13" s="6" t="n"/>
+      <c r="BX13" s="7" t="n"/>
+      <c r="BY13" s="7" t="n"/>
+      <c r="BZ13" s="7" t="n"/>
+      <c r="CA13" s="7" t="n"/>
+      <c r="CB13" s="7" t="n"/>
+      <c r="CC13" s="7" t="n"/>
+      <c r="CD13" s="7" t="n"/>
+      <c r="CE13" s="7" t="n"/>
+      <c r="CF13" s="7" t="n"/>
+      <c r="CG13" s="7" t="n"/>
+      <c r="CH13" s="7" t="n"/>
+      <c r="CI13" s="6" t="n"/>
+      <c r="CJ13" s="7" t="n"/>
+      <c r="CK13" s="7" t="n"/>
+      <c r="CL13" s="7" t="n"/>
+      <c r="CM13" s="7" t="n"/>
+      <c r="CN13" s="8" t="inlineStr">
+        <is>
+          <t>Asaf Avidan</t>
+        </is>
+      </c>
+      <c r="CO13" s="9" t="n"/>
+      <c r="CP13" s="9" t="n"/>
+      <c r="CQ13" s="9" t="n"/>
+      <c r="CR13" s="9" t="n"/>
+      <c r="CS13" s="9" t="n"/>
+      <c r="CT13" s="9" t="n"/>
+      <c r="CU13" s="10" t="n"/>
+      <c r="CV13" s="9" t="n"/>
+      <c r="CW13" s="9" t="n"/>
+      <c r="CX13" s="9" t="n"/>
+      <c r="CY13" s="9" t="n"/>
+      <c r="CZ13" s="9" t="n"/>
+      <c r="DA13" s="9" t="n"/>
+      <c r="DB13" s="9" t="n"/>
+      <c r="DC13" s="7" t="n"/>
+      <c r="DD13" s="7" t="n"/>
+      <c r="DE13" s="7" t="n"/>
+      <c r="DF13" s="7" t="n"/>
       <c r="DG13" s="6" t="n"/>
       <c r="DH13" s="7" t="n"/>
       <c r="DI13" s="7" t="n"/>
@@ -2579,18 +2789,22 @@
       <c r="DV13" s="7" t="n"/>
       <c r="DW13" s="7" t="n"/>
       <c r="DX13" s="7" t="n"/>
-      <c r="DY13" s="7" t="n"/>
-      <c r="DZ13" s="7" t="n"/>
-      <c r="EA13" s="7" t="n"/>
-      <c r="EB13" s="7" t="n"/>
-      <c r="EC13" s="7" t="n"/>
-      <c r="ED13" s="7" t="n"/>
-      <c r="EE13" s="6" t="n"/>
-      <c r="EF13" s="7" t="n"/>
-      <c r="EG13" s="7" t="n"/>
-      <c r="EH13" s="7" t="n"/>
-      <c r="EI13" s="7" t="n"/>
-      <c r="EJ13" s="7" t="n"/>
+      <c r="DY13" s="8" t="inlineStr">
+        <is>
+          <t>Perceval</t>
+        </is>
+      </c>
+      <c r="DZ13" s="9" t="n"/>
+      <c r="EA13" s="9" t="n"/>
+      <c r="EB13" s="9" t="n"/>
+      <c r="EC13" s="9" t="n"/>
+      <c r="ED13" s="9" t="n"/>
+      <c r="EE13" s="10" t="n"/>
+      <c r="EF13" s="9" t="n"/>
+      <c r="EG13" s="9" t="n"/>
+      <c r="EH13" s="9" t="n"/>
+      <c r="EI13" s="9" t="n"/>
+      <c r="EJ13" s="9" t="n"/>
       <c r="EK13" s="7" t="n"/>
       <c r="EL13" s="7" t="n"/>
       <c r="EM13" s="7" t="n"/>
@@ -2598,10 +2812,10 @@
       <c r="EO13" s="7" t="n"/>
       <c r="EP13" s="7" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Bar loges</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="C14" s="6" t="n"/>
@@ -2622,116 +2836,108 @@
       <c r="R14" s="7" t="n"/>
       <c r="S14" s="7" t="n"/>
       <c r="T14" s="7" t="n"/>
-      <c r="U14" s="16" t="inlineStr">
-        <is>
-          <t>Louis P., Titouan</t>
-        </is>
-      </c>
-      <c r="V14" s="14" t="n"/>
-      <c r="W14" s="14" t="n"/>
-      <c r="X14" s="14" t="n"/>
-      <c r="Y14" s="14" t="n"/>
-      <c r="Z14" s="14" t="n"/>
-      <c r="AA14" s="15" t="n"/>
-      <c r="AB14" s="14" t="n"/>
-      <c r="AC14" s="14" t="n"/>
-      <c r="AD14" s="14" t="n"/>
-      <c r="AE14" s="14" t="n"/>
-      <c r="AF14" s="14" t="n"/>
-      <c r="AG14" s="14" t="n"/>
-      <c r="AH14" s="14" t="n"/>
-      <c r="AI14" s="14" t="n"/>
-      <c r="AJ14" s="14" t="n"/>
-      <c r="AK14" s="14" t="n"/>
-      <c r="AL14" s="14" t="n"/>
-      <c r="AM14" s="13" t="inlineStr">
-        <is>
-          <t>Lisa J., Ysatis</t>
-        </is>
-      </c>
-      <c r="AN14" s="14" t="n"/>
-      <c r="AO14" s="14" t="n"/>
-      <c r="AP14" s="14" t="n"/>
-      <c r="AQ14" s="14" t="n"/>
-      <c r="AR14" s="14" t="n"/>
-      <c r="AS14" s="14" t="n"/>
-      <c r="AT14" s="14" t="n"/>
-      <c r="AU14" s="14" t="n"/>
-      <c r="AV14" s="14" t="n"/>
-      <c r="AW14" s="14" t="n"/>
-      <c r="AX14" s="14" t="n"/>
-      <c r="AY14" s="15" t="n"/>
-      <c r="AZ14" s="14" t="n"/>
-      <c r="BA14" s="14" t="n"/>
-      <c r="BB14" s="14" t="n"/>
-      <c r="BC14" s="14" t="n"/>
-      <c r="BD14" s="14" t="n"/>
-      <c r="BE14" s="16" t="inlineStr">
-        <is>
-          <t>Lina-Rosa, Mickaël</t>
-        </is>
-      </c>
-      <c r="BF14" s="14" t="n"/>
-      <c r="BG14" s="14" t="n"/>
-      <c r="BH14" s="14" t="n"/>
-      <c r="BI14" s="14" t="n"/>
-      <c r="BJ14" s="14" t="n"/>
-      <c r="BK14" s="15" t="n"/>
-      <c r="BL14" s="14" t="n"/>
-      <c r="BM14" s="14" t="n"/>
-      <c r="BN14" s="14" t="n"/>
-      <c r="BO14" s="14" t="n"/>
-      <c r="BP14" s="14" t="n"/>
-      <c r="BQ14" s="14" t="n"/>
-      <c r="BR14" s="14" t="n"/>
-      <c r="BS14" s="14" t="n"/>
-      <c r="BT14" s="14" t="n"/>
-      <c r="BU14" s="14" t="n"/>
-      <c r="BV14" s="14" t="n"/>
-      <c r="BW14" s="13" t="inlineStr">
-        <is>
-          <t>Arsène, Louis P.</t>
-        </is>
-      </c>
-      <c r="BX14" s="14" t="n"/>
-      <c r="BY14" s="14" t="n"/>
-      <c r="BZ14" s="14" t="n"/>
-      <c r="CA14" s="14" t="n"/>
-      <c r="CB14" s="14" t="n"/>
-      <c r="CC14" s="14" t="n"/>
-      <c r="CD14" s="14" t="n"/>
-      <c r="CE14" s="14" t="n"/>
-      <c r="CF14" s="14" t="n"/>
-      <c r="CG14" s="14" t="n"/>
-      <c r="CH14" s="14" t="n"/>
-      <c r="CI14" s="15" t="n"/>
-      <c r="CJ14" s="14" t="n"/>
-      <c r="CK14" s="14" t="n"/>
-      <c r="CL14" s="14" t="n"/>
-      <c r="CM14" s="14" t="n"/>
-      <c r="CN14" s="14" t="n"/>
-      <c r="CO14" s="16" t="inlineStr">
-        <is>
-          <t>Léa C., Raphaël</t>
-        </is>
-      </c>
-      <c r="CP14" s="14" t="n"/>
-      <c r="CQ14" s="14" t="n"/>
-      <c r="CR14" s="14" t="n"/>
-      <c r="CS14" s="14" t="n"/>
-      <c r="CT14" s="14" t="n"/>
-      <c r="CU14" s="15" t="n"/>
-      <c r="CV14" s="14" t="n"/>
-      <c r="CW14" s="14" t="n"/>
-      <c r="CX14" s="14" t="n"/>
-      <c r="CY14" s="14" t="n"/>
-      <c r="CZ14" s="14" t="n"/>
-      <c r="DA14" s="14" t="n"/>
-      <c r="DB14" s="14" t="n"/>
-      <c r="DC14" s="14" t="n"/>
-      <c r="DD14" s="14" t="n"/>
-      <c r="DE14" s="14" t="n"/>
-      <c r="DF14" s="14" t="n"/>
+      <c r="U14" s="7" t="n"/>
+      <c r="V14" s="7" t="n"/>
+      <c r="W14" s="7" t="n"/>
+      <c r="X14" s="7" t="n"/>
+      <c r="Y14" s="7" t="n"/>
+      <c r="Z14" s="7" t="n"/>
+      <c r="AA14" s="6" t="n"/>
+      <c r="AB14" s="7" t="n"/>
+      <c r="AC14" s="7" t="n"/>
+      <c r="AD14" s="8" t="inlineStr">
+        <is>
+          <t>Club Katel</t>
+        </is>
+      </c>
+      <c r="AE14" s="9" t="n"/>
+      <c r="AF14" s="9" t="n"/>
+      <c r="AG14" s="9" t="n"/>
+      <c r="AH14" s="9" t="n"/>
+      <c r="AI14" s="9" t="n"/>
+      <c r="AJ14" s="9" t="n"/>
+      <c r="AK14" s="9" t="n"/>
+      <c r="AL14" s="9" t="n"/>
+      <c r="AM14" s="10" t="n"/>
+      <c r="AN14" s="9" t="n"/>
+      <c r="AO14" s="9" t="n"/>
+      <c r="AP14" s="9" t="n"/>
+      <c r="AQ14" s="9" t="n"/>
+      <c r="AR14" s="9" t="n"/>
+      <c r="AS14" s="7" t="n"/>
+      <c r="AT14" s="7" t="n"/>
+      <c r="AU14" s="7" t="n"/>
+      <c r="AV14" s="7" t="n"/>
+      <c r="AW14" s="7" t="n"/>
+      <c r="AX14" s="7" t="n"/>
+      <c r="AY14" s="6" t="n"/>
+      <c r="AZ14" s="7" t="n"/>
+      <c r="BA14" s="7" t="n"/>
+      <c r="BB14" s="7" t="n"/>
+      <c r="BC14" s="7" t="n"/>
+      <c r="BD14" s="7" t="n"/>
+      <c r="BE14" s="8" t="inlineStr">
+        <is>
+          <t>Dylan Dylan</t>
+        </is>
+      </c>
+      <c r="BF14" s="9" t="n"/>
+      <c r="BG14" s="9" t="n"/>
+      <c r="BH14" s="9" t="n"/>
+      <c r="BI14" s="9" t="n"/>
+      <c r="BJ14" s="9" t="n"/>
+      <c r="BK14" s="10" t="n"/>
+      <c r="BL14" s="9" t="n"/>
+      <c r="BM14" s="9" t="n"/>
+      <c r="BN14" s="9" t="n"/>
+      <c r="BO14" s="9" t="n"/>
+      <c r="BP14" s="9" t="n"/>
+      <c r="BQ14" s="9" t="n"/>
+      <c r="BR14" s="9" t="n"/>
+      <c r="BS14" s="9" t="n"/>
+      <c r="BT14" s="9" t="n"/>
+      <c r="BU14" s="9" t="n"/>
+      <c r="BV14" s="7" t="n"/>
+      <c r="BW14" s="6" t="n"/>
+      <c r="BX14" s="7" t="n"/>
+      <c r="BY14" s="7" t="n"/>
+      <c r="BZ14" s="7" t="n"/>
+      <c r="CA14" s="7" t="n"/>
+      <c r="CB14" s="7" t="n"/>
+      <c r="CC14" s="7" t="n"/>
+      <c r="CD14" s="7" t="n"/>
+      <c r="CE14" s="7" t="n"/>
+      <c r="CF14" s="7" t="n"/>
+      <c r="CG14" s="7" t="n"/>
+      <c r="CH14" s="7" t="n"/>
+      <c r="CI14" s="6" t="n"/>
+      <c r="CJ14" s="7" t="n"/>
+      <c r="CK14" s="7" t="n"/>
+      <c r="CL14" s="8" t="inlineStr">
+        <is>
+          <t>okgiorgio</t>
+        </is>
+      </c>
+      <c r="CM14" s="9" t="n"/>
+      <c r="CN14" s="9" t="n"/>
+      <c r="CO14" s="9" t="n"/>
+      <c r="CP14" s="9" t="n"/>
+      <c r="CQ14" s="9" t="n"/>
+      <c r="CR14" s="9" t="n"/>
+      <c r="CS14" s="9" t="n"/>
+      <c r="CT14" s="9" t="n"/>
+      <c r="CU14" s="10" t="n"/>
+      <c r="CV14" s="9" t="n"/>
+      <c r="CW14" s="9" t="n"/>
+      <c r="CX14" s="9" t="n"/>
+      <c r="CY14" s="9" t="n"/>
+      <c r="CZ14" s="9" t="n"/>
+      <c r="DA14" s="9" t="n"/>
+      <c r="DB14" s="9" t="n"/>
+      <c r="DC14" s="9" t="n"/>
+      <c r="DD14" s="7" t="n"/>
+      <c r="DE14" s="7" t="n"/>
+      <c r="DF14" s="7" t="n"/>
       <c r="DG14" s="6" t="n"/>
       <c r="DH14" s="7" t="n"/>
       <c r="DI14" s="7" t="n"/>
@@ -2749,19 +2955,23 @@
       <c r="DU14" s="7" t="n"/>
       <c r="DV14" s="7" t="n"/>
       <c r="DW14" s="7" t="n"/>
-      <c r="DX14" s="7" t="n"/>
-      <c r="DY14" s="7" t="n"/>
-      <c r="DZ14" s="7" t="n"/>
-      <c r="EA14" s="7" t="n"/>
-      <c r="EB14" s="7" t="n"/>
-      <c r="EC14" s="7" t="n"/>
-      <c r="ED14" s="7" t="n"/>
-      <c r="EE14" s="6" t="n"/>
-      <c r="EF14" s="7" t="n"/>
-      <c r="EG14" s="7" t="n"/>
-      <c r="EH14" s="7" t="n"/>
-      <c r="EI14" s="7" t="n"/>
-      <c r="EJ14" s="7" t="n"/>
+      <c r="DX14" s="8" t="inlineStr">
+        <is>
+          <t>Upsilone</t>
+        </is>
+      </c>
+      <c r="DY14" s="9" t="n"/>
+      <c r="DZ14" s="9" t="n"/>
+      <c r="EA14" s="9" t="n"/>
+      <c r="EB14" s="9" t="n"/>
+      <c r="EC14" s="9" t="n"/>
+      <c r="ED14" s="9" t="n"/>
+      <c r="EE14" s="10" t="n"/>
+      <c r="EF14" s="9" t="n"/>
+      <c r="EG14" s="9" t="n"/>
+      <c r="EH14" s="9" t="n"/>
+      <c r="EI14" s="9" t="n"/>
+      <c r="EJ14" s="9" t="n"/>
       <c r="EK14" s="7" t="n"/>
       <c r="EL14" s="7" t="n"/>
       <c r="EM14" s="7" t="n"/>
@@ -2769,10 +2979,10 @@
       <c r="EO14" s="7" t="n"/>
       <c r="EP14" s="7" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="26" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Bar public</t>
+          <t>Dôme</t>
         </is>
       </c>
       <c r="C15" s="6" t="n"/>
@@ -2787,132 +2997,120 @@
       <c r="L15" s="7" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
-      <c r="O15" s="13" t="inlineStr">
-        <is>
-          <t>Alice, Athénaé, Lina-Rosa</t>
-        </is>
-      </c>
-      <c r="P15" s="14" t="n"/>
-      <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="14" t="n"/>
-      <c r="S15" s="14" t="n"/>
-      <c r="T15" s="14" t="n"/>
-      <c r="U15" s="14" t="n"/>
-      <c r="V15" s="14" t="n"/>
-      <c r="W15" s="14" t="n"/>
-      <c r="X15" s="14" t="n"/>
-      <c r="Y15" s="14" t="n"/>
-      <c r="Z15" s="14" t="n"/>
-      <c r="AA15" s="15" t="n"/>
-      <c r="AB15" s="14" t="n"/>
-      <c r="AC15" s="14" t="n"/>
-      <c r="AD15" s="14" t="n"/>
-      <c r="AE15" s="14" t="n"/>
-      <c r="AF15" s="14" t="n"/>
-      <c r="AG15" s="16" t="inlineStr">
-        <is>
-          <t>Anna, Antonin, Jolan</t>
-        </is>
-      </c>
-      <c r="AH15" s="14" t="n"/>
-      <c r="AI15" s="14" t="n"/>
-      <c r="AJ15" s="14" t="n"/>
-      <c r="AK15" s="14" t="n"/>
-      <c r="AL15" s="14" t="n"/>
-      <c r="AM15" s="15" t="n"/>
-      <c r="AN15" s="14" t="n"/>
-      <c r="AO15" s="14" t="n"/>
-      <c r="AP15" s="14" t="n"/>
-      <c r="AQ15" s="14" t="n"/>
-      <c r="AR15" s="14" t="n"/>
-      <c r="AS15" s="14" t="n"/>
-      <c r="AT15" s="14" t="n"/>
-      <c r="AU15" s="14" t="n"/>
-      <c r="AV15" s="14" t="n"/>
-      <c r="AW15" s="14" t="n"/>
-      <c r="AX15" s="14" t="n"/>
-      <c r="AY15" s="13" t="inlineStr">
-        <is>
-          <t>Iris, Léa C., Lucie, Noah</t>
-        </is>
-      </c>
-      <c r="AZ15" s="14" t="n"/>
-      <c r="BA15" s="14" t="n"/>
-      <c r="BB15" s="14" t="n"/>
-      <c r="BC15" s="14" t="n"/>
-      <c r="BD15" s="14" t="n"/>
-      <c r="BE15" s="14" t="n"/>
-      <c r="BF15" s="14" t="n"/>
-      <c r="BG15" s="14" t="n"/>
-      <c r="BH15" s="14" t="n"/>
-      <c r="BI15" s="14" t="n"/>
-      <c r="BJ15" s="14" t="n"/>
-      <c r="BK15" s="15" t="n"/>
-      <c r="BL15" s="14" t="n"/>
-      <c r="BM15" s="14" t="n"/>
-      <c r="BN15" s="14" t="n"/>
-      <c r="BO15" s="14" t="n"/>
-      <c r="BP15" s="14" t="n"/>
-      <c r="BQ15" s="16" t="inlineStr">
-        <is>
-          <t>Analou, Annouk, Corentin, Emma</t>
-        </is>
-      </c>
-      <c r="BR15" s="14" t="n"/>
-      <c r="BS15" s="14" t="n"/>
-      <c r="BT15" s="14" t="n"/>
-      <c r="BU15" s="14" t="n"/>
-      <c r="BV15" s="14" t="n"/>
-      <c r="BW15" s="15" t="n"/>
-      <c r="BX15" s="14" t="n"/>
-      <c r="BY15" s="14" t="n"/>
-      <c r="BZ15" s="14" t="n"/>
-      <c r="CA15" s="14" t="n"/>
-      <c r="CB15" s="14" t="n"/>
-      <c r="CC15" s="14" t="n"/>
-      <c r="CD15" s="14" t="n"/>
-      <c r="CE15" s="14" t="n"/>
-      <c r="CF15" s="14" t="n"/>
-      <c r="CG15" s="14" t="n"/>
-      <c r="CH15" s="14" t="n"/>
-      <c r="CI15" s="13" t="inlineStr">
-        <is>
-          <t>Alice, Anna, Jolan</t>
-        </is>
-      </c>
-      <c r="CJ15" s="14" t="n"/>
-      <c r="CK15" s="14" t="n"/>
-      <c r="CL15" s="14" t="n"/>
-      <c r="CM15" s="14" t="n"/>
-      <c r="CN15" s="14" t="n"/>
-      <c r="CO15" s="14" t="n"/>
-      <c r="CP15" s="14" t="n"/>
-      <c r="CQ15" s="14" t="n"/>
-      <c r="CR15" s="14" t="n"/>
-      <c r="CS15" s="14" t="n"/>
-      <c r="CT15" s="14" t="n"/>
-      <c r="CU15" s="15" t="n"/>
-      <c r="CV15" s="14" t="n"/>
-      <c r="CW15" s="14" t="n"/>
-      <c r="CX15" s="14" t="n"/>
-      <c r="CY15" s="14" t="n"/>
-      <c r="CZ15" s="14" t="n"/>
-      <c r="DA15" s="16" t="inlineStr">
-        <is>
-          <t>Louis C., Mickaël, Simon</t>
-        </is>
-      </c>
-      <c r="DB15" s="14" t="n"/>
-      <c r="DC15" s="14" t="n"/>
-      <c r="DD15" s="14" t="n"/>
-      <c r="DE15" s="14" t="n"/>
-      <c r="DF15" s="14" t="n"/>
-      <c r="DG15" s="15" t="n"/>
-      <c r="DH15" s="14" t="n"/>
-      <c r="DI15" s="14" t="n"/>
-      <c r="DJ15" s="14" t="n"/>
-      <c r="DK15" s="14" t="n"/>
-      <c r="DL15" s="14" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="7" t="n"/>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="6" t="n"/>
+      <c r="AB15" s="7" t="n"/>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>Maustetytöt</t>
+        </is>
+      </c>
+      <c r="AE15" s="9" t="n"/>
+      <c r="AF15" s="9" t="n"/>
+      <c r="AG15" s="9" t="n"/>
+      <c r="AH15" s="9" t="n"/>
+      <c r="AI15" s="9" t="n"/>
+      <c r="AJ15" s="9" t="n"/>
+      <c r="AK15" s="9" t="n"/>
+      <c r="AL15" s="9" t="n"/>
+      <c r="AM15" s="10" t="n"/>
+      <c r="AN15" s="9" t="n"/>
+      <c r="AO15" s="9" t="n"/>
+      <c r="AP15" s="9" t="n"/>
+      <c r="AQ15" s="9" t="n"/>
+      <c r="AR15" s="9" t="n"/>
+      <c r="AS15" s="7" t="n"/>
+      <c r="AT15" s="7" t="n"/>
+      <c r="AU15" s="7" t="n"/>
+      <c r="AV15" s="7" t="n"/>
+      <c r="AW15" s="7" t="n"/>
+      <c r="AX15" s="7" t="n"/>
+      <c r="AY15" s="6" t="n"/>
+      <c r="AZ15" s="7" t="n"/>
+      <c r="BA15" s="7" t="n"/>
+      <c r="BB15" s="7" t="n"/>
+      <c r="BC15" s="7" t="n"/>
+      <c r="BD15" s="7" t="n"/>
+      <c r="BE15" s="8" t="inlineStr">
+        <is>
+          <t>Skald</t>
+        </is>
+      </c>
+      <c r="BF15" s="9" t="n"/>
+      <c r="BG15" s="9" t="n"/>
+      <c r="BH15" s="9" t="n"/>
+      <c r="BI15" s="9" t="n"/>
+      <c r="BJ15" s="9" t="n"/>
+      <c r="BK15" s="10" t="n"/>
+      <c r="BL15" s="9" t="n"/>
+      <c r="BM15" s="9" t="n"/>
+      <c r="BN15" s="9" t="n"/>
+      <c r="BO15" s="9" t="n"/>
+      <c r="BP15" s="9" t="n"/>
+      <c r="BQ15" s="9" t="n"/>
+      <c r="BR15" s="9" t="n"/>
+      <c r="BS15" s="9" t="n"/>
+      <c r="BT15" s="7" t="n"/>
+      <c r="BU15" s="7" t="n"/>
+      <c r="BV15" s="7" t="n"/>
+      <c r="BW15" s="6" t="n"/>
+      <c r="BX15" s="7" t="n"/>
+      <c r="BY15" s="7" t="n"/>
+      <c r="BZ15" s="7" t="n"/>
+      <c r="CA15" s="7" t="n"/>
+      <c r="CB15" s="7" t="n"/>
+      <c r="CC15" s="7" t="n"/>
+      <c r="CD15" s="7" t="n"/>
+      <c r="CE15" s="7" t="n"/>
+      <c r="CF15" s="7" t="n"/>
+      <c r="CG15" s="7" t="n"/>
+      <c r="CH15" s="7" t="n"/>
+      <c r="CI15" s="6" t="n"/>
+      <c r="CJ15" s="7" t="n"/>
+      <c r="CK15" s="7" t="n"/>
+      <c r="CL15" s="7" t="n"/>
+      <c r="CM15" s="7" t="n"/>
+      <c r="CN15" s="7" t="n"/>
+      <c r="CO15" s="8" t="inlineStr">
+        <is>
+          <t>Witch Club Satan</t>
+        </is>
+      </c>
+      <c r="CP15" s="9" t="n"/>
+      <c r="CQ15" s="9" t="n"/>
+      <c r="CR15" s="9" t="n"/>
+      <c r="CS15" s="9" t="n"/>
+      <c r="CT15" s="9" t="n"/>
+      <c r="CU15" s="10" t="n"/>
+      <c r="CV15" s="9" t="n"/>
+      <c r="CW15" s="9" t="n"/>
+      <c r="CX15" s="9" t="n"/>
+      <c r="CY15" s="9" t="n"/>
+      <c r="CZ15" s="9" t="n"/>
+      <c r="DA15" s="7" t="n"/>
+      <c r="DB15" s="7" t="n"/>
+      <c r="DC15" s="7" t="n"/>
+      <c r="DD15" s="7" t="n"/>
+      <c r="DE15" s="7" t="n"/>
+      <c r="DF15" s="7" t="n"/>
+      <c r="DG15" s="6" t="n"/>
+      <c r="DH15" s="7" t="n"/>
+      <c r="DI15" s="7" t="n"/>
+      <c r="DJ15" s="7" t="n"/>
+      <c r="DK15" s="7" t="n"/>
+      <c r="DL15" s="7" t="n"/>
       <c r="DM15" s="7" t="n"/>
       <c r="DN15" s="7" t="n"/>
       <c r="DO15" s="7" t="n"/>
@@ -2944,10 +3142,10 @@
       <c r="EO15" s="7" t="n"/>
       <c r="EP15" s="7" t="n"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Entrée backstage</t>
+          <t>Club Tent</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
@@ -2962,144 +3160,136 @@
       <c r="L16" s="7" t="n"/>
       <c r="M16" s="7" t="n"/>
       <c r="N16" s="7" t="n"/>
-      <c r="O16" s="13" t="inlineStr">
-        <is>
-          <t>Annouk</t>
-        </is>
-      </c>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="14" t="n"/>
-      <c r="S16" s="14" t="n"/>
-      <c r="T16" s="14" t="n"/>
-      <c r="U16" s="14" t="n"/>
-      <c r="V16" s="14" t="n"/>
-      <c r="W16" s="14" t="n"/>
-      <c r="X16" s="14" t="n"/>
-      <c r="Y16" s="14" t="n"/>
-      <c r="Z16" s="14" t="n"/>
-      <c r="AA16" s="15" t="n"/>
-      <c r="AB16" s="14" t="n"/>
-      <c r="AC16" s="14" t="n"/>
-      <c r="AD16" s="14" t="n"/>
-      <c r="AE16" s="14" t="n"/>
-      <c r="AF16" s="14" t="n"/>
-      <c r="AG16" s="16" t="inlineStr">
-        <is>
-          <t>Auxence</t>
-        </is>
-      </c>
-      <c r="AH16" s="14" t="n"/>
-      <c r="AI16" s="14" t="n"/>
-      <c r="AJ16" s="14" t="n"/>
-      <c r="AK16" s="14" t="n"/>
-      <c r="AL16" s="14" t="n"/>
-      <c r="AM16" s="15" t="n"/>
-      <c r="AN16" s="14" t="n"/>
-      <c r="AO16" s="14" t="n"/>
-      <c r="AP16" s="14" t="n"/>
-      <c r="AQ16" s="14" t="n"/>
-      <c r="AR16" s="14" t="n"/>
-      <c r="AS16" s="14" t="n"/>
-      <c r="AT16" s="14" t="n"/>
-      <c r="AU16" s="14" t="n"/>
-      <c r="AV16" s="14" t="n"/>
-      <c r="AW16" s="14" t="n"/>
-      <c r="AX16" s="14" t="n"/>
-      <c r="AY16" s="13" t="inlineStr">
-        <is>
-          <t>Jules</t>
-        </is>
-      </c>
-      <c r="AZ16" s="14" t="n"/>
-      <c r="BA16" s="14" t="n"/>
-      <c r="BB16" s="14" t="n"/>
-      <c r="BC16" s="14" t="n"/>
-      <c r="BD16" s="14" t="n"/>
-      <c r="BE16" s="14" t="n"/>
-      <c r="BF16" s="14" t="n"/>
-      <c r="BG16" s="14" t="n"/>
-      <c r="BH16" s="14" t="n"/>
-      <c r="BI16" s="14" t="n"/>
-      <c r="BJ16" s="14" t="n"/>
-      <c r="BK16" s="15" t="n"/>
-      <c r="BL16" s="14" t="n"/>
-      <c r="BM16" s="14" t="n"/>
-      <c r="BN16" s="14" t="n"/>
-      <c r="BO16" s="14" t="n"/>
-      <c r="BP16" s="14" t="n"/>
-      <c r="BQ16" s="16" t="inlineStr">
-        <is>
-          <t>Athénaé</t>
-        </is>
-      </c>
-      <c r="BR16" s="14" t="n"/>
-      <c r="BS16" s="14" t="n"/>
-      <c r="BT16" s="14" t="n"/>
-      <c r="BU16" s="14" t="n"/>
-      <c r="BV16" s="14" t="n"/>
-      <c r="BW16" s="15" t="n"/>
-      <c r="BX16" s="14" t="n"/>
-      <c r="BY16" s="14" t="n"/>
-      <c r="BZ16" s="14" t="n"/>
-      <c r="CA16" s="14" t="n"/>
-      <c r="CB16" s="14" t="n"/>
-      <c r="CC16" s="14" t="n"/>
-      <c r="CD16" s="14" t="n"/>
-      <c r="CE16" s="14" t="n"/>
-      <c r="CF16" s="14" t="n"/>
-      <c r="CG16" s="14" t="n"/>
-      <c r="CH16" s="14" t="n"/>
-      <c r="CI16" s="13" t="inlineStr">
-        <is>
-          <t>Antonin</t>
-        </is>
-      </c>
-      <c r="CJ16" s="14" t="n"/>
-      <c r="CK16" s="14" t="n"/>
-      <c r="CL16" s="14" t="n"/>
-      <c r="CM16" s="14" t="n"/>
-      <c r="CN16" s="14" t="n"/>
-      <c r="CO16" s="14" t="n"/>
-      <c r="CP16" s="14" t="n"/>
-      <c r="CQ16" s="14" t="n"/>
-      <c r="CR16" s="14" t="n"/>
-      <c r="CS16" s="14" t="n"/>
-      <c r="CT16" s="14" t="n"/>
-      <c r="CU16" s="15" t="n"/>
-      <c r="CV16" s="14" t="n"/>
-      <c r="CW16" s="14" t="n"/>
-      <c r="CX16" s="14" t="n"/>
-      <c r="CY16" s="14" t="n"/>
-      <c r="CZ16" s="14" t="n"/>
-      <c r="DA16" s="16" t="inlineStr">
-        <is>
-          <t>Yann</t>
-        </is>
-      </c>
-      <c r="DB16" s="14" t="n"/>
-      <c r="DC16" s="14" t="n"/>
-      <c r="DD16" s="14" t="n"/>
-      <c r="DE16" s="14" t="n"/>
-      <c r="DF16" s="14" t="n"/>
-      <c r="DG16" s="15" t="n"/>
-      <c r="DH16" s="14" t="n"/>
-      <c r="DI16" s="14" t="n"/>
-      <c r="DJ16" s="14" t="n"/>
-      <c r="DK16" s="14" t="n"/>
-      <c r="DL16" s="14" t="n"/>
-      <c r="DM16" s="7" t="n"/>
-      <c r="DN16" s="7" t="n"/>
-      <c r="DO16" s="7" t="n"/>
-      <c r="DP16" s="7" t="n"/>
-      <c r="DQ16" s="7" t="n"/>
-      <c r="DR16" s="7" t="n"/>
-      <c r="DS16" s="6" t="n"/>
-      <c r="DT16" s="7" t="n"/>
-      <c r="DU16" s="7" t="n"/>
-      <c r="DV16" s="7" t="n"/>
-      <c r="DW16" s="7" t="n"/>
-      <c r="DX16" s="7" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="7" t="n"/>
+      <c r="Q16" s="7" t="n"/>
+      <c r="R16" s="7" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="7" t="n"/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>Soft Loft</t>
+        </is>
+      </c>
+      <c r="V16" s="9" t="n"/>
+      <c r="W16" s="9" t="n"/>
+      <c r="X16" s="9" t="n"/>
+      <c r="Y16" s="9" t="n"/>
+      <c r="Z16" s="9" t="n"/>
+      <c r="AA16" s="10" t="n"/>
+      <c r="AB16" s="9" t="n"/>
+      <c r="AC16" s="9" t="n"/>
+      <c r="AD16" s="9" t="n"/>
+      <c r="AE16" s="9" t="n"/>
+      <c r="AF16" s="9" t="n"/>
+      <c r="AG16" s="7" t="n"/>
+      <c r="AH16" s="7" t="n"/>
+      <c r="AI16" s="7" t="n"/>
+      <c r="AJ16" s="7" t="n"/>
+      <c r="AK16" s="7" t="n"/>
+      <c r="AL16" s="7" t="n"/>
+      <c r="AM16" s="6" t="n"/>
+      <c r="AN16" s="7" t="n"/>
+      <c r="AO16" s="7" t="n"/>
+      <c r="AP16" s="7" t="n"/>
+      <c r="AQ16" s="7" t="n"/>
+      <c r="AR16" s="7" t="n"/>
+      <c r="AS16" s="7" t="n"/>
+      <c r="AT16" s="7" t="n"/>
+      <c r="AU16" s="7" t="n"/>
+      <c r="AV16" s="8" t="inlineStr">
+        <is>
+          <t>DITTER</t>
+        </is>
+      </c>
+      <c r="AW16" s="9" t="n"/>
+      <c r="AX16" s="9" t="n"/>
+      <c r="AY16" s="10" t="n"/>
+      <c r="AZ16" s="9" t="n"/>
+      <c r="BA16" s="9" t="n"/>
+      <c r="BB16" s="9" t="n"/>
+      <c r="BC16" s="9" t="n"/>
+      <c r="BD16" s="9" t="n"/>
+      <c r="BE16" s="9" t="n"/>
+      <c r="BF16" s="9" t="n"/>
+      <c r="BG16" s="9" t="n"/>
+      <c r="BH16" s="7" t="n"/>
+      <c r="BI16" s="7" t="n"/>
+      <c r="BJ16" s="7" t="n"/>
+      <c r="BK16" s="6" t="n"/>
+      <c r="BL16" s="7" t="n"/>
+      <c r="BM16" s="7" t="n"/>
+      <c r="BN16" s="7" t="n"/>
+      <c r="BO16" s="7" t="n"/>
+      <c r="BP16" s="7" t="n"/>
+      <c r="BQ16" s="7" t="n"/>
+      <c r="BR16" s="7" t="n"/>
+      <c r="BS16" s="7" t="n"/>
+      <c r="BT16" s="7" t="n"/>
+      <c r="BU16" s="7" t="n"/>
+      <c r="BV16" s="7" t="n"/>
+      <c r="BW16" s="6" t="n"/>
+      <c r="BX16" s="7" t="n"/>
+      <c r="BY16" s="7" t="n"/>
+      <c r="BZ16" s="8" t="inlineStr">
+        <is>
+          <t>Sprints</t>
+        </is>
+      </c>
+      <c r="CA16" s="9" t="n"/>
+      <c r="CB16" s="9" t="n"/>
+      <c r="CC16" s="9" t="n"/>
+      <c r="CD16" s="9" t="n"/>
+      <c r="CE16" s="9" t="n"/>
+      <c r="CF16" s="9" t="n"/>
+      <c r="CG16" s="9" t="n"/>
+      <c r="CH16" s="9" t="n"/>
+      <c r="CI16" s="10" t="n"/>
+      <c r="CJ16" s="9" t="n"/>
+      <c r="CK16" s="9" t="n"/>
+      <c r="CL16" s="7" t="n"/>
+      <c r="CM16" s="7" t="n"/>
+      <c r="CN16" s="7" t="n"/>
+      <c r="CO16" s="7" t="n"/>
+      <c r="CP16" s="7" t="n"/>
+      <c r="CQ16" s="7" t="n"/>
+      <c r="CR16" s="7" t="n"/>
+      <c r="CS16" s="7" t="n"/>
+      <c r="CT16" s="7" t="n"/>
+      <c r="CU16" s="6" t="n"/>
+      <c r="CV16" s="7" t="n"/>
+      <c r="CW16" s="7" t="n"/>
+      <c r="CX16" s="7" t="n"/>
+      <c r="CY16" s="7" t="n"/>
+      <c r="CZ16" s="7" t="n"/>
+      <c r="DA16" s="7" t="n"/>
+      <c r="DB16" s="7" t="n"/>
+      <c r="DC16" s="7" t="n"/>
+      <c r="DD16" s="7" t="n"/>
+      <c r="DE16" s="7" t="n"/>
+      <c r="DF16" s="7" t="n"/>
+      <c r="DG16" s="6" t="n"/>
+      <c r="DH16" s="7" t="n"/>
+      <c r="DI16" s="7" t="n"/>
+      <c r="DJ16" s="7" t="n"/>
+      <c r="DK16" s="7" t="n"/>
+      <c r="DL16" s="7" t="n"/>
+      <c r="DM16" s="8" t="inlineStr">
+        <is>
+          <t>Sam Quealy</t>
+        </is>
+      </c>
+      <c r="DN16" s="9" t="n"/>
+      <c r="DO16" s="9" t="n"/>
+      <c r="DP16" s="9" t="n"/>
+      <c r="DQ16" s="9" t="n"/>
+      <c r="DR16" s="9" t="n"/>
+      <c r="DS16" s="10" t="n"/>
+      <c r="DT16" s="9" t="n"/>
+      <c r="DU16" s="9" t="n"/>
+      <c r="DV16" s="9" t="n"/>
+      <c r="DW16" s="9" t="n"/>
+      <c r="DX16" s="9" t="n"/>
       <c r="DY16" s="7" t="n"/>
       <c r="DZ16" s="7" t="n"/>
       <c r="EA16" s="7" t="n"/>
@@ -3119,169 +3309,205 @@
       <c r="EO16" s="7" t="n"/>
       <c r="EP16" s="7" t="n"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Déambule Gerry</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="7" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="7" t="n"/>
-      <c r="R17" s="7" t="n"/>
-      <c r="S17" s="7" t="n"/>
-      <c r="T17" s="7" t="n"/>
-      <c r="U17" s="16" t="inlineStr">
-        <is>
-          <t>Arthur</t>
-        </is>
-      </c>
-      <c r="V17" s="14" t="n"/>
-      <c r="W17" s="14" t="n"/>
-      <c r="X17" s="14" t="n"/>
-      <c r="Y17" s="14" t="n"/>
-      <c r="Z17" s="14" t="n"/>
-      <c r="AA17" s="15" t="n"/>
-      <c r="AB17" s="14" t="n"/>
-      <c r="AC17" s="14" t="n"/>
-      <c r="AD17" s="14" t="n"/>
-      <c r="AE17" s="14" t="n"/>
-      <c r="AF17" s="14" t="n"/>
-      <c r="AG17" s="14" t="n"/>
-      <c r="AH17" s="14" t="n"/>
-      <c r="AI17" s="14" t="n"/>
-      <c r="AJ17" s="14" t="n"/>
-      <c r="AK17" s="14" t="n"/>
-      <c r="AL17" s="14" t="n"/>
-      <c r="AM17" s="6" t="n"/>
-      <c r="AN17" s="7" t="n"/>
-      <c r="AO17" s="7" t="n"/>
-      <c r="AP17" s="7" t="n"/>
-      <c r="AQ17" s="7" t="n"/>
-      <c r="AR17" s="7" t="n"/>
-      <c r="AS17" s="7" t="n"/>
-      <c r="AT17" s="7" t="n"/>
-      <c r="AU17" s="7" t="n"/>
-      <c r="AV17" s="7" t="n"/>
-      <c r="AW17" s="7" t="n"/>
-      <c r="AX17" s="7" t="n"/>
-      <c r="AY17" s="6" t="n"/>
-      <c r="AZ17" s="7" t="n"/>
-      <c r="BA17" s="7" t="n"/>
-      <c r="BB17" s="7" t="n"/>
-      <c r="BC17" s="7" t="n"/>
-      <c r="BD17" s="7" t="n"/>
-      <c r="BE17" s="7" t="n"/>
-      <c r="BF17" s="7" t="n"/>
-      <c r="BG17" s="7" t="n"/>
-      <c r="BH17" s="7" t="n"/>
-      <c r="BI17" s="7" t="n"/>
-      <c r="BJ17" s="7" t="n"/>
-      <c r="BK17" s="6" t="n"/>
-      <c r="BL17" s="7" t="n"/>
-      <c r="BM17" s="7" t="n"/>
-      <c r="BN17" s="7" t="n"/>
-      <c r="BO17" s="7" t="n"/>
-      <c r="BP17" s="7" t="n"/>
-      <c r="BQ17" s="16" t="inlineStr">
-        <is>
-          <t>Alegria Lily</t>
-        </is>
-      </c>
-      <c r="BR17" s="14" t="n"/>
-      <c r="BS17" s="14" t="n"/>
-      <c r="BT17" s="14" t="n"/>
-      <c r="BU17" s="14" t="n"/>
-      <c r="BV17" s="14" t="n"/>
-      <c r="BW17" s="15" t="n"/>
-      <c r="BX17" s="14" t="n"/>
-      <c r="BY17" s="14" t="n"/>
-      <c r="BZ17" s="14" t="n"/>
-      <c r="CA17" s="14" t="n"/>
-      <c r="CB17" s="14" t="n"/>
-      <c r="CC17" s="14" t="n"/>
-      <c r="CD17" s="14" t="n"/>
-      <c r="CE17" s="14" t="n"/>
-      <c r="CF17" s="14" t="n"/>
-      <c r="CG17" s="14" t="n"/>
-      <c r="CH17" s="14" t="n"/>
-      <c r="CI17" s="6" t="n"/>
-      <c r="CJ17" s="7" t="n"/>
-      <c r="CK17" s="7" t="n"/>
-      <c r="CL17" s="7" t="n"/>
-      <c r="CM17" s="7" t="n"/>
-      <c r="CN17" s="7" t="n"/>
-      <c r="CO17" s="7" t="n"/>
-      <c r="CP17" s="7" t="n"/>
-      <c r="CQ17" s="7" t="n"/>
-      <c r="CR17" s="7" t="n"/>
-      <c r="CS17" s="7" t="n"/>
-      <c r="CT17" s="7" t="n"/>
-      <c r="CU17" s="6" t="n"/>
-      <c r="CV17" s="7" t="n"/>
-      <c r="CW17" s="7" t="n"/>
-      <c r="CX17" s="7" t="n"/>
-      <c r="CY17" s="7" t="n"/>
-      <c r="CZ17" s="7" t="n"/>
-      <c r="DA17" s="7" t="n"/>
-      <c r="DB17" s="7" t="n"/>
-      <c r="DC17" s="7" t="n"/>
-      <c r="DD17" s="7" t="n"/>
-      <c r="DE17" s="7" t="n"/>
-      <c r="DF17" s="7" t="n"/>
-      <c r="DG17" s="6" t="n"/>
-      <c r="DH17" s="7" t="n"/>
-      <c r="DI17" s="7" t="n"/>
-      <c r="DJ17" s="7" t="n"/>
-      <c r="DK17" s="7" t="n"/>
-      <c r="DL17" s="7" t="n"/>
-      <c r="DM17" s="7" t="n"/>
-      <c r="DN17" s="7" t="n"/>
-      <c r="DO17" s="7" t="n"/>
-      <c r="DP17" s="7" t="n"/>
-      <c r="DQ17" s="7" t="n"/>
-      <c r="DR17" s="7" t="n"/>
-      <c r="DS17" s="6" t="n"/>
-      <c r="DT17" s="7" t="n"/>
-      <c r="DU17" s="7" t="n"/>
-      <c r="DV17" s="7" t="n"/>
-      <c r="DW17" s="7" t="n"/>
-      <c r="DX17" s="7" t="n"/>
-      <c r="DY17" s="7" t="n"/>
-      <c r="DZ17" s="7" t="n"/>
-      <c r="EA17" s="7" t="n"/>
-      <c r="EB17" s="7" t="n"/>
-      <c r="EC17" s="7" t="n"/>
-      <c r="ED17" s="7" t="n"/>
-      <c r="EE17" s="6" t="n"/>
-      <c r="EF17" s="7" t="n"/>
-      <c r="EG17" s="7" t="n"/>
-      <c r="EH17" s="7" t="n"/>
-      <c r="EI17" s="7" t="n"/>
-      <c r="EJ17" s="7" t="n"/>
-      <c r="EK17" s="7" t="n"/>
-      <c r="EL17" s="7" t="n"/>
-      <c r="EM17" s="7" t="n"/>
-      <c r="EN17" s="7" t="n"/>
-      <c r="EO17" s="7" t="n"/>
-      <c r="EP17" s="7" t="n"/>
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="2" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4" t="n"/>
+      <c r="V17" s="4" t="n"/>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n"/>
+      <c r="Z17" s="4" t="n"/>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="4" t="n"/>
+      <c r="AD17" s="4" t="n"/>
+      <c r="AE17" s="4" t="n"/>
+      <c r="AF17" s="4" t="n"/>
+      <c r="AG17" s="4" t="n"/>
+      <c r="AH17" s="4" t="n"/>
+      <c r="AI17" s="4" t="n"/>
+      <c r="AJ17" s="4" t="n"/>
+      <c r="AK17" s="4" t="n"/>
+      <c r="AL17" s="4" t="n"/>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="AN17" s="4" t="n"/>
+      <c r="AO17" s="4" t="n"/>
+      <c r="AP17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="4" t="n"/>
+      <c r="AT17" s="4" t="n"/>
+      <c r="AU17" s="4" t="n"/>
+      <c r="AV17" s="4" t="n"/>
+      <c r="AW17" s="4" t="n"/>
+      <c r="AX17" s="4" t="n"/>
+      <c r="AY17" s="3" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="AZ17" s="4" t="n"/>
+      <c r="BA17" s="4" t="n"/>
+      <c r="BB17" s="4" t="n"/>
+      <c r="BC17" s="4" t="n"/>
+      <c r="BD17" s="4" t="n"/>
+      <c r="BE17" s="4" t="n"/>
+      <c r="BF17" s="4" t="n"/>
+      <c r="BG17" s="4" t="n"/>
+      <c r="BH17" s="4" t="n"/>
+      <c r="BI17" s="4" t="n"/>
+      <c r="BJ17" s="4" t="n"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="n"/>
+      <c r="BM17" s="4" t="n"/>
+      <c r="BN17" s="4" t="n"/>
+      <c r="BO17" s="4" t="n"/>
+      <c r="BP17" s="4" t="n"/>
+      <c r="BQ17" s="4" t="n"/>
+      <c r="BR17" s="4" t="n"/>
+      <c r="BS17" s="4" t="n"/>
+      <c r="BT17" s="4" t="n"/>
+      <c r="BU17" s="4" t="n"/>
+      <c r="BV17" s="4" t="n"/>
+      <c r="BW17" s="3" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="BX17" s="4" t="n"/>
+      <c r="BY17" s="4" t="n"/>
+      <c r="BZ17" s="4" t="n"/>
+      <c r="CA17" s="4" t="n"/>
+      <c r="CB17" s="4" t="n"/>
+      <c r="CC17" s="4" t="n"/>
+      <c r="CD17" s="4" t="n"/>
+      <c r="CE17" s="4" t="n"/>
+      <c r="CF17" s="4" t="n"/>
+      <c r="CG17" s="4" t="n"/>
+      <c r="CH17" s="4" t="n"/>
+      <c r="CI17" s="3" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="CJ17" s="4" t="n"/>
+      <c r="CK17" s="4" t="n"/>
+      <c r="CL17" s="4" t="n"/>
+      <c r="CM17" s="4" t="n"/>
+      <c r="CN17" s="4" t="n"/>
+      <c r="CO17" s="4" t="n"/>
+      <c r="CP17" s="4" t="n"/>
+      <c r="CQ17" s="4" t="n"/>
+      <c r="CR17" s="4" t="n"/>
+      <c r="CS17" s="4" t="n"/>
+      <c r="CT17" s="4" t="n"/>
+      <c r="CU17" s="3" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="CV17" s="4" t="n"/>
+      <c r="CW17" s="4" t="n"/>
+      <c r="CX17" s="4" t="n"/>
+      <c r="CY17" s="4" t="n"/>
+      <c r="CZ17" s="4" t="n"/>
+      <c r="DA17" s="4" t="n"/>
+      <c r="DB17" s="4" t="n"/>
+      <c r="DC17" s="4" t="n"/>
+      <c r="DD17" s="4" t="n"/>
+      <c r="DE17" s="4" t="n"/>
+      <c r="DF17" s="4" t="n"/>
+      <c r="DG17" s="3" t="inlineStr">
+        <is>
+          <t>00h</t>
+        </is>
+      </c>
+      <c r="DH17" s="4" t="n"/>
+      <c r="DI17" s="4" t="n"/>
+      <c r="DJ17" s="4" t="n"/>
+      <c r="DK17" s="4" t="n"/>
+      <c r="DL17" s="4" t="n"/>
+      <c r="DM17" s="4" t="n"/>
+      <c r="DN17" s="4" t="n"/>
+      <c r="DO17" s="4" t="n"/>
+      <c r="DP17" s="4" t="n"/>
+      <c r="DQ17" s="4" t="n"/>
+      <c r="DR17" s="4" t="n"/>
+      <c r="DS17" s="3" t="inlineStr">
+        <is>
+          <t>01h</t>
+        </is>
+      </c>
+      <c r="DT17" s="4" t="n"/>
+      <c r="DU17" s="4" t="n"/>
+      <c r="DV17" s="4" t="n"/>
+      <c r="DW17" s="4" t="n"/>
+      <c r="DX17" s="4" t="n"/>
+      <c r="DY17" s="4" t="n"/>
+      <c r="DZ17" s="4" t="n"/>
+      <c r="EA17" s="4" t="n"/>
+      <c r="EB17" s="4" t="n"/>
+      <c r="EC17" s="4" t="n"/>
+      <c r="ED17" s="4" t="n"/>
+      <c r="EE17" s="3" t="inlineStr">
+        <is>
+          <t>02h</t>
+        </is>
+      </c>
+      <c r="EF17" s="4" t="n"/>
+      <c r="EG17" s="4" t="n"/>
+      <c r="EH17" s="4" t="n"/>
+      <c r="EI17" s="4" t="n"/>
+      <c r="EJ17" s="4" t="n"/>
+      <c r="EK17" s="4" t="n"/>
+      <c r="EL17" s="4" t="n"/>
+      <c r="EM17" s="4" t="n"/>
+      <c r="EN17" s="4" t="n"/>
+      <c r="EO17" s="4" t="n"/>
+      <c r="EP17" s="4" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Déambule Colbok</t>
+          <t>Tech Jacquard</t>
         </is>
       </c>
       <c r="C18" s="6" t="n"/>
@@ -3308,34 +3534,30 @@
       <c r="X18" s="7" t="n"/>
       <c r="Y18" s="7" t="n"/>
       <c r="Z18" s="7" t="n"/>
-      <c r="AA18" s="13" t="inlineStr">
-        <is>
-          <t>Maëlan</t>
-        </is>
-      </c>
-      <c r="AB18" s="14" t="n"/>
-      <c r="AC18" s="14" t="n"/>
-      <c r="AD18" s="14" t="n"/>
-      <c r="AE18" s="14" t="n"/>
-      <c r="AF18" s="14" t="n"/>
-      <c r="AG18" s="14" t="n"/>
-      <c r="AH18" s="14" t="n"/>
-      <c r="AI18" s="14" t="n"/>
-      <c r="AJ18" s="14" t="n"/>
-      <c r="AK18" s="14" t="n"/>
-      <c r="AL18" s="14" t="n"/>
-      <c r="AM18" s="15" t="n"/>
-      <c r="AN18" s="14" t="n"/>
-      <c r="AO18" s="14" t="n"/>
-      <c r="AP18" s="14" t="n"/>
-      <c r="AQ18" s="14" t="n"/>
-      <c r="AR18" s="14" t="n"/>
-      <c r="AS18" s="14" t="n"/>
-      <c r="AT18" s="14" t="n"/>
-      <c r="AU18" s="14" t="n"/>
-      <c r="AV18" s="14" t="n"/>
-      <c r="AW18" s="14" t="n"/>
-      <c r="AX18" s="14" t="n"/>
+      <c r="AA18" s="6" t="n"/>
+      <c r="AB18" s="7" t="n"/>
+      <c r="AC18" s="7" t="n"/>
+      <c r="AD18" s="7" t="n"/>
+      <c r="AE18" s="7" t="n"/>
+      <c r="AF18" s="7" t="n"/>
+      <c r="AG18" s="7" t="n"/>
+      <c r="AH18" s="7" t="n"/>
+      <c r="AI18" s="7" t="n"/>
+      <c r="AJ18" s="7" t="n"/>
+      <c r="AK18" s="7" t="n"/>
+      <c r="AL18" s="7" t="n"/>
+      <c r="AM18" s="6" t="n"/>
+      <c r="AN18" s="7" t="n"/>
+      <c r="AO18" s="7" t="n"/>
+      <c r="AP18" s="7" t="n"/>
+      <c r="AQ18" s="7" t="n"/>
+      <c r="AR18" s="7" t="n"/>
+      <c r="AS18" s="7" t="n"/>
+      <c r="AT18" s="7" t="n"/>
+      <c r="AU18" s="7" t="n"/>
+      <c r="AV18" s="7" t="n"/>
+      <c r="AW18" s="7" t="n"/>
+      <c r="AX18" s="7" t="n"/>
       <c r="AY18" s="6" t="n"/>
       <c r="AZ18" s="7" t="n"/>
       <c r="BA18" s="7" t="n"/>
@@ -3360,34 +3582,34 @@
       <c r="BT18" s="7" t="n"/>
       <c r="BU18" s="7" t="n"/>
       <c r="BV18" s="7" t="n"/>
-      <c r="BW18" s="13" t="inlineStr">
-        <is>
-          <t>Ava</t>
-        </is>
-      </c>
-      <c r="BX18" s="14" t="n"/>
-      <c r="BY18" s="14" t="n"/>
-      <c r="BZ18" s="14" t="n"/>
-      <c r="CA18" s="14" t="n"/>
-      <c r="CB18" s="14" t="n"/>
-      <c r="CC18" s="14" t="n"/>
-      <c r="CD18" s="14" t="n"/>
-      <c r="CE18" s="14" t="n"/>
-      <c r="CF18" s="14" t="n"/>
-      <c r="CG18" s="14" t="n"/>
-      <c r="CH18" s="14" t="n"/>
-      <c r="CI18" s="15" t="n"/>
-      <c r="CJ18" s="14" t="n"/>
-      <c r="CK18" s="14" t="n"/>
-      <c r="CL18" s="14" t="n"/>
-      <c r="CM18" s="14" t="n"/>
-      <c r="CN18" s="14" t="n"/>
-      <c r="CO18" s="14" t="n"/>
-      <c r="CP18" s="14" t="n"/>
-      <c r="CQ18" s="14" t="n"/>
-      <c r="CR18" s="14" t="n"/>
-      <c r="CS18" s="14" t="n"/>
-      <c r="CT18" s="14" t="n"/>
+      <c r="BW18" s="12" t="inlineStr">
+        <is>
+          <t>Mathis</t>
+        </is>
+      </c>
+      <c r="BX18" s="13" t="n"/>
+      <c r="BY18" s="13" t="n"/>
+      <c r="BZ18" s="13" t="n"/>
+      <c r="CA18" s="13" t="n"/>
+      <c r="CB18" s="13" t="n"/>
+      <c r="CC18" s="13" t="n"/>
+      <c r="CD18" s="13" t="n"/>
+      <c r="CE18" s="13" t="n"/>
+      <c r="CF18" s="13" t="n"/>
+      <c r="CG18" s="13" t="n"/>
+      <c r="CH18" s="13" t="n"/>
+      <c r="CI18" s="14" t="n"/>
+      <c r="CJ18" s="13" t="n"/>
+      <c r="CK18" s="13" t="n"/>
+      <c r="CL18" s="13" t="n"/>
+      <c r="CM18" s="13" t="n"/>
+      <c r="CN18" s="13" t="n"/>
+      <c r="CO18" s="13" t="n"/>
+      <c r="CP18" s="13" t="n"/>
+      <c r="CQ18" s="13" t="n"/>
+      <c r="CR18" s="13" t="n"/>
+      <c r="CS18" s="13" t="n"/>
+      <c r="CT18" s="13" t="n"/>
       <c r="CU18" s="6" t="n"/>
       <c r="CV18" s="7" t="n"/>
       <c r="CW18" s="7" t="n"/>
@@ -3440,7 +3662,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Déambule Goulus</t>
+          <t>Tech PCGB</t>
         </is>
       </c>
       <c r="C19" s="6" t="n"/>
@@ -3461,28 +3683,24 @@
       <c r="R19" s="7" t="n"/>
       <c r="S19" s="7" t="n"/>
       <c r="T19" s="7" t="n"/>
-      <c r="U19" s="16" t="inlineStr">
-        <is>
-          <t>Morgane, Theo</t>
-        </is>
-      </c>
-      <c r="V19" s="14" t="n"/>
-      <c r="W19" s="14" t="n"/>
-      <c r="X19" s="14" t="n"/>
-      <c r="Y19" s="14" t="n"/>
-      <c r="Z19" s="14" t="n"/>
-      <c r="AA19" s="15" t="n"/>
-      <c r="AB19" s="14" t="n"/>
-      <c r="AC19" s="14" t="n"/>
-      <c r="AD19" s="14" t="n"/>
-      <c r="AE19" s="14" t="n"/>
-      <c r="AF19" s="14" t="n"/>
-      <c r="AG19" s="14" t="n"/>
-      <c r="AH19" s="14" t="n"/>
-      <c r="AI19" s="14" t="n"/>
-      <c r="AJ19" s="14" t="n"/>
-      <c r="AK19" s="14" t="n"/>
-      <c r="AL19" s="14" t="n"/>
+      <c r="U19" s="7" t="n"/>
+      <c r="V19" s="7" t="n"/>
+      <c r="W19" s="7" t="n"/>
+      <c r="X19" s="7" t="n"/>
+      <c r="Y19" s="7" t="n"/>
+      <c r="Z19" s="7" t="n"/>
+      <c r="AA19" s="6" t="n"/>
+      <c r="AB19" s="7" t="n"/>
+      <c r="AC19" s="7" t="n"/>
+      <c r="AD19" s="7" t="n"/>
+      <c r="AE19" s="7" t="n"/>
+      <c r="AF19" s="7" t="n"/>
+      <c r="AG19" s="7" t="n"/>
+      <c r="AH19" s="7" t="n"/>
+      <c r="AI19" s="7" t="n"/>
+      <c r="AJ19" s="7" t="n"/>
+      <c r="AK19" s="7" t="n"/>
+      <c r="AL19" s="7" t="n"/>
       <c r="AM19" s="6" t="n"/>
       <c r="AN19" s="7" t="n"/>
       <c r="AO19" s="7" t="n"/>
@@ -3501,34 +3719,34 @@
       <c r="BB19" s="7" t="n"/>
       <c r="BC19" s="7" t="n"/>
       <c r="BD19" s="7" t="n"/>
-      <c r="BE19" s="7" t="n"/>
-      <c r="BF19" s="7" t="n"/>
-      <c r="BG19" s="7" t="n"/>
-      <c r="BH19" s="7" t="n"/>
-      <c r="BI19" s="7" t="n"/>
-      <c r="BJ19" s="7" t="n"/>
-      <c r="BK19" s="13" t="inlineStr">
-        <is>
-          <t>Morgane, Simon</t>
-        </is>
-      </c>
-      <c r="BL19" s="14" t="n"/>
-      <c r="BM19" s="14" t="n"/>
-      <c r="BN19" s="14" t="n"/>
-      <c r="BO19" s="14" t="n"/>
-      <c r="BP19" s="14" t="n"/>
-      <c r="BQ19" s="14" t="n"/>
-      <c r="BR19" s="14" t="n"/>
-      <c r="BS19" s="14" t="n"/>
-      <c r="BT19" s="14" t="n"/>
-      <c r="BU19" s="14" t="n"/>
-      <c r="BV19" s="14" t="n"/>
-      <c r="BW19" s="15" t="n"/>
-      <c r="BX19" s="14" t="n"/>
-      <c r="BY19" s="14" t="n"/>
-      <c r="BZ19" s="14" t="n"/>
-      <c r="CA19" s="14" t="n"/>
-      <c r="CB19" s="14" t="n"/>
+      <c r="BE19" s="15" t="inlineStr">
+        <is>
+          <t>Morgana</t>
+        </is>
+      </c>
+      <c r="BF19" s="13" t="n"/>
+      <c r="BG19" s="13" t="n"/>
+      <c r="BH19" s="13" t="n"/>
+      <c r="BI19" s="13" t="n"/>
+      <c r="BJ19" s="13" t="n"/>
+      <c r="BK19" s="14" t="n"/>
+      <c r="BL19" s="13" t="n"/>
+      <c r="BM19" s="13" t="n"/>
+      <c r="BN19" s="13" t="n"/>
+      <c r="BO19" s="13" t="n"/>
+      <c r="BP19" s="13" t="n"/>
+      <c r="BQ19" s="7" t="n"/>
+      <c r="BR19" s="7" t="n"/>
+      <c r="BS19" s="7" t="n"/>
+      <c r="BT19" s="7" t="n"/>
+      <c r="BU19" s="7" t="n"/>
+      <c r="BV19" s="7" t="n"/>
+      <c r="BW19" s="6" t="n"/>
+      <c r="BX19" s="7" t="n"/>
+      <c r="BY19" s="7" t="n"/>
+      <c r="BZ19" s="7" t="n"/>
+      <c r="CA19" s="7" t="n"/>
+      <c r="CB19" s="7" t="n"/>
       <c r="CC19" s="7" t="n"/>
       <c r="CD19" s="7" t="n"/>
       <c r="CE19" s="7" t="n"/>
@@ -3599,7 +3817,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Déambule Volkanik</t>
+          <t>Tech T'es rien…</t>
         </is>
       </c>
       <c r="C20" s="6" t="n"/>
@@ -3620,34 +3838,34 @@
       <c r="R20" s="7" t="n"/>
       <c r="S20" s="7" t="n"/>
       <c r="T20" s="7" t="n"/>
-      <c r="U20" s="16" t="inlineStr">
-        <is>
-          <t>Emma</t>
-        </is>
-      </c>
-      <c r="V20" s="14" t="n"/>
-      <c r="W20" s="14" t="n"/>
-      <c r="X20" s="14" t="n"/>
-      <c r="Y20" s="14" t="n"/>
-      <c r="Z20" s="14" t="n"/>
-      <c r="AA20" s="15" t="n"/>
-      <c r="AB20" s="14" t="n"/>
-      <c r="AC20" s="14" t="n"/>
-      <c r="AD20" s="14" t="n"/>
-      <c r="AE20" s="14" t="n"/>
-      <c r="AF20" s="14" t="n"/>
-      <c r="AG20" s="14" t="n"/>
-      <c r="AH20" s="14" t="n"/>
-      <c r="AI20" s="14" t="n"/>
-      <c r="AJ20" s="14" t="n"/>
-      <c r="AK20" s="14" t="n"/>
-      <c r="AL20" s="14" t="n"/>
-      <c r="AM20" s="15" t="n"/>
-      <c r="AN20" s="14" t="n"/>
-      <c r="AO20" s="14" t="n"/>
-      <c r="AP20" s="14" t="n"/>
-      <c r="AQ20" s="14" t="n"/>
-      <c r="AR20" s="14" t="n"/>
+      <c r="U20" s="7" t="n"/>
+      <c r="V20" s="7" t="n"/>
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n"/>
+      <c r="Y20" s="7" t="n"/>
+      <c r="Z20" s="7" t="n"/>
+      <c r="AA20" s="12" t="inlineStr">
+        <is>
+          <t>Raphaël</t>
+        </is>
+      </c>
+      <c r="AB20" s="13" t="n"/>
+      <c r="AC20" s="13" t="n"/>
+      <c r="AD20" s="13" t="n"/>
+      <c r="AE20" s="13" t="n"/>
+      <c r="AF20" s="13" t="n"/>
+      <c r="AG20" s="13" t="n"/>
+      <c r="AH20" s="13" t="n"/>
+      <c r="AI20" s="13" t="n"/>
+      <c r="AJ20" s="13" t="n"/>
+      <c r="AK20" s="13" t="n"/>
+      <c r="AL20" s="13" t="n"/>
+      <c r="AM20" s="14" t="n"/>
+      <c r="AN20" s="13" t="n"/>
+      <c r="AO20" s="13" t="n"/>
+      <c r="AP20" s="13" t="n"/>
+      <c r="AQ20" s="13" t="n"/>
+      <c r="AR20" s="13" t="n"/>
       <c r="AS20" s="7" t="n"/>
       <c r="AT20" s="7" t="n"/>
       <c r="AU20" s="7" t="n"/>
@@ -3696,28 +3914,24 @@
       <c r="CL20" s="7" t="n"/>
       <c r="CM20" s="7" t="n"/>
       <c r="CN20" s="7" t="n"/>
-      <c r="CO20" s="16" t="inlineStr">
-        <is>
-          <t>Iris</t>
-        </is>
-      </c>
-      <c r="CP20" s="14" t="n"/>
-      <c r="CQ20" s="14" t="n"/>
-      <c r="CR20" s="14" t="n"/>
-      <c r="CS20" s="14" t="n"/>
-      <c r="CT20" s="14" t="n"/>
-      <c r="CU20" s="15" t="n"/>
-      <c r="CV20" s="14" t="n"/>
-      <c r="CW20" s="14" t="n"/>
-      <c r="CX20" s="14" t="n"/>
-      <c r="CY20" s="14" t="n"/>
-      <c r="CZ20" s="14" t="n"/>
-      <c r="DA20" s="14" t="n"/>
-      <c r="DB20" s="14" t="n"/>
-      <c r="DC20" s="14" t="n"/>
-      <c r="DD20" s="14" t="n"/>
-      <c r="DE20" s="14" t="n"/>
-      <c r="DF20" s="14" t="n"/>
+      <c r="CO20" s="7" t="n"/>
+      <c r="CP20" s="7" t="n"/>
+      <c r="CQ20" s="7" t="n"/>
+      <c r="CR20" s="7" t="n"/>
+      <c r="CS20" s="7" t="n"/>
+      <c r="CT20" s="7" t="n"/>
+      <c r="CU20" s="6" t="n"/>
+      <c r="CV20" s="7" t="n"/>
+      <c r="CW20" s="7" t="n"/>
+      <c r="CX20" s="7" t="n"/>
+      <c r="CY20" s="7" t="n"/>
+      <c r="CZ20" s="7" t="n"/>
+      <c r="DA20" s="7" t="n"/>
+      <c r="DB20" s="7" t="n"/>
+      <c r="DC20" s="7" t="n"/>
+      <c r="DD20" s="7" t="n"/>
+      <c r="DE20" s="7" t="n"/>
+      <c r="DF20" s="7" t="n"/>
       <c r="DG20" s="6" t="n"/>
       <c r="DH20" s="7" t="n"/>
       <c r="DI20" s="7" t="n"/>
@@ -3758,7 +3972,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Déambule Spoutnik</t>
+          <t>Tech Phusis</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
@@ -3785,40 +3999,40 @@
       <c r="X21" s="7" t="n"/>
       <c r="Y21" s="7" t="n"/>
       <c r="Z21" s="7" t="n"/>
-      <c r="AA21" s="13" t="inlineStr">
-        <is>
-          <t>Alexandra</t>
-        </is>
-      </c>
-      <c r="AB21" s="14" t="n"/>
-      <c r="AC21" s="14" t="n"/>
-      <c r="AD21" s="14" t="n"/>
-      <c r="AE21" s="14" t="n"/>
-      <c r="AF21" s="14" t="n"/>
-      <c r="AG21" s="14" t="n"/>
-      <c r="AH21" s="14" t="n"/>
-      <c r="AI21" s="14" t="n"/>
-      <c r="AJ21" s="14" t="n"/>
-      <c r="AK21" s="14" t="n"/>
-      <c r="AL21" s="14" t="n"/>
-      <c r="AM21" s="15" t="n"/>
-      <c r="AN21" s="14" t="n"/>
-      <c r="AO21" s="14" t="n"/>
-      <c r="AP21" s="14" t="n"/>
-      <c r="AQ21" s="14" t="n"/>
-      <c r="AR21" s="14" t="n"/>
-      <c r="AS21" s="14" t="n"/>
-      <c r="AT21" s="14" t="n"/>
-      <c r="AU21" s="14" t="n"/>
-      <c r="AV21" s="14" t="n"/>
-      <c r="AW21" s="14" t="n"/>
-      <c r="AX21" s="14" t="n"/>
-      <c r="AY21" s="6" t="n"/>
-      <c r="AZ21" s="7" t="n"/>
-      <c r="BA21" s="7" t="n"/>
-      <c r="BB21" s="7" t="n"/>
-      <c r="BC21" s="7" t="n"/>
-      <c r="BD21" s="7" t="n"/>
+      <c r="AA21" s="6" t="n"/>
+      <c r="AB21" s="7" t="n"/>
+      <c r="AC21" s="7" t="n"/>
+      <c r="AD21" s="7" t="n"/>
+      <c r="AE21" s="7" t="n"/>
+      <c r="AF21" s="7" t="n"/>
+      <c r="AG21" s="7" t="n"/>
+      <c r="AH21" s="7" t="n"/>
+      <c r="AI21" s="7" t="n"/>
+      <c r="AJ21" s="7" t="n"/>
+      <c r="AK21" s="7" t="n"/>
+      <c r="AL21" s="7" t="n"/>
+      <c r="AM21" s="12" t="inlineStr">
+        <is>
+          <t>Mireille</t>
+        </is>
+      </c>
+      <c r="AN21" s="13" t="n"/>
+      <c r="AO21" s="13" t="n"/>
+      <c r="AP21" s="13" t="n"/>
+      <c r="AQ21" s="13" t="n"/>
+      <c r="AR21" s="13" t="n"/>
+      <c r="AS21" s="13" t="n"/>
+      <c r="AT21" s="13" t="n"/>
+      <c r="AU21" s="13" t="n"/>
+      <c r="AV21" s="13" t="n"/>
+      <c r="AW21" s="13" t="n"/>
+      <c r="AX21" s="13" t="n"/>
+      <c r="AY21" s="14" t="n"/>
+      <c r="AZ21" s="13" t="n"/>
+      <c r="BA21" s="13" t="n"/>
+      <c r="BB21" s="13" t="n"/>
+      <c r="BC21" s="13" t="n"/>
+      <c r="BD21" s="13" t="n"/>
       <c r="BE21" s="7" t="n"/>
       <c r="BF21" s="7" t="n"/>
       <c r="BG21" s="7" t="n"/>
@@ -3849,22 +4063,18 @@
       <c r="CF21" s="7" t="n"/>
       <c r="CG21" s="7" t="n"/>
       <c r="CH21" s="7" t="n"/>
-      <c r="CI21" s="13" t="inlineStr">
-        <is>
-          <t>Alexandra</t>
-        </is>
-      </c>
-      <c r="CJ21" s="14" t="n"/>
-      <c r="CK21" s="14" t="n"/>
-      <c r="CL21" s="14" t="n"/>
-      <c r="CM21" s="14" t="n"/>
-      <c r="CN21" s="14" t="n"/>
-      <c r="CO21" s="14" t="n"/>
-      <c r="CP21" s="14" t="n"/>
-      <c r="CQ21" s="14" t="n"/>
-      <c r="CR21" s="14" t="n"/>
-      <c r="CS21" s="14" t="n"/>
-      <c r="CT21" s="14" t="n"/>
+      <c r="CI21" s="6" t="n"/>
+      <c r="CJ21" s="7" t="n"/>
+      <c r="CK21" s="7" t="n"/>
+      <c r="CL21" s="7" t="n"/>
+      <c r="CM21" s="7" t="n"/>
+      <c r="CN21" s="7" t="n"/>
+      <c r="CO21" s="7" t="n"/>
+      <c r="CP21" s="7" t="n"/>
+      <c r="CQ21" s="7" t="n"/>
+      <c r="CR21" s="7" t="n"/>
+      <c r="CS21" s="7" t="n"/>
+      <c r="CT21" s="7" t="n"/>
       <c r="CU21" s="6" t="n"/>
       <c r="CV21" s="7" t="n"/>
       <c r="CW21" s="7" t="n"/>
@@ -3917,7 +4127,7 @@
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Déambule FBI</t>
+          <t>Déambule Gerry</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
@@ -3938,40 +4148,40 @@
       <c r="R22" s="7" t="n"/>
       <c r="S22" s="7" t="n"/>
       <c r="T22" s="7" t="n"/>
-      <c r="U22" s="7" t="n"/>
-      <c r="V22" s="7" t="n"/>
-      <c r="W22" s="7" t="n"/>
-      <c r="X22" s="7" t="n"/>
-      <c r="Y22" s="7" t="n"/>
-      <c r="Z22" s="7" t="n"/>
-      <c r="AA22" s="13" t="inlineStr">
-        <is>
-          <t>Mathis</t>
-        </is>
-      </c>
-      <c r="AB22" s="14" t="n"/>
-      <c r="AC22" s="14" t="n"/>
-      <c r="AD22" s="14" t="n"/>
-      <c r="AE22" s="14" t="n"/>
-      <c r="AF22" s="14" t="n"/>
-      <c r="AG22" s="14" t="n"/>
-      <c r="AH22" s="14" t="n"/>
-      <c r="AI22" s="14" t="n"/>
-      <c r="AJ22" s="14" t="n"/>
-      <c r="AK22" s="14" t="n"/>
-      <c r="AL22" s="14" t="n"/>
-      <c r="AM22" s="15" t="n"/>
-      <c r="AN22" s="14" t="n"/>
-      <c r="AO22" s="14" t="n"/>
-      <c r="AP22" s="14" t="n"/>
-      <c r="AQ22" s="14" t="n"/>
-      <c r="AR22" s="14" t="n"/>
-      <c r="AS22" s="14" t="n"/>
-      <c r="AT22" s="14" t="n"/>
-      <c r="AU22" s="14" t="n"/>
-      <c r="AV22" s="14" t="n"/>
-      <c r="AW22" s="14" t="n"/>
-      <c r="AX22" s="14" t="n"/>
+      <c r="U22" s="15" t="inlineStr">
+        <is>
+          <t>Matteo</t>
+        </is>
+      </c>
+      <c r="V22" s="13" t="n"/>
+      <c r="W22" s="13" t="n"/>
+      <c r="X22" s="13" t="n"/>
+      <c r="Y22" s="13" t="n"/>
+      <c r="Z22" s="13" t="n"/>
+      <c r="AA22" s="14" t="n"/>
+      <c r="AB22" s="13" t="n"/>
+      <c r="AC22" s="13" t="n"/>
+      <c r="AD22" s="13" t="n"/>
+      <c r="AE22" s="13" t="n"/>
+      <c r="AF22" s="13" t="n"/>
+      <c r="AG22" s="13" t="n"/>
+      <c r="AH22" s="13" t="n"/>
+      <c r="AI22" s="13" t="n"/>
+      <c r="AJ22" s="13" t="n"/>
+      <c r="AK22" s="13" t="n"/>
+      <c r="AL22" s="13" t="n"/>
+      <c r="AM22" s="6" t="n"/>
+      <c r="AN22" s="7" t="n"/>
+      <c r="AO22" s="7" t="n"/>
+      <c r="AP22" s="7" t="n"/>
+      <c r="AQ22" s="7" t="n"/>
+      <c r="AR22" s="7" t="n"/>
+      <c r="AS22" s="7" t="n"/>
+      <c r="AT22" s="7" t="n"/>
+      <c r="AU22" s="7" t="n"/>
+      <c r="AV22" s="7" t="n"/>
+      <c r="AW22" s="7" t="n"/>
+      <c r="AX22" s="7" t="n"/>
       <c r="AY22" s="6" t="n"/>
       <c r="AZ22" s="7" t="n"/>
       <c r="BA22" s="7" t="n"/>
@@ -3990,46 +4200,46 @@
       <c r="BN22" s="7" t="n"/>
       <c r="BO22" s="7" t="n"/>
       <c r="BP22" s="7" t="n"/>
-      <c r="BQ22" s="7" t="n"/>
-      <c r="BR22" s="7" t="n"/>
-      <c r="BS22" s="7" t="n"/>
-      <c r="BT22" s="7" t="n"/>
-      <c r="BU22" s="7" t="n"/>
-      <c r="BV22" s="7" t="n"/>
-      <c r="BW22" s="6" t="n"/>
-      <c r="BX22" s="7" t="n"/>
-      <c r="BY22" s="7" t="n"/>
-      <c r="BZ22" s="7" t="n"/>
-      <c r="CA22" s="7" t="n"/>
-      <c r="CB22" s="7" t="n"/>
-      <c r="CC22" s="16" t="inlineStr">
-        <is>
-          <t>Rama</t>
-        </is>
-      </c>
-      <c r="CD22" s="14" t="n"/>
-      <c r="CE22" s="14" t="n"/>
-      <c r="CF22" s="14" t="n"/>
-      <c r="CG22" s="14" t="n"/>
-      <c r="CH22" s="14" t="n"/>
-      <c r="CI22" s="15" t="n"/>
-      <c r="CJ22" s="14" t="n"/>
-      <c r="CK22" s="14" t="n"/>
-      <c r="CL22" s="14" t="n"/>
-      <c r="CM22" s="14" t="n"/>
-      <c r="CN22" s="14" t="n"/>
-      <c r="CO22" s="14" t="n"/>
-      <c r="CP22" s="14" t="n"/>
-      <c r="CQ22" s="14" t="n"/>
-      <c r="CR22" s="14" t="n"/>
-      <c r="CS22" s="14" t="n"/>
-      <c r="CT22" s="14" t="n"/>
-      <c r="CU22" s="15" t="n"/>
-      <c r="CV22" s="14" t="n"/>
-      <c r="CW22" s="14" t="n"/>
-      <c r="CX22" s="14" t="n"/>
-      <c r="CY22" s="14" t="n"/>
-      <c r="CZ22" s="14" t="n"/>
+      <c r="BQ22" s="15" t="inlineStr">
+        <is>
+          <t>Yann</t>
+        </is>
+      </c>
+      <c r="BR22" s="13" t="n"/>
+      <c r="BS22" s="13" t="n"/>
+      <c r="BT22" s="13" t="n"/>
+      <c r="BU22" s="13" t="n"/>
+      <c r="BV22" s="13" t="n"/>
+      <c r="BW22" s="14" t="n"/>
+      <c r="BX22" s="13" t="n"/>
+      <c r="BY22" s="13" t="n"/>
+      <c r="BZ22" s="13" t="n"/>
+      <c r="CA22" s="13" t="n"/>
+      <c r="CB22" s="13" t="n"/>
+      <c r="CC22" s="13" t="n"/>
+      <c r="CD22" s="13" t="n"/>
+      <c r="CE22" s="13" t="n"/>
+      <c r="CF22" s="13" t="n"/>
+      <c r="CG22" s="13" t="n"/>
+      <c r="CH22" s="13" t="n"/>
+      <c r="CI22" s="6" t="n"/>
+      <c r="CJ22" s="7" t="n"/>
+      <c r="CK22" s="7" t="n"/>
+      <c r="CL22" s="7" t="n"/>
+      <c r="CM22" s="7" t="n"/>
+      <c r="CN22" s="7" t="n"/>
+      <c r="CO22" s="7" t="n"/>
+      <c r="CP22" s="7" t="n"/>
+      <c r="CQ22" s="7" t="n"/>
+      <c r="CR22" s="7" t="n"/>
+      <c r="CS22" s="7" t="n"/>
+      <c r="CT22" s="7" t="n"/>
+      <c r="CU22" s="6" t="n"/>
+      <c r="CV22" s="7" t="n"/>
+      <c r="CW22" s="7" t="n"/>
+      <c r="CX22" s="7" t="n"/>
+      <c r="CY22" s="7" t="n"/>
+      <c r="CZ22" s="7" t="n"/>
       <c r="DA22" s="7" t="n"/>
       <c r="DB22" s="7" t="n"/>
       <c r="DC22" s="7" t="n"/>
@@ -4076,7 +4286,7 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Tech Jacquard</t>
+          <t>Déambule Colbok</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
@@ -4103,30 +4313,34 @@
       <c r="X23" s="7" t="n"/>
       <c r="Y23" s="7" t="n"/>
       <c r="Z23" s="7" t="n"/>
-      <c r="AA23" s="6" t="n"/>
-      <c r="AB23" s="7" t="n"/>
-      <c r="AC23" s="7" t="n"/>
-      <c r="AD23" s="7" t="n"/>
-      <c r="AE23" s="7" t="n"/>
-      <c r="AF23" s="7" t="n"/>
-      <c r="AG23" s="7" t="n"/>
-      <c r="AH23" s="7" t="n"/>
-      <c r="AI23" s="7" t="n"/>
-      <c r="AJ23" s="7" t="n"/>
-      <c r="AK23" s="7" t="n"/>
-      <c r="AL23" s="7" t="n"/>
-      <c r="AM23" s="6" t="n"/>
-      <c r="AN23" s="7" t="n"/>
-      <c r="AO23" s="7" t="n"/>
-      <c r="AP23" s="7" t="n"/>
-      <c r="AQ23" s="7" t="n"/>
-      <c r="AR23" s="7" t="n"/>
-      <c r="AS23" s="7" t="n"/>
-      <c r="AT23" s="7" t="n"/>
-      <c r="AU23" s="7" t="n"/>
-      <c r="AV23" s="7" t="n"/>
-      <c r="AW23" s="7" t="n"/>
-      <c r="AX23" s="7" t="n"/>
+      <c r="AA23" s="12" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="AB23" s="13" t="n"/>
+      <c r="AC23" s="13" t="n"/>
+      <c r="AD23" s="13" t="n"/>
+      <c r="AE23" s="13" t="n"/>
+      <c r="AF23" s="13" t="n"/>
+      <c r="AG23" s="13" t="n"/>
+      <c r="AH23" s="13" t="n"/>
+      <c r="AI23" s="13" t="n"/>
+      <c r="AJ23" s="13" t="n"/>
+      <c r="AK23" s="13" t="n"/>
+      <c r="AL23" s="13" t="n"/>
+      <c r="AM23" s="14" t="n"/>
+      <c r="AN23" s="13" t="n"/>
+      <c r="AO23" s="13" t="n"/>
+      <c r="AP23" s="13" t="n"/>
+      <c r="AQ23" s="13" t="n"/>
+      <c r="AR23" s="13" t="n"/>
+      <c r="AS23" s="13" t="n"/>
+      <c r="AT23" s="13" t="n"/>
+      <c r="AU23" s="13" t="n"/>
+      <c r="AV23" s="13" t="n"/>
+      <c r="AW23" s="13" t="n"/>
+      <c r="AX23" s="13" t="n"/>
       <c r="AY23" s="6" t="n"/>
       <c r="AZ23" s="7" t="n"/>
       <c r="BA23" s="7" t="n"/>
@@ -4151,34 +4365,34 @@
       <c r="BT23" s="7" t="n"/>
       <c r="BU23" s="7" t="n"/>
       <c r="BV23" s="7" t="n"/>
-      <c r="BW23" s="13" t="inlineStr">
-        <is>
-          <t>Mathis</t>
-        </is>
-      </c>
-      <c r="BX23" s="14" t="n"/>
-      <c r="BY23" s="14" t="n"/>
-      <c r="BZ23" s="14" t="n"/>
-      <c r="CA23" s="14" t="n"/>
-      <c r="CB23" s="14" t="n"/>
-      <c r="CC23" s="14" t="n"/>
-      <c r="CD23" s="14" t="n"/>
-      <c r="CE23" s="14" t="n"/>
-      <c r="CF23" s="14" t="n"/>
-      <c r="CG23" s="14" t="n"/>
-      <c r="CH23" s="14" t="n"/>
-      <c r="CI23" s="15" t="n"/>
-      <c r="CJ23" s="14" t="n"/>
-      <c r="CK23" s="14" t="n"/>
-      <c r="CL23" s="14" t="n"/>
-      <c r="CM23" s="14" t="n"/>
-      <c r="CN23" s="14" t="n"/>
-      <c r="CO23" s="14" t="n"/>
-      <c r="CP23" s="14" t="n"/>
-      <c r="CQ23" s="14" t="n"/>
-      <c r="CR23" s="14" t="n"/>
-      <c r="CS23" s="14" t="n"/>
-      <c r="CT23" s="14" t="n"/>
+      <c r="BW23" s="12" t="inlineStr">
+        <is>
+          <t>Theo</t>
+        </is>
+      </c>
+      <c r="BX23" s="13" t="n"/>
+      <c r="BY23" s="13" t="n"/>
+      <c r="BZ23" s="13" t="n"/>
+      <c r="CA23" s="13" t="n"/>
+      <c r="CB23" s="13" t="n"/>
+      <c r="CC23" s="13" t="n"/>
+      <c r="CD23" s="13" t="n"/>
+      <c r="CE23" s="13" t="n"/>
+      <c r="CF23" s="13" t="n"/>
+      <c r="CG23" s="13" t="n"/>
+      <c r="CH23" s="13" t="n"/>
+      <c r="CI23" s="14" t="n"/>
+      <c r="CJ23" s="13" t="n"/>
+      <c r="CK23" s="13" t="n"/>
+      <c r="CL23" s="13" t="n"/>
+      <c r="CM23" s="13" t="n"/>
+      <c r="CN23" s="13" t="n"/>
+      <c r="CO23" s="13" t="n"/>
+      <c r="CP23" s="13" t="n"/>
+      <c r="CQ23" s="13" t="n"/>
+      <c r="CR23" s="13" t="n"/>
+      <c r="CS23" s="13" t="n"/>
+      <c r="CT23" s="13" t="n"/>
       <c r="CU23" s="6" t="n"/>
       <c r="CV23" s="7" t="n"/>
       <c r="CW23" s="7" t="n"/>
@@ -4231,7 +4445,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Tech PCGB</t>
+          <t>Déambule Goulus</t>
         </is>
       </c>
       <c r="C24" s="6" t="n"/>
@@ -4252,24 +4466,28 @@
       <c r="R24" s="7" t="n"/>
       <c r="S24" s="7" t="n"/>
       <c r="T24" s="7" t="n"/>
-      <c r="U24" s="7" t="n"/>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="7" t="n"/>
-      <c r="X24" s="7" t="n"/>
-      <c r="Y24" s="7" t="n"/>
-      <c r="Z24" s="7" t="n"/>
-      <c r="AA24" s="6" t="n"/>
-      <c r="AB24" s="7" t="n"/>
-      <c r="AC24" s="7" t="n"/>
-      <c r="AD24" s="7" t="n"/>
-      <c r="AE24" s="7" t="n"/>
-      <c r="AF24" s="7" t="n"/>
-      <c r="AG24" s="7" t="n"/>
-      <c r="AH24" s="7" t="n"/>
-      <c r="AI24" s="7" t="n"/>
-      <c r="AJ24" s="7" t="n"/>
-      <c r="AK24" s="7" t="n"/>
-      <c r="AL24" s="7" t="n"/>
+      <c r="U24" s="15" t="inlineStr">
+        <is>
+          <t>Auxence, Mathis</t>
+        </is>
+      </c>
+      <c r="V24" s="13" t="n"/>
+      <c r="W24" s="13" t="n"/>
+      <c r="X24" s="13" t="n"/>
+      <c r="Y24" s="13" t="n"/>
+      <c r="Z24" s="13" t="n"/>
+      <c r="AA24" s="14" t="n"/>
+      <c r="AB24" s="13" t="n"/>
+      <c r="AC24" s="13" t="n"/>
+      <c r="AD24" s="13" t="n"/>
+      <c r="AE24" s="13" t="n"/>
+      <c r="AF24" s="13" t="n"/>
+      <c r="AG24" s="13" t="n"/>
+      <c r="AH24" s="13" t="n"/>
+      <c r="AI24" s="13" t="n"/>
+      <c r="AJ24" s="13" t="n"/>
+      <c r="AK24" s="13" t="n"/>
+      <c r="AL24" s="13" t="n"/>
       <c r="AM24" s="6" t="n"/>
       <c r="AN24" s="7" t="n"/>
       <c r="AO24" s="7" t="n"/>
@@ -4288,34 +4506,34 @@
       <c r="BB24" s="7" t="n"/>
       <c r="BC24" s="7" t="n"/>
       <c r="BD24" s="7" t="n"/>
-      <c r="BE24" s="16" t="inlineStr">
-        <is>
-          <t>Morgana</t>
-        </is>
-      </c>
-      <c r="BF24" s="14" t="n"/>
-      <c r="BG24" s="14" t="n"/>
-      <c r="BH24" s="14" t="n"/>
-      <c r="BI24" s="14" t="n"/>
-      <c r="BJ24" s="14" t="n"/>
-      <c r="BK24" s="15" t="n"/>
-      <c r="BL24" s="14" t="n"/>
-      <c r="BM24" s="14" t="n"/>
-      <c r="BN24" s="14" t="n"/>
-      <c r="BO24" s="14" t="n"/>
-      <c r="BP24" s="14" t="n"/>
-      <c r="BQ24" s="7" t="n"/>
-      <c r="BR24" s="7" t="n"/>
-      <c r="BS24" s="7" t="n"/>
-      <c r="BT24" s="7" t="n"/>
-      <c r="BU24" s="7" t="n"/>
-      <c r="BV24" s="7" t="n"/>
-      <c r="BW24" s="6" t="n"/>
-      <c r="BX24" s="7" t="n"/>
-      <c r="BY24" s="7" t="n"/>
-      <c r="BZ24" s="7" t="n"/>
-      <c r="CA24" s="7" t="n"/>
-      <c r="CB24" s="7" t="n"/>
+      <c r="BE24" s="7" t="n"/>
+      <c r="BF24" s="7" t="n"/>
+      <c r="BG24" s="7" t="n"/>
+      <c r="BH24" s="7" t="n"/>
+      <c r="BI24" s="7" t="n"/>
+      <c r="BJ24" s="7" t="n"/>
+      <c r="BK24" s="12" t="inlineStr">
+        <is>
+          <t>Arthur, Maya</t>
+        </is>
+      </c>
+      <c r="BL24" s="13" t="n"/>
+      <c r="BM24" s="13" t="n"/>
+      <c r="BN24" s="13" t="n"/>
+      <c r="BO24" s="13" t="n"/>
+      <c r="BP24" s="13" t="n"/>
+      <c r="BQ24" s="13" t="n"/>
+      <c r="BR24" s="13" t="n"/>
+      <c r="BS24" s="13" t="n"/>
+      <c r="BT24" s="13" t="n"/>
+      <c r="BU24" s="13" t="n"/>
+      <c r="BV24" s="13" t="n"/>
+      <c r="BW24" s="14" t="n"/>
+      <c r="BX24" s="13" t="n"/>
+      <c r="BY24" s="13" t="n"/>
+      <c r="BZ24" s="13" t="n"/>
+      <c r="CA24" s="13" t="n"/>
+      <c r="CB24" s="13" t="n"/>
       <c r="CC24" s="7" t="n"/>
       <c r="CD24" s="7" t="n"/>
       <c r="CE24" s="7" t="n"/>
@@ -4386,7 +4604,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Tech T'es rien…</t>
+          <t>Déambule Volkanik</t>
         </is>
       </c>
       <c r="C25" s="6" t="n"/>
@@ -4407,34 +4625,34 @@
       <c r="R25" s="7" t="n"/>
       <c r="S25" s="7" t="n"/>
       <c r="T25" s="7" t="n"/>
-      <c r="U25" s="7" t="n"/>
-      <c r="V25" s="7" t="n"/>
-      <c r="W25" s="7" t="n"/>
-      <c r="X25" s="7" t="n"/>
-      <c r="Y25" s="7" t="n"/>
-      <c r="Z25" s="7" t="n"/>
-      <c r="AA25" s="13" t="inlineStr">
-        <is>
-          <t>Raphaël</t>
-        </is>
-      </c>
-      <c r="AB25" s="14" t="n"/>
-      <c r="AC25" s="14" t="n"/>
-      <c r="AD25" s="14" t="n"/>
-      <c r="AE25" s="14" t="n"/>
-      <c r="AF25" s="14" t="n"/>
-      <c r="AG25" s="14" t="n"/>
-      <c r="AH25" s="14" t="n"/>
-      <c r="AI25" s="14" t="n"/>
-      <c r="AJ25" s="14" t="n"/>
-      <c r="AK25" s="14" t="n"/>
-      <c r="AL25" s="14" t="n"/>
-      <c r="AM25" s="15" t="n"/>
-      <c r="AN25" s="14" t="n"/>
-      <c r="AO25" s="14" t="n"/>
-      <c r="AP25" s="14" t="n"/>
-      <c r="AQ25" s="14" t="n"/>
-      <c r="AR25" s="14" t="n"/>
+      <c r="U25" s="15" t="inlineStr">
+        <is>
+          <t>Alegria Lily</t>
+        </is>
+      </c>
+      <c r="V25" s="13" t="n"/>
+      <c r="W25" s="13" t="n"/>
+      <c r="X25" s="13" t="n"/>
+      <c r="Y25" s="13" t="n"/>
+      <c r="Z25" s="13" t="n"/>
+      <c r="AA25" s="14" t="n"/>
+      <c r="AB25" s="13" t="n"/>
+      <c r="AC25" s="13" t="n"/>
+      <c r="AD25" s="13" t="n"/>
+      <c r="AE25" s="13" t="n"/>
+      <c r="AF25" s="13" t="n"/>
+      <c r="AG25" s="13" t="n"/>
+      <c r="AH25" s="13" t="n"/>
+      <c r="AI25" s="13" t="n"/>
+      <c r="AJ25" s="13" t="n"/>
+      <c r="AK25" s="13" t="n"/>
+      <c r="AL25" s="13" t="n"/>
+      <c r="AM25" s="14" t="n"/>
+      <c r="AN25" s="13" t="n"/>
+      <c r="AO25" s="13" t="n"/>
+      <c r="AP25" s="13" t="n"/>
+      <c r="AQ25" s="13" t="n"/>
+      <c r="AR25" s="13" t="n"/>
       <c r="AS25" s="7" t="n"/>
       <c r="AT25" s="7" t="n"/>
       <c r="AU25" s="7" t="n"/>
@@ -4483,24 +4701,28 @@
       <c r="CL25" s="7" t="n"/>
       <c r="CM25" s="7" t="n"/>
       <c r="CN25" s="7" t="n"/>
-      <c r="CO25" s="7" t="n"/>
-      <c r="CP25" s="7" t="n"/>
-      <c r="CQ25" s="7" t="n"/>
-      <c r="CR25" s="7" t="n"/>
-      <c r="CS25" s="7" t="n"/>
-      <c r="CT25" s="7" t="n"/>
-      <c r="CU25" s="6" t="n"/>
-      <c r="CV25" s="7" t="n"/>
-      <c r="CW25" s="7" t="n"/>
-      <c r="CX25" s="7" t="n"/>
-      <c r="CY25" s="7" t="n"/>
-      <c r="CZ25" s="7" t="n"/>
-      <c r="DA25" s="7" t="n"/>
-      <c r="DB25" s="7" t="n"/>
-      <c r="DC25" s="7" t="n"/>
-      <c r="DD25" s="7" t="n"/>
-      <c r="DE25" s="7" t="n"/>
-      <c r="DF25" s="7" t="n"/>
+      <c r="CO25" s="15" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="CP25" s="13" t="n"/>
+      <c r="CQ25" s="13" t="n"/>
+      <c r="CR25" s="13" t="n"/>
+      <c r="CS25" s="13" t="n"/>
+      <c r="CT25" s="13" t="n"/>
+      <c r="CU25" s="14" t="n"/>
+      <c r="CV25" s="13" t="n"/>
+      <c r="CW25" s="13" t="n"/>
+      <c r="CX25" s="13" t="n"/>
+      <c r="CY25" s="13" t="n"/>
+      <c r="CZ25" s="13" t="n"/>
+      <c r="DA25" s="13" t="n"/>
+      <c r="DB25" s="13" t="n"/>
+      <c r="DC25" s="13" t="n"/>
+      <c r="DD25" s="13" t="n"/>
+      <c r="DE25" s="13" t="n"/>
+      <c r="DF25" s="13" t="n"/>
       <c r="DG25" s="6" t="n"/>
       <c r="DH25" s="7" t="n"/>
       <c r="DI25" s="7" t="n"/>
@@ -4541,7 +4763,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Tech Phusis</t>
+          <t>Déambule Spoutnik</t>
         </is>
       </c>
       <c r="C26" s="6" t="n"/>
@@ -4568,40 +4790,40 @@
       <c r="X26" s="7" t="n"/>
       <c r="Y26" s="7" t="n"/>
       <c r="Z26" s="7" t="n"/>
-      <c r="AA26" s="6" t="n"/>
-      <c r="AB26" s="7" t="n"/>
-      <c r="AC26" s="7" t="n"/>
-      <c r="AD26" s="7" t="n"/>
-      <c r="AE26" s="7" t="n"/>
-      <c r="AF26" s="7" t="n"/>
-      <c r="AG26" s="7" t="n"/>
-      <c r="AH26" s="7" t="n"/>
-      <c r="AI26" s="7" t="n"/>
-      <c r="AJ26" s="7" t="n"/>
-      <c r="AK26" s="7" t="n"/>
-      <c r="AL26" s="7" t="n"/>
-      <c r="AM26" s="13" t="inlineStr">
-        <is>
-          <t>Mireille</t>
-        </is>
-      </c>
-      <c r="AN26" s="14" t="n"/>
-      <c r="AO26" s="14" t="n"/>
-      <c r="AP26" s="14" t="n"/>
-      <c r="AQ26" s="14" t="n"/>
-      <c r="AR26" s="14" t="n"/>
-      <c r="AS26" s="14" t="n"/>
-      <c r="AT26" s="14" t="n"/>
-      <c r="AU26" s="14" t="n"/>
-      <c r="AV26" s="14" t="n"/>
-      <c r="AW26" s="14" t="n"/>
-      <c r="AX26" s="14" t="n"/>
-      <c r="AY26" s="15" t="n"/>
-      <c r="AZ26" s="14" t="n"/>
-      <c r="BA26" s="14" t="n"/>
-      <c r="BB26" s="14" t="n"/>
-      <c r="BC26" s="14" t="n"/>
-      <c r="BD26" s="14" t="n"/>
+      <c r="AA26" s="12" t="inlineStr">
+        <is>
+          <t>Annouk</t>
+        </is>
+      </c>
+      <c r="AB26" s="13" t="n"/>
+      <c r="AC26" s="13" t="n"/>
+      <c r="AD26" s="13" t="n"/>
+      <c r="AE26" s="13" t="n"/>
+      <c r="AF26" s="13" t="n"/>
+      <c r="AG26" s="13" t="n"/>
+      <c r="AH26" s="13" t="n"/>
+      <c r="AI26" s="13" t="n"/>
+      <c r="AJ26" s="13" t="n"/>
+      <c r="AK26" s="13" t="n"/>
+      <c r="AL26" s="13" t="n"/>
+      <c r="AM26" s="14" t="n"/>
+      <c r="AN26" s="13" t="n"/>
+      <c r="AO26" s="13" t="n"/>
+      <c r="AP26" s="13" t="n"/>
+      <c r="AQ26" s="13" t="n"/>
+      <c r="AR26" s="13" t="n"/>
+      <c r="AS26" s="13" t="n"/>
+      <c r="AT26" s="13" t="n"/>
+      <c r="AU26" s="13" t="n"/>
+      <c r="AV26" s="13" t="n"/>
+      <c r="AW26" s="13" t="n"/>
+      <c r="AX26" s="13" t="n"/>
+      <c r="AY26" s="6" t="n"/>
+      <c r="AZ26" s="7" t="n"/>
+      <c r="BA26" s="7" t="n"/>
+      <c r="BB26" s="7" t="n"/>
+      <c r="BC26" s="7" t="n"/>
+      <c r="BD26" s="7" t="n"/>
       <c r="BE26" s="7" t="n"/>
       <c r="BF26" s="7" t="n"/>
       <c r="BG26" s="7" t="n"/>
@@ -4632,18 +4854,22 @@
       <c r="CF26" s="7" t="n"/>
       <c r="CG26" s="7" t="n"/>
       <c r="CH26" s="7" t="n"/>
-      <c r="CI26" s="6" t="n"/>
-      <c r="CJ26" s="7" t="n"/>
-      <c r="CK26" s="7" t="n"/>
-      <c r="CL26" s="7" t="n"/>
-      <c r="CM26" s="7" t="n"/>
-      <c r="CN26" s="7" t="n"/>
-      <c r="CO26" s="7" t="n"/>
-      <c r="CP26" s="7" t="n"/>
-      <c r="CQ26" s="7" t="n"/>
-      <c r="CR26" s="7" t="n"/>
-      <c r="CS26" s="7" t="n"/>
-      <c r="CT26" s="7" t="n"/>
+      <c r="CI26" s="12" t="inlineStr">
+        <is>
+          <t>Marot</t>
+        </is>
+      </c>
+      <c r="CJ26" s="13" t="n"/>
+      <c r="CK26" s="13" t="n"/>
+      <c r="CL26" s="13" t="n"/>
+      <c r="CM26" s="13" t="n"/>
+      <c r="CN26" s="13" t="n"/>
+      <c r="CO26" s="13" t="n"/>
+      <c r="CP26" s="13" t="n"/>
+      <c r="CQ26" s="13" t="n"/>
+      <c r="CR26" s="13" t="n"/>
+      <c r="CS26" s="13" t="n"/>
+      <c r="CT26" s="13" t="n"/>
       <c r="CU26" s="6" t="n"/>
       <c r="CV26" s="7" t="n"/>
       <c r="CW26" s="7" t="n"/>
@@ -4693,75 +4919,429 @@
       <c r="EO26" s="7" t="n"/>
       <c r="EP26" s="7" t="n"/>
     </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Déambule FBI</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="7" t="n"/>
+      <c r="N27" s="7" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="7" t="n"/>
+      <c r="Q27" s="7" t="n"/>
+      <c r="R27" s="7" t="n"/>
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="7" t="n"/>
+      <c r="U27" s="7" t="n"/>
+      <c r="V27" s="7" t="n"/>
+      <c r="W27" s="7" t="n"/>
+      <c r="X27" s="7" t="n"/>
+      <c r="Y27" s="7" t="n"/>
+      <c r="Z27" s="7" t="n"/>
+      <c r="AA27" s="12" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="AB27" s="13" t="n"/>
+      <c r="AC27" s="13" t="n"/>
+      <c r="AD27" s="13" t="n"/>
+      <c r="AE27" s="13" t="n"/>
+      <c r="AF27" s="13" t="n"/>
+      <c r="AG27" s="13" t="n"/>
+      <c r="AH27" s="13" t="n"/>
+      <c r="AI27" s="13" t="n"/>
+      <c r="AJ27" s="13" t="n"/>
+      <c r="AK27" s="13" t="n"/>
+      <c r="AL27" s="13" t="n"/>
+      <c r="AM27" s="14" t="n"/>
+      <c r="AN27" s="13" t="n"/>
+      <c r="AO27" s="13" t="n"/>
+      <c r="AP27" s="13" t="n"/>
+      <c r="AQ27" s="13" t="n"/>
+      <c r="AR27" s="13" t="n"/>
+      <c r="AS27" s="13" t="n"/>
+      <c r="AT27" s="13" t="n"/>
+      <c r="AU27" s="13" t="n"/>
+      <c r="AV27" s="13" t="n"/>
+      <c r="AW27" s="13" t="n"/>
+      <c r="AX27" s="13" t="n"/>
+      <c r="AY27" s="6" t="n"/>
+      <c r="AZ27" s="7" t="n"/>
+      <c r="BA27" s="7" t="n"/>
+      <c r="BB27" s="7" t="n"/>
+      <c r="BC27" s="7" t="n"/>
+      <c r="BD27" s="7" t="n"/>
+      <c r="BE27" s="7" t="n"/>
+      <c r="BF27" s="7" t="n"/>
+      <c r="BG27" s="7" t="n"/>
+      <c r="BH27" s="7" t="n"/>
+      <c r="BI27" s="7" t="n"/>
+      <c r="BJ27" s="7" t="n"/>
+      <c r="BK27" s="6" t="n"/>
+      <c r="BL27" s="7" t="n"/>
+      <c r="BM27" s="7" t="n"/>
+      <c r="BN27" s="7" t="n"/>
+      <c r="BO27" s="7" t="n"/>
+      <c r="BP27" s="7" t="n"/>
+      <c r="BQ27" s="7" t="n"/>
+      <c r="BR27" s="7" t="n"/>
+      <c r="BS27" s="7" t="n"/>
+      <c r="BT27" s="7" t="n"/>
+      <c r="BU27" s="7" t="n"/>
+      <c r="BV27" s="7" t="n"/>
+      <c r="BW27" s="6" t="n"/>
+      <c r="BX27" s="7" t="n"/>
+      <c r="BY27" s="7" t="n"/>
+      <c r="BZ27" s="7" t="n"/>
+      <c r="CA27" s="7" t="n"/>
+      <c r="CB27" s="7" t="n"/>
+      <c r="CC27" s="15" t="inlineStr">
+        <is>
+          <t>Léa C.</t>
+        </is>
+      </c>
+      <c r="CD27" s="13" t="n"/>
+      <c r="CE27" s="13" t="n"/>
+      <c r="CF27" s="13" t="n"/>
+      <c r="CG27" s="13" t="n"/>
+      <c r="CH27" s="13" t="n"/>
+      <c r="CI27" s="14" t="n"/>
+      <c r="CJ27" s="13" t="n"/>
+      <c r="CK27" s="13" t="n"/>
+      <c r="CL27" s="13" t="n"/>
+      <c r="CM27" s="13" t="n"/>
+      <c r="CN27" s="13" t="n"/>
+      <c r="CO27" s="13" t="n"/>
+      <c r="CP27" s="13" t="n"/>
+      <c r="CQ27" s="13" t="n"/>
+      <c r="CR27" s="13" t="n"/>
+      <c r="CS27" s="13" t="n"/>
+      <c r="CT27" s="13" t="n"/>
+      <c r="CU27" s="14" t="n"/>
+      <c r="CV27" s="13" t="n"/>
+      <c r="CW27" s="13" t="n"/>
+      <c r="CX27" s="13" t="n"/>
+      <c r="CY27" s="13" t="n"/>
+      <c r="CZ27" s="13" t="n"/>
+      <c r="DA27" s="7" t="n"/>
+      <c r="DB27" s="7" t="n"/>
+      <c r="DC27" s="7" t="n"/>
+      <c r="DD27" s="7" t="n"/>
+      <c r="DE27" s="7" t="n"/>
+      <c r="DF27" s="7" t="n"/>
+      <c r="DG27" s="6" t="n"/>
+      <c r="DH27" s="7" t="n"/>
+      <c r="DI27" s="7" t="n"/>
+      <c r="DJ27" s="7" t="n"/>
+      <c r="DK27" s="7" t="n"/>
+      <c r="DL27" s="7" t="n"/>
+      <c r="DM27" s="7" t="n"/>
+      <c r="DN27" s="7" t="n"/>
+      <c r="DO27" s="7" t="n"/>
+      <c r="DP27" s="7" t="n"/>
+      <c r="DQ27" s="7" t="n"/>
+      <c r="DR27" s="7" t="n"/>
+      <c r="DS27" s="6" t="n"/>
+      <c r="DT27" s="7" t="n"/>
+      <c r="DU27" s="7" t="n"/>
+      <c r="DV27" s="7" t="n"/>
+      <c r="DW27" s="7" t="n"/>
+      <c r="DX27" s="7" t="n"/>
+      <c r="DY27" s="7" t="n"/>
+      <c r="DZ27" s="7" t="n"/>
+      <c r="EA27" s="7" t="n"/>
+      <c r="EB27" s="7" t="n"/>
+      <c r="EC27" s="7" t="n"/>
+      <c r="ED27" s="7" t="n"/>
+      <c r="EE27" s="6" t="n"/>
+      <c r="EF27" s="7" t="n"/>
+      <c r="EG27" s="7" t="n"/>
+      <c r="EH27" s="7" t="n"/>
+      <c r="EI27" s="7" t="n"/>
+      <c r="EJ27" s="7" t="n"/>
+      <c r="EK27" s="7" t="n"/>
+      <c r="EL27" s="7" t="n"/>
+      <c r="EM27" s="7" t="n"/>
+      <c r="EN27" s="7" t="n"/>
+      <c r="EO27" s="7" t="n"/>
+      <c r="EP27" s="7" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="2" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="n"/>
+      <c r="W28" s="4" t="n"/>
+      <c r="X28" s="4" t="n"/>
+      <c r="Y28" s="4" t="n"/>
+      <c r="Z28" s="4" t="n"/>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="AB28" s="4" t="n"/>
+      <c r="AC28" s="4" t="n"/>
+      <c r="AD28" s="4" t="n"/>
+      <c r="AE28" s="4" t="n"/>
+      <c r="AF28" s="4" t="n"/>
+      <c r="AG28" s="4" t="n"/>
+      <c r="AH28" s="4" t="n"/>
+      <c r="AI28" s="4" t="n"/>
+      <c r="AJ28" s="4" t="n"/>
+      <c r="AK28" s="4" t="n"/>
+      <c r="AL28" s="4" t="n"/>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="AN28" s="4" t="n"/>
+      <c r="AO28" s="4" t="n"/>
+      <c r="AP28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="n"/>
+      <c r="AV28" s="4" t="n"/>
+      <c r="AW28" s="4" t="n"/>
+      <c r="AX28" s="4" t="n"/>
+      <c r="AY28" s="3" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="AZ28" s="4" t="n"/>
+      <c r="BA28" s="4" t="n"/>
+      <c r="BB28" s="4" t="n"/>
+      <c r="BC28" s="4" t="n"/>
+      <c r="BD28" s="4" t="n"/>
+      <c r="BE28" s="4" t="n"/>
+      <c r="BF28" s="4" t="n"/>
+      <c r="BG28" s="4" t="n"/>
+      <c r="BH28" s="4" t="n"/>
+      <c r="BI28" s="4" t="n"/>
+      <c r="BJ28" s="4" t="n"/>
+      <c r="BK28" s="3" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="BL28" s="4" t="n"/>
+      <c r="BM28" s="4" t="n"/>
+      <c r="BN28" s="4" t="n"/>
+      <c r="BO28" s="4" t="n"/>
+      <c r="BP28" s="4" t="n"/>
+      <c r="BQ28" s="4" t="n"/>
+      <c r="BR28" s="4" t="n"/>
+      <c r="BS28" s="4" t="n"/>
+      <c r="BT28" s="4" t="n"/>
+      <c r="BU28" s="4" t="n"/>
+      <c r="BV28" s="4" t="n"/>
+      <c r="BW28" s="3" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="BX28" s="4" t="n"/>
+      <c r="BY28" s="4" t="n"/>
+      <c r="BZ28" s="4" t="n"/>
+      <c r="CA28" s="4" t="n"/>
+      <c r="CB28" s="4" t="n"/>
+      <c r="CC28" s="4" t="n"/>
+      <c r="CD28" s="4" t="n"/>
+      <c r="CE28" s="4" t="n"/>
+      <c r="CF28" s="4" t="n"/>
+      <c r="CG28" s="4" t="n"/>
+      <c r="CH28" s="4" t="n"/>
+      <c r="CI28" s="3" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="CJ28" s="4" t="n"/>
+      <c r="CK28" s="4" t="n"/>
+      <c r="CL28" s="4" t="n"/>
+      <c r="CM28" s="4" t="n"/>
+      <c r="CN28" s="4" t="n"/>
+      <c r="CO28" s="4" t="n"/>
+      <c r="CP28" s="4" t="n"/>
+      <c r="CQ28" s="4" t="n"/>
+      <c r="CR28" s="4" t="n"/>
+      <c r="CS28" s="4" t="n"/>
+      <c r="CT28" s="4" t="n"/>
+      <c r="CU28" s="3" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="CV28" s="4" t="n"/>
+      <c r="CW28" s="4" t="n"/>
+      <c r="CX28" s="4" t="n"/>
+      <c r="CY28" s="4" t="n"/>
+      <c r="CZ28" s="4" t="n"/>
+      <c r="DA28" s="4" t="n"/>
+      <c r="DB28" s="4" t="n"/>
+      <c r="DC28" s="4" t="n"/>
+      <c r="DD28" s="4" t="n"/>
+      <c r="DE28" s="4" t="n"/>
+      <c r="DF28" s="4" t="n"/>
+      <c r="DG28" s="3" t="inlineStr">
+        <is>
+          <t>00h</t>
+        </is>
+      </c>
+      <c r="DH28" s="4" t="n"/>
+      <c r="DI28" s="4" t="n"/>
+      <c r="DJ28" s="4" t="n"/>
+      <c r="DK28" s="4" t="n"/>
+      <c r="DL28" s="4" t="n"/>
+      <c r="DM28" s="4" t="n"/>
+      <c r="DN28" s="4" t="n"/>
+      <c r="DO28" s="4" t="n"/>
+      <c r="DP28" s="4" t="n"/>
+      <c r="DQ28" s="4" t="n"/>
+      <c r="DR28" s="4" t="n"/>
+      <c r="DS28" s="3" t="inlineStr">
+        <is>
+          <t>01h</t>
+        </is>
+      </c>
+      <c r="DT28" s="4" t="n"/>
+      <c r="DU28" s="4" t="n"/>
+      <c r="DV28" s="4" t="n"/>
+      <c r="DW28" s="4" t="n"/>
+      <c r="DX28" s="4" t="n"/>
+      <c r="DY28" s="4" t="n"/>
+      <c r="DZ28" s="4" t="n"/>
+      <c r="EA28" s="4" t="n"/>
+      <c r="EB28" s="4" t="n"/>
+      <c r="EC28" s="4" t="n"/>
+      <c r="ED28" s="4" t="n"/>
+      <c r="EE28" s="3" t="inlineStr">
+        <is>
+          <t>02h</t>
+        </is>
+      </c>
+      <c r="EF28" s="4" t="n"/>
+      <c r="EG28" s="4" t="n"/>
+      <c r="EH28" s="4" t="n"/>
+      <c r="EI28" s="4" t="n"/>
+      <c r="EJ28" s="4" t="n"/>
+      <c r="EK28" s="4" t="n"/>
+      <c r="EL28" s="4" t="n"/>
+      <c r="EM28" s="4" t="n"/>
+      <c r="EN28" s="4" t="n"/>
+      <c r="EO28" s="4" t="n"/>
+      <c r="EP28" s="4" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="AM13:BJ13"/>
-    <mergeCell ref="U17:AL17"/>
-    <mergeCell ref="CI21:CT21"/>
-    <mergeCell ref="CO6:CZ6"/>
-    <mergeCell ref="AD6:AR6"/>
-    <mergeCell ref="BQ16:CH16"/>
-    <mergeCell ref="DA15:DL15"/>
-    <mergeCell ref="U7:AF7"/>
-    <mergeCell ref="BK13:CH13"/>
-    <mergeCell ref="BE5:BU5"/>
-    <mergeCell ref="AS8:BA8"/>
-    <mergeCell ref="O9:CH9"/>
-    <mergeCell ref="O16:AF16"/>
-    <mergeCell ref="BW3:CK3"/>
-    <mergeCell ref="AG16:AX16"/>
-    <mergeCell ref="DY4:EJ4"/>
-    <mergeCell ref="AA25:AR25"/>
-    <mergeCell ref="BQ12:CH12"/>
-    <mergeCell ref="CI16:CZ16"/>
-    <mergeCell ref="CI13:DF13"/>
+    <mergeCell ref="DE12:DW12"/>
+    <mergeCell ref="CL14:DC14"/>
+    <mergeCell ref="O5:AF5"/>
+    <mergeCell ref="AG6:AX6"/>
+    <mergeCell ref="AS12:BD12"/>
+    <mergeCell ref="U16:AF16"/>
+    <mergeCell ref="CO15:CZ15"/>
+    <mergeCell ref="AD15:AR15"/>
+    <mergeCell ref="U25:AR25"/>
+    <mergeCell ref="DA6:DL6"/>
+    <mergeCell ref="DA9:DL9"/>
+    <mergeCell ref="AY9:BP9"/>
+    <mergeCell ref="BQ22:CH22"/>
+    <mergeCell ref="CN13:DB13"/>
+    <mergeCell ref="BE14:BU14"/>
+    <mergeCell ref="AA20:AR20"/>
+    <mergeCell ref="AA26:AX26"/>
+    <mergeCell ref="CC27:CZ27"/>
+    <mergeCell ref="CI8:DF8"/>
+    <mergeCell ref="BW12:CK12"/>
+    <mergeCell ref="CT3:DB3"/>
+    <mergeCell ref="AA27:AX27"/>
+    <mergeCell ref="BK8:CH8"/>
+    <mergeCell ref="AM10:BD10"/>
     <mergeCell ref="BW18:CT18"/>
-    <mergeCell ref="DX5:EJ5"/>
-    <mergeCell ref="BE8:BP8"/>
-    <mergeCell ref="O12:AF12"/>
-    <mergeCell ref="CL5:DC5"/>
-    <mergeCell ref="CC22:CZ22"/>
-    <mergeCell ref="AS3:BD3"/>
-    <mergeCell ref="BQ15:CH15"/>
-    <mergeCell ref="BW14:CN14"/>
-    <mergeCell ref="AG12:AX12"/>
-    <mergeCell ref="AA18:AX18"/>
-    <mergeCell ref="CT8:DB8"/>
-    <mergeCell ref="BQ17:CH17"/>
-    <mergeCell ref="AA21:AX21"/>
+    <mergeCell ref="U24:AL24"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BK24:CB24"/>
+    <mergeCell ref="BH13:BS13"/>
+    <mergeCell ref="DX14:EJ14"/>
+    <mergeCell ref="O4:CH4"/>
+    <mergeCell ref="CO10:DF10"/>
+    <mergeCell ref="AS3:BA3"/>
+    <mergeCell ref="O8:AL8"/>
+    <mergeCell ref="CI9:CZ9"/>
     <mergeCell ref="BW23:CT23"/>
-    <mergeCell ref="CI12:CZ12"/>
-    <mergeCell ref="DA16:DL16"/>
-    <mergeCell ref="CN4:DB4"/>
-    <mergeCell ref="AY16:BP16"/>
-    <mergeCell ref="U20:AR20"/>
-    <mergeCell ref="U14:AL14"/>
-    <mergeCell ref="AG15:AX15"/>
-    <mergeCell ref="AY15:BP15"/>
-    <mergeCell ref="BK19:CB19"/>
-    <mergeCell ref="CI15:CZ15"/>
-    <mergeCell ref="DM7:DX7"/>
-    <mergeCell ref="U19:AL19"/>
-    <mergeCell ref="O13:AL13"/>
-    <mergeCell ref="AY12:BP12"/>
-    <mergeCell ref="AM26:BD26"/>
-    <mergeCell ref="AA22:AX22"/>
-    <mergeCell ref="BH4:BS4"/>
-    <mergeCell ref="AD8:AO8"/>
-    <mergeCell ref="AV7:BG7"/>
-    <mergeCell ref="DA12:DL12"/>
-    <mergeCell ref="CO14:DF14"/>
-    <mergeCell ref="CO20:DF20"/>
-    <mergeCell ref="BE24:BP24"/>
-    <mergeCell ref="BE6:BS6"/>
-    <mergeCell ref="AD5:AR5"/>
-    <mergeCell ref="O15:AF15"/>
-    <mergeCell ref="BZ7:CK7"/>
-    <mergeCell ref="AM14:BD14"/>
-    <mergeCell ref="BE14:BV14"/>
-    <mergeCell ref="BT8:CI8"/>
-    <mergeCell ref="CL8:CQ8"/>
-    <mergeCell ref="DE3:DW3"/>
+    <mergeCell ref="AM21:BD21"/>
+    <mergeCell ref="BZ16:CK16"/>
+    <mergeCell ref="CO25:DF25"/>
+    <mergeCell ref="AY6:BP6"/>
+    <mergeCell ref="BE19:BP19"/>
+    <mergeCell ref="U10:AL10"/>
+    <mergeCell ref="DM16:DX16"/>
+    <mergeCell ref="AG5:AX5"/>
+    <mergeCell ref="BE10:BV10"/>
+    <mergeCell ref="BW10:CN10"/>
+    <mergeCell ref="CI5:CZ5"/>
+    <mergeCell ref="BE3:BP3"/>
+    <mergeCell ref="AD3:AO3"/>
+    <mergeCell ref="AA23:AX23"/>
+    <mergeCell ref="U22:AL22"/>
+    <mergeCell ref="AV16:BG16"/>
+    <mergeCell ref="CL3:CQ3"/>
+    <mergeCell ref="CI26:CT26"/>
+    <mergeCell ref="BQ9:CH9"/>
+    <mergeCell ref="AM8:BJ8"/>
+    <mergeCell ref="DY13:EJ13"/>
+    <mergeCell ref="BE15:BS15"/>
+    <mergeCell ref="O6:AF6"/>
+    <mergeCell ref="BQ6:CH6"/>
+    <mergeCell ref="AD14:AR14"/>
+    <mergeCell ref="BT3:CI3"/>
+    <mergeCell ref="O9:AF9"/>
+    <mergeCell ref="DA5:DL5"/>
+    <mergeCell ref="BQ5:CH5"/>
+    <mergeCell ref="CI6:CZ6"/>
+    <mergeCell ref="AG9:AX9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.3" bottom="0.3" header="0" footer="0"/>
